--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49409D4-92C5-41EE-8EF4-C7F7A4521FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C14FF6C-F29E-499C-8074-4F442EAFBBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="16" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="16" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -32,7 +32,8 @@
     <sheet name="Line Objects" sheetId="28" r:id="rId17"/>
     <sheet name="Surface Objects" sheetId="29" r:id="rId18"/>
     <sheet name="Restraints" sheetId="18" r:id="rId19"/>
-    <sheet name="Loads" sheetId="19" r:id="rId20"/>
+    <sheet name="Surface Loads" sheetId="32" r:id="rId20"/>
+    <sheet name="Loads" sheetId="19" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="Base_Mat">Materials!$A$14:$A$1013</definedName>
@@ -109,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="344">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1185,6 +1186,9 @@
   <si>
     <t>- J-End: Point object at the end (J) of the line object (Choose from the list)</t>
   </si>
+  <si>
+    <t>Surface Object</t>
+  </si>
 </sst>
 </file>
 
@@ -1411,7 +1415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2011,6 +2015,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -45999,6 +46004,24 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8BF8F5-8B72-4F82-8AD5-2105268CD711}">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="211"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="211" t="s">
+        <v>343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B39FACB-756A-E348-83BC-C70442772EC8}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:E7"/>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C14FF6C-F29E-499C-8074-4F442EAFBBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC49BA5-A280-48C0-8943-34D8AAB5876D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="16" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="15" activeTab="21" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -32,8 +32,11 @@
     <sheet name="Line Objects" sheetId="28" r:id="rId17"/>
     <sheet name="Surface Objects" sheetId="29" r:id="rId18"/>
     <sheet name="Restraints" sheetId="18" r:id="rId19"/>
-    <sheet name="Surface Loads" sheetId="32" r:id="rId20"/>
-    <sheet name="Loads" sheetId="19" r:id="rId21"/>
+    <sheet name="Point Loads" sheetId="32" r:id="rId20"/>
+    <sheet name="Concentrated Line Loads" sheetId="33" r:id="rId21"/>
+    <sheet name="Distributed Line Loads" sheetId="34" r:id="rId22"/>
+    <sheet name="Surface Loads" sheetId="36" r:id="rId23"/>
+    <sheet name="Loads" sheetId="19" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="Base_Mat">Materials!$A$14:$A$1013</definedName>
@@ -88,7 +91,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -110,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="366">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1187,7 +1190,73 @@
     <t>- J-End: Point object at the end (J) of the line object (Choose from the list)</t>
   </si>
   <si>
-    <t>Surface Object</t>
+    <t>FX</t>
+  </si>
+  <si>
+    <t>FY</t>
+  </si>
+  <si>
+    <t>FZ</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>MY</t>
+  </si>
+  <si>
+    <t>MZ</t>
+  </si>
+  <si>
+    <t>Load Case</t>
+  </si>
+  <si>
+    <t>Line</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>- Point: Point name to be subjected point load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Load Case: Load case of subjected point load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Line: Line name to be subjected line point load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Load Case: Load case of subjected line point load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Direction: Direction of subjected line point load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Line: Line name to be subjected line distributed load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Load Case: Load case of subjected line distributed load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Direction: Direction of subjected line distributed load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>- Surface: Surface name to be subjected surface load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>Load</t>
+  </si>
+  <si>
+    <t>- Load Case: Load case of subjected surface load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Direction: Direction of subjected surface load (Choose from the list)</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1994,6 +2063,9 @@
     </xf>
     <xf numFmtId="1" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2013,9 +2085,44 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12790,23 +12897,23 @@
       <c r="AE4" s="109"/>
     </row>
     <row r="5" spans="1:31" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="204" t="s">
+      <c r="A5" s="205" t="s">
         <v>241</v>
       </c>
-      <c r="B5" s="205"/>
-      <c r="C5" s="205"/>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="205"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="205"/>
-      <c r="L5" s="205"/>
-      <c r="M5" s="205"/>
-      <c r="N5" s="205"/>
-      <c r="O5" s="206"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="206"/>
+      <c r="D5" s="206"/>
+      <c r="E5" s="206"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="206"/>
+      <c r="H5" s="206"/>
+      <c r="I5" s="206"/>
+      <c r="J5" s="206"/>
+      <c r="K5" s="206"/>
+      <c r="L5" s="206"/>
+      <c r="M5" s="206"/>
+      <c r="N5" s="206"/>
+      <c r="O5" s="207"/>
       <c r="P5" s="141" t="s">
         <v>248</v>
       </c>
@@ -12827,23 +12934,23 @@
       <c r="AE5" s="109"/>
     </row>
     <row r="6" spans="1:31" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="205" t="s">
         <v>242</v>
       </c>
-      <c r="B6" s="205"/>
-      <c r="C6" s="205"/>
-      <c r="D6" s="205"/>
-      <c r="E6" s="205"/>
-      <c r="F6" s="205"/>
-      <c r="G6" s="205"/>
-      <c r="H6" s="205"/>
-      <c r="I6" s="205"/>
-      <c r="J6" s="205"/>
-      <c r="K6" s="205"/>
-      <c r="L6" s="205"/>
-      <c r="M6" s="205"/>
-      <c r="N6" s="205"/>
-      <c r="O6" s="206"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="206"/>
+      <c r="E6" s="206"/>
+      <c r="F6" s="206"/>
+      <c r="G6" s="206"/>
+      <c r="H6" s="206"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="206"/>
+      <c r="K6" s="206"/>
+      <c r="L6" s="206"/>
+      <c r="M6" s="206"/>
+      <c r="N6" s="206"/>
+      <c r="O6" s="207"/>
       <c r="P6" s="141" t="s">
         <v>249</v>
       </c>
@@ -13016,23 +13123,23 @@
       <c r="AE10" s="109"/>
     </row>
     <row r="11" spans="1:31" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="204" t="s">
+      <c r="A11" s="205" t="s">
         <v>251</v>
       </c>
-      <c r="B11" s="205"/>
-      <c r="C11" s="205"/>
-      <c r="D11" s="205"/>
-      <c r="E11" s="205"/>
-      <c r="F11" s="205"/>
-      <c r="G11" s="205"/>
-      <c r="H11" s="205"/>
-      <c r="I11" s="205"/>
-      <c r="J11" s="205"/>
-      <c r="K11" s="205"/>
-      <c r="L11" s="205"/>
-      <c r="M11" s="205"/>
-      <c r="N11" s="205"/>
-      <c r="O11" s="206"/>
+      <c r="B11" s="206"/>
+      <c r="C11" s="206"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="206"/>
+      <c r="G11" s="206"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="206"/>
+      <c r="J11" s="206"/>
+      <c r="K11" s="206"/>
+      <c r="L11" s="206"/>
+      <c r="M11" s="206"/>
+      <c r="N11" s="206"/>
+      <c r="O11" s="207"/>
       <c r="P11" s="141" t="s">
         <v>258</v>
       </c>
@@ -13053,23 +13160,23 @@
       <c r="AE11" s="109"/>
     </row>
     <row r="12" spans="1:31" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="204" t="s">
+      <c r="A12" s="205" t="s">
         <v>252</v>
       </c>
-      <c r="B12" s="205"/>
-      <c r="C12" s="205"/>
-      <c r="D12" s="205"/>
-      <c r="E12" s="205"/>
-      <c r="F12" s="205"/>
-      <c r="G12" s="205"/>
-      <c r="H12" s="205"/>
-      <c r="I12" s="205"/>
-      <c r="J12" s="205"/>
-      <c r="K12" s="205"/>
-      <c r="L12" s="205"/>
-      <c r="M12" s="205"/>
-      <c r="N12" s="205"/>
-      <c r="O12" s="206"/>
+      <c r="B12" s="206"/>
+      <c r="C12" s="206"/>
+      <c r="D12" s="206"/>
+      <c r="E12" s="206"/>
+      <c r="F12" s="206"/>
+      <c r="G12" s="206"/>
+      <c r="H12" s="206"/>
+      <c r="I12" s="206"/>
+      <c r="J12" s="206"/>
+      <c r="K12" s="206"/>
+      <c r="L12" s="206"/>
+      <c r="M12" s="206"/>
+      <c r="N12" s="206"/>
+      <c r="O12" s="207"/>
       <c r="P12" s="141" t="s">
         <v>259</v>
       </c>
@@ -13201,23 +13308,23 @@
       <c r="AE15" s="109"/>
     </row>
     <row r="16" spans="1:31" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="207" t="s">
+      <c r="A16" s="208" t="s">
         <v>244</v>
       </c>
-      <c r="B16" s="208"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="208"/>
-      <c r="E16" s="208"/>
-      <c r="F16" s="208"/>
-      <c r="G16" s="208"/>
-      <c r="H16" s="208"/>
-      <c r="I16" s="208"/>
-      <c r="J16" s="208"/>
-      <c r="K16" s="208"/>
-      <c r="L16" s="208"/>
-      <c r="M16" s="208"/>
-      <c r="N16" s="208"/>
-      <c r="O16" s="209"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+      <c r="F16" s="209"/>
+      <c r="G16" s="209"/>
+      <c r="H16" s="209"/>
+      <c r="I16" s="209"/>
+      <c r="J16" s="209"/>
+      <c r="K16" s="209"/>
+      <c r="L16" s="209"/>
+      <c r="M16" s="209"/>
+      <c r="N16" s="209"/>
+      <c r="O16" s="210"/>
       <c r="P16" s="141" t="s">
         <v>263</v>
       </c>
@@ -34870,10 +34977,10 @@
       <c r="D16" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="210" t="s">
+      <c r="E16" s="204" t="s">
         <v>207</v>
       </c>
-      <c r="F16" s="210">
+      <c r="F16" s="204">
         <v>1</v>
       </c>
       <c r="G16" s="98">
@@ -34905,7 +35012,7 @@
       <c r="E17" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F17" s="210">
+      <c r="F17" s="204">
         <v>1</v>
       </c>
       <c r="G17" s="98">
@@ -34937,7 +35044,7 @@
       <c r="E18" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F18" s="210">
+      <c r="F18" s="204">
         <v>1</v>
       </c>
       <c r="G18" s="98">
@@ -34969,7 +35076,7 @@
       <c r="E19" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F19" s="210">
+      <c r="F19" s="204">
         <v>1</v>
       </c>
       <c r="G19" s="98">
@@ -35001,7 +35108,7 @@
       <c r="E20" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F20" s="210">
+      <c r="F20" s="204">
         <v>1</v>
       </c>
       <c r="G20" s="98">
@@ -35033,7 +35140,7 @@
       <c r="E21" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F21" s="210">
+      <c r="F21" s="204">
         <v>1</v>
       </c>
       <c r="G21" s="98">
@@ -35065,7 +35172,7 @@
       <c r="E22" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F22" s="210">
+      <c r="F22" s="204">
         <v>1</v>
       </c>
       <c r="G22" s="98">
@@ -35097,7 +35204,7 @@
       <c r="E23" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F23" s="210">
+      <c r="F23" s="204">
         <v>1</v>
       </c>
       <c r="G23" s="98">
@@ -35129,7 +35236,7 @@
       <c r="E24" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F24" s="210">
+      <c r="F24" s="204">
         <v>1</v>
       </c>
       <c r="G24" s="98">
@@ -35161,7 +35268,7 @@
       <c r="E25" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F25" s="210">
+      <c r="F25" s="204">
         <v>1</v>
       </c>
       <c r="G25" s="98">
@@ -35193,7 +35300,7 @@
       <c r="E26" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F26" s="210">
+      <c r="F26" s="204">
         <v>1</v>
       </c>
       <c r="G26" s="98">
@@ -35225,7 +35332,7 @@
       <c r="E27" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F27" s="210">
+      <c r="F27" s="204">
         <v>1</v>
       </c>
       <c r="G27" s="98">
@@ -35257,7 +35364,7 @@
       <c r="E28" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F28" s="210">
+      <c r="F28" s="204">
         <v>1</v>
       </c>
       <c r="G28" s="98">
@@ -35289,7 +35396,7 @@
       <c r="E29" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F29" s="210">
+      <c r="F29" s="204">
         <v>1</v>
       </c>
       <c r="G29" s="98">
@@ -35321,7 +35428,7 @@
       <c r="E30" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F30" s="210">
+      <c r="F30" s="204">
         <v>1</v>
       </c>
       <c r="G30" s="98">
@@ -35353,7 +35460,7 @@
       <c r="E31" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F31" s="210">
+      <c r="F31" s="204">
         <v>1</v>
       </c>
       <c r="G31" s="98">
@@ -35385,7 +35492,7 @@
       <c r="E32" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F32" s="210">
+      <c r="F32" s="204">
         <v>1</v>
       </c>
       <c r="G32" s="98">
@@ -35417,7 +35524,7 @@
       <c r="E33" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F33" s="210">
+      <c r="F33" s="204">
         <v>1</v>
       </c>
       <c r="G33" s="98">
@@ -35449,7 +35556,7 @@
       <c r="E34" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F34" s="210">
+      <c r="F34" s="204">
         <v>1</v>
       </c>
       <c r="G34" s="98">
@@ -35481,7 +35588,7 @@
       <c r="E35" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F35" s="210">
+      <c r="F35" s="204">
         <v>1</v>
       </c>
       <c r="G35" s="98">
@@ -35513,7 +35620,7 @@
       <c r="E36" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F36" s="210">
+      <c r="F36" s="204">
         <v>1</v>
       </c>
       <c r="G36" s="98">
@@ -35545,7 +35652,7 @@
       <c r="E37" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F37" s="210">
+      <c r="F37" s="204">
         <v>1</v>
       </c>
       <c r="G37" s="98">
@@ -35577,7 +35684,7 @@
       <c r="E38" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F38" s="210">
+      <c r="F38" s="204">
         <v>1</v>
       </c>
       <c r="G38" s="98">
@@ -35609,7 +35716,7 @@
       <c r="E39" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F39" s="210">
+      <c r="F39" s="204">
         <v>1</v>
       </c>
       <c r="G39" s="98">
@@ -35641,7 +35748,7 @@
       <c r="E40" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F40" s="210">
+      <c r="F40" s="204">
         <v>1</v>
       </c>
       <c r="G40" s="98">
@@ -35673,7 +35780,7 @@
       <c r="E41" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F41" s="210">
+      <c r="F41" s="204">
         <v>1</v>
       </c>
       <c r="G41" s="98">
@@ -35705,7 +35812,7 @@
       <c r="E42" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F42" s="210">
+      <c r="F42" s="204">
         <v>1</v>
       </c>
       <c r="G42" s="98">
@@ -35737,7 +35844,7 @@
       <c r="E43" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F43" s="210">
+      <c r="F43" s="204">
         <v>1</v>
       </c>
       <c r="G43" s="98">
@@ -35769,7 +35876,7 @@
       <c r="E44" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F44" s="210">
+      <c r="F44" s="204">
         <v>1</v>
       </c>
       <c r="G44" s="98">
@@ -35801,7 +35908,7 @@
       <c r="E45" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F45" s="210">
+      <c r="F45" s="204">
         <v>1</v>
       </c>
       <c r="G45" s="98">
@@ -35833,7 +35940,7 @@
       <c r="E46" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F46" s="210">
+      <c r="F46" s="204">
         <v>1</v>
       </c>
       <c r="G46" s="98">
@@ -35865,7 +35972,7 @@
       <c r="E47" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F47" s="210">
+      <c r="F47" s="204">
         <v>1</v>
       </c>
       <c r="G47" s="98">
@@ -35897,7 +36004,7 @@
       <c r="E48" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F48" s="210">
+      <c r="F48" s="204">
         <v>1</v>
       </c>
       <c r="G48" s="98">
@@ -35929,7 +36036,7 @@
       <c r="E49" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F49" s="210">
+      <c r="F49" s="204">
         <v>1</v>
       </c>
       <c r="G49" s="98">
@@ -35961,7 +36068,7 @@
       <c r="E50" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F50" s="210">
+      <c r="F50" s="204">
         <v>1</v>
       </c>
       <c r="G50" s="98">
@@ -35993,7 +36100,7 @@
       <c r="E51" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F51" s="210">
+      <c r="F51" s="204">
         <v>1</v>
       </c>
       <c r="G51" s="98">
@@ -36025,7 +36132,7 @@
       <c r="E52" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F52" s="210">
+      <c r="F52" s="204">
         <v>1</v>
       </c>
       <c r="G52" s="98">
@@ -36057,7 +36164,7 @@
       <c r="E53" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F53" s="210">
+      <c r="F53" s="204">
         <v>1</v>
       </c>
       <c r="G53" s="98">
@@ -36089,7 +36196,7 @@
       <c r="E54" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F54" s="210">
+      <c r="F54" s="204">
         <v>1</v>
       </c>
       <c r="G54" s="98">
@@ -36121,7 +36228,7 @@
       <c r="E55" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F55" s="210">
+      <c r="F55" s="204">
         <v>1</v>
       </c>
       <c r="G55" s="98">
@@ -36153,7 +36260,7 @@
       <c r="E56" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F56" s="210">
+      <c r="F56" s="204">
         <v>1</v>
       </c>
       <c r="G56" s="98">
@@ -36185,7 +36292,7 @@
       <c r="E57" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F57" s="210">
+      <c r="F57" s="204">
         <v>1</v>
       </c>
       <c r="G57" s="98">
@@ -36217,7 +36324,7 @@
       <c r="E58" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F58" s="210">
+      <c r="F58" s="204">
         <v>1</v>
       </c>
       <c r="G58" s="98">
@@ -36249,7 +36356,7 @@
       <c r="E59" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F59" s="210">
+      <c r="F59" s="204">
         <v>1</v>
       </c>
       <c r="G59" s="98">
@@ -36281,7 +36388,7 @@
       <c r="E60" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F60" s="210">
+      <c r="F60" s="204">
         <v>1</v>
       </c>
       <c r="G60" s="98">
@@ -36313,7 +36420,7 @@
       <c r="E61" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F61" s="210">
+      <c r="F61" s="204">
         <v>1</v>
       </c>
       <c r="G61" s="98">
@@ -36345,7 +36452,7 @@
       <c r="E62" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F62" s="210">
+      <c r="F62" s="204">
         <v>1</v>
       </c>
       <c r="G62" s="98">
@@ -36377,7 +36484,7 @@
       <c r="E63" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F63" s="210">
+      <c r="F63" s="204">
         <v>1</v>
       </c>
       <c r="G63" s="98">
@@ -36409,7 +36516,7 @@
       <c r="E64" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F64" s="210">
+      <c r="F64" s="204">
         <v>1</v>
       </c>
       <c r="G64" s="98">
@@ -36441,7 +36548,7 @@
       <c r="E65" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F65" s="210">
+      <c r="F65" s="204">
         <v>1</v>
       </c>
       <c r="G65" s="98">
@@ -36473,7 +36580,7 @@
       <c r="E66" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F66" s="210">
+      <c r="F66" s="204">
         <v>1</v>
       </c>
       <c r="G66" s="98">
@@ -36505,7 +36612,7 @@
       <c r="E67" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F67" s="210">
+      <c r="F67" s="204">
         <v>1</v>
       </c>
       <c r="G67" s="98">
@@ -36537,7 +36644,7 @@
       <c r="E68" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F68" s="210">
+      <c r="F68" s="204">
         <v>1</v>
       </c>
       <c r="G68" s="98">
@@ -36569,7 +36676,7 @@
       <c r="E69" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F69" s="210">
+      <c r="F69" s="204">
         <v>1</v>
       </c>
       <c r="G69" s="98">
@@ -36601,7 +36708,7 @@
       <c r="E70" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F70" s="210">
+      <c r="F70" s="204">
         <v>1</v>
       </c>
       <c r="G70" s="98">
@@ -36633,7 +36740,7 @@
       <c r="E71" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F71" s="210">
+      <c r="F71" s="204">
         <v>1</v>
       </c>
       <c r="G71" s="98">
@@ -36665,7 +36772,7 @@
       <c r="E72" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F72" s="210">
+      <c r="F72" s="204">
         <v>1</v>
       </c>
       <c r="G72" s="98">
@@ -36697,7 +36804,7 @@
       <c r="E73" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F73" s="210">
+      <c r="F73" s="204">
         <v>1</v>
       </c>
       <c r="G73" s="98">
@@ -36729,7 +36836,7 @@
       <c r="E74" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F74" s="210">
+      <c r="F74" s="204">
         <v>1</v>
       </c>
       <c r="G74" s="98">
@@ -36761,7 +36868,7 @@
       <c r="E75" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F75" s="210">
+      <c r="F75" s="204">
         <v>1</v>
       </c>
       <c r="G75" s="98">
@@ -36793,7 +36900,7 @@
       <c r="E76" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F76" s="210">
+      <c r="F76" s="204">
         <v>1</v>
       </c>
       <c r="G76" s="98">
@@ -36825,7 +36932,7 @@
       <c r="E77" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F77" s="210">
+      <c r="F77" s="204">
         <v>1</v>
       </c>
       <c r="G77" s="98">
@@ -36857,7 +36964,7 @@
       <c r="E78" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F78" s="210">
+      <c r="F78" s="204">
         <v>1</v>
       </c>
       <c r="G78" s="98">
@@ -36889,7 +36996,7 @@
       <c r="E79" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F79" s="210">
+      <c r="F79" s="204">
         <v>1</v>
       </c>
       <c r="G79" s="98">
@@ -36921,7 +37028,7 @@
       <c r="E80" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F80" s="210">
+      <c r="F80" s="204">
         <v>1</v>
       </c>
       <c r="G80" s="98">
@@ -36953,7 +37060,7 @@
       <c r="E81" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F81" s="210">
+      <c r="F81" s="204">
         <v>1</v>
       </c>
       <c r="G81" s="98">
@@ -36985,7 +37092,7 @@
       <c r="E82" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F82" s="210">
+      <c r="F82" s="204">
         <v>1</v>
       </c>
       <c r="G82" s="98">
@@ -37017,7 +37124,7 @@
       <c r="E83" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F83" s="210">
+      <c r="F83" s="204">
         <v>1</v>
       </c>
       <c r="G83" s="98">
@@ -37049,7 +37156,7 @@
       <c r="E84" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F84" s="210">
+      <c r="F84" s="204">
         <v>1</v>
       </c>
       <c r="G84" s="98">
@@ -37081,7 +37188,7 @@
       <c r="E85" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F85" s="210">
+      <c r="F85" s="204">
         <v>1</v>
       </c>
       <c r="G85" s="98">
@@ -37113,7 +37220,7 @@
       <c r="E86" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F86" s="210">
+      <c r="F86" s="204">
         <v>1</v>
       </c>
       <c r="G86" s="98">
@@ -37145,7 +37252,7 @@
       <c r="E87" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F87" s="210">
+      <c r="F87" s="204">
         <v>1</v>
       </c>
       <c r="G87" s="98">
@@ -37177,7 +37284,7 @@
       <c r="E88" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F88" s="210">
+      <c r="F88" s="204">
         <v>1</v>
       </c>
       <c r="G88" s="98">
@@ -37209,7 +37316,7 @@
       <c r="E89" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F89" s="210">
+      <c r="F89" s="204">
         <v>1</v>
       </c>
       <c r="G89" s="98">
@@ -37241,7 +37348,7 @@
       <c r="E90" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F90" s="210">
+      <c r="F90" s="204">
         <v>1</v>
       </c>
       <c r="G90" s="98">
@@ -37273,7 +37380,7 @@
       <c r="E91" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F91" s="210">
+      <c r="F91" s="204">
         <v>1</v>
       </c>
       <c r="G91" s="98">
@@ -37305,7 +37412,7 @@
       <c r="E92" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F92" s="210">
+      <c r="F92" s="204">
         <v>1</v>
       </c>
       <c r="G92" s="98">
@@ -37337,7 +37444,7 @@
       <c r="E93" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F93" s="210">
+      <c r="F93" s="204">
         <v>1</v>
       </c>
       <c r="G93" s="98">
@@ -37369,7 +37476,7 @@
       <c r="E94" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F94" s="210">
+      <c r="F94" s="204">
         <v>1</v>
       </c>
       <c r="G94" s="98">
@@ -37401,7 +37508,7 @@
       <c r="E95" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F95" s="210">
+      <c r="F95" s="204">
         <v>1</v>
       </c>
       <c r="G95" s="98">
@@ -37433,7 +37540,7 @@
       <c r="E96" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F96" s="210">
+      <c r="F96" s="204">
         <v>1</v>
       </c>
       <c r="G96" s="98">
@@ -37465,7 +37572,7 @@
       <c r="E97" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F97" s="210">
+      <c r="F97" s="204">
         <v>1</v>
       </c>
       <c r="G97" s="98">
@@ -37497,7 +37604,7 @@
       <c r="E98" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F98" s="210">
+      <c r="F98" s="204">
         <v>1</v>
       </c>
       <c r="G98" s="98">
@@ -37529,7 +37636,7 @@
       <c r="E99" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F99" s="210">
+      <c r="F99" s="204">
         <v>1</v>
       </c>
       <c r="G99" s="98">
@@ -37561,7 +37668,7 @@
       <c r="E100" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F100" s="210">
+      <c r="F100" s="204">
         <v>1</v>
       </c>
       <c r="G100" s="98">
@@ -37593,7 +37700,7 @@
       <c r="E101" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F101" s="210">
+      <c r="F101" s="204">
         <v>1</v>
       </c>
       <c r="G101" s="98">
@@ -37625,7 +37732,7 @@
       <c r="E102" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F102" s="210">
+      <c r="F102" s="204">
         <v>1</v>
       </c>
       <c r="G102" s="98">
@@ -37657,7 +37764,7 @@
       <c r="E103" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F103" s="210">
+      <c r="F103" s="204">
         <v>1</v>
       </c>
       <c r="G103" s="98">
@@ -37689,7 +37796,7 @@
       <c r="E104" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F104" s="210">
+      <c r="F104" s="204">
         <v>1</v>
       </c>
       <c r="G104" s="98">
@@ -37721,7 +37828,7 @@
       <c r="E105" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F105" s="210">
+      <c r="F105" s="204">
         <v>1</v>
       </c>
       <c r="G105" s="98">
@@ -37753,7 +37860,7 @@
       <c r="E106" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F106" s="210">
+      <c r="F106" s="204">
         <v>1</v>
       </c>
       <c r="G106" s="98">
@@ -37785,7 +37892,7 @@
       <c r="E107" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F107" s="210">
+      <c r="F107" s="204">
         <v>1</v>
       </c>
       <c r="G107" s="98">
@@ -37817,7 +37924,7 @@
       <c r="E108" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F108" s="210">
+      <c r="F108" s="204">
         <v>1</v>
       </c>
       <c r="G108" s="98">
@@ -37849,7 +37956,7 @@
       <c r="E109" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F109" s="210">
+      <c r="F109" s="204">
         <v>1</v>
       </c>
       <c r="G109" s="98">
@@ -37881,7 +37988,7 @@
       <c r="E110" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F110" s="210">
+      <c r="F110" s="204">
         <v>1</v>
       </c>
       <c r="G110" s="98">
@@ -37913,7 +38020,7 @@
       <c r="E111" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F111" s="210">
+      <c r="F111" s="204">
         <v>1</v>
       </c>
       <c r="G111" s="98">
@@ -37945,7 +38052,7 @@
       <c r="E112" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F112" s="210">
+      <c r="F112" s="204">
         <v>1</v>
       </c>
       <c r="G112" s="98">
@@ -37977,7 +38084,7 @@
       <c r="E113" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F113" s="210">
+      <c r="F113" s="204">
         <v>1</v>
       </c>
       <c r="G113" s="98">
@@ -38009,7 +38116,7 @@
       <c r="E114" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F114" s="210">
+      <c r="F114" s="204">
         <v>1</v>
       </c>
       <c r="G114" s="98">
@@ -38041,7 +38148,7 @@
       <c r="E115" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="F115" s="210">
+      <c r="F115" s="204">
         <v>1</v>
       </c>
       <c r="G115" s="98">
@@ -46005,23 +46112,500 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8BF8F5-8B72-4F82-8AD5-2105268CD711}">
-  <dimension ref="A2"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="211"/>
+    <col min="1" max="2" width="15.7109375" style="222" customWidth="1"/>
+    <col min="3" max="8" width="10.7109375" style="223" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="211"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="211" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="213" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="215"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="216" t="s">
+        <v>353</v>
+      </c>
+      <c r="B2" s="217"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="218"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="216" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3" s="217"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="217"/>
+      <c r="F3" s="217"/>
+      <c r="G3" s="217"/>
+      <c r="H3" s="218"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="216" t="str">
+        <f>"- FX: Force along global X-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
+        <v>- FX: Force along global X-axis (Input as Float) (kN)</v>
+      </c>
+      <c r="B4" s="217"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="217"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="218"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="216" t="str">
+        <f>"- FY: Force along global Y-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
+        <v>- FY: Force along global Y-axis (Input as Float) (kN)</v>
+      </c>
+      <c r="B5" s="217"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="218"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="216" t="str">
+        <f>"- FZ: Force along global Z-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
+        <v>- FZ: Force along global Z-axis (Input as Float) (kN)</v>
+      </c>
+      <c r="B6" s="217"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="218"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="216" t="str">
+        <f>"- MX: Moment about global X-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"-"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- MX: Moment about global X-axis (Input as Float) (kN-m)</v>
+      </c>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="218"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="216" t="str">
+        <f>"- MY: Moment about global Y-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"-"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- MY: Moment about global Y-axis (Input as Float) (kN-m)</v>
+      </c>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="217"/>
+      <c r="F8" s="217"/>
+      <c r="G8" s="217"/>
+      <c r="H8" s="218"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="219" t="str">
+        <f>"- MZ: Moment about global Z-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"-"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- MZ: Moment about global Z-axis (Input as Float) (kN-m)</v>
+      </c>
+      <c r="B9" s="220"/>
+      <c r="C9" s="220"/>
+      <c r="D9" s="220"/>
+      <c r="E9" s="220"/>
+      <c r="F9" s="220"/>
+      <c r="G9" s="220"/>
+      <c r="H9" s="221"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="211"/>
+      <c r="B10" s="211"/>
+      <c r="C10" s="211"/>
+      <c r="D10" s="211"/>
+      <c r="E10" s="211"/>
+      <c r="F10" s="211"/>
+      <c r="G10" s="211"/>
+      <c r="H10" s="211"/>
+    </row>
+    <row r="11" spans="1:8" s="196" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="212" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11" s="212" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" s="212" t="s">
         <v>343</v>
       </c>
+      <c r="D11" s="212" t="s">
+        <v>344</v>
+      </c>
+      <c r="E11" s="212" t="s">
+        <v>345</v>
+      </c>
+      <c r="F11" s="212" t="s">
+        <v>346</v>
+      </c>
+      <c r="G11" s="212" t="s">
+        <v>347</v>
+      </c>
+      <c r="H11" s="212" t="s">
+        <v>348</v>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A12:A1048576" xr:uid="{EA426CEF-76D2-46B7-BCF5-9565E78F0EB2}">
+      <formula1>Point_ID</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="C12:H1048576" xr:uid="{FF595AA7-A6E3-4769-9683-1BD41C8B25C0}">
+      <formula1>-1000000000000</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B12:B1048576" xr:uid="{E93D2070-1536-4868-9F08-ED7C2E7CB253}">
+      <formula1>LC_Type</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105CF277-1F6A-492D-8E1A-EC3101EF3425}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="223" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="223" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="211"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="213" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="215"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="216" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" s="217"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="218"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="216" t="s">
+        <v>356</v>
+      </c>
+      <c r="B3" s="217"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="218"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="216" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="217"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="218"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="216" t="str">
+        <f>"- Load: Value of subjected line point load (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
+        <v>- Load: Value of subjected line point load (Input as Float) (kN)</v>
+      </c>
+      <c r="B5" s="217"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="218"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="219" t="str">
+        <f>"- Location: Location of subjected line point load (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location: Location of subjected line point load (Input as Float) (m)</v>
+      </c>
+      <c r="B6" s="220"/>
+      <c r="C6" s="220"/>
+      <c r="D6" s="220"/>
+      <c r="E6" s="221"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="211"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+    </row>
+    <row r="8" spans="1:5" s="196" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="212" t="s">
+        <v>350</v>
+      </c>
+      <c r="B8" s="212" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="212" t="s">
+        <v>352</v>
+      </c>
+      <c r="D8" s="212" t="s">
+        <v>363</v>
+      </c>
+      <c r="E8" s="212" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B9:B1048576" xr:uid="{8399D4E5-15D3-44EB-BAF5-D4D9376E21A9}">
+      <formula1>LC_Type</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A9:A1048576" xr:uid="{E806BA54-F03E-4170-B409-665005B7362E}">
+      <formula1>Line_ID</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="D9:E1048576" xr:uid="{6DEDB52A-6E32-4CDB-9BBB-C36A5BFBDF1F}">
+      <formula1>-1000000000000</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C9:C1048576" xr:uid="{C69DB190-B0B4-41DC-BB24-EADCC7640530}">
+      <formula1>"Global-X, Global-Y, Gravity, Local-x, Local-y, Local-z"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAB727D-5FF3-4C5E-99AD-1C31CEAF2053}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="196" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="196" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="211"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="213" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="215"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="216" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" s="217"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="218"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="216" t="s">
+        <v>359</v>
+      </c>
+      <c r="B3" s="217"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="218"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="216" t="s">
+        <v>360</v>
+      </c>
+      <c r="B4" s="217"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="218"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="216" t="str">
+        <f>"- Load: Value of subjected line distributed load (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"/"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Load: Value of subjected line distributed load (Input as Float) (kN/m)</v>
+      </c>
+      <c r="B5" s="217"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="218"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="219" t="str">
+        <f>"- Location: Location of subjected line distributed load (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location: Location of subjected line distributed load (Input as Float) (m)</v>
+      </c>
+      <c r="B6" s="220"/>
+      <c r="C6" s="220"/>
+      <c r="D6" s="220"/>
+      <c r="E6" s="221"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="211"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
+      <c r="D7" s="211"/>
+      <c r="E7" s="211"/>
+    </row>
+    <row r="8" spans="1:5" s="196" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="212" t="s">
+        <v>350</v>
+      </c>
+      <c r="B8" s="212" t="s">
+        <v>349</v>
+      </c>
+      <c r="C8" s="212" t="s">
+        <v>352</v>
+      </c>
+      <c r="D8" s="212" t="s">
+        <v>363</v>
+      </c>
+      <c r="E8" s="212" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations disablePrompts="1" count="4">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C9:C1048576" xr:uid="{A06960A0-574A-4091-89DC-3EAC93A1B00B}">
+      <formula1>"Global-X, Global-Y, Gravity, Local-x, Local-y, Local-z"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="D9:E1048576" xr:uid="{DF4D0C80-0563-4CC2-B0A8-6B52582B452C}">
+      <formula1>-1000000000000</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A9:A1048576" xr:uid="{CFFEC136-BD4D-41A8-9172-2C735BE136D8}">
+      <formula1>Line_ID</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B9:B1048576" xr:uid="{E3D690A9-3459-485B-9D38-6E5066FAA865}">
+      <formula1>LC_Type</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10204173-8D21-44EB-9119-A6BC046B304C}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="196" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="211"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="213" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="215"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="216" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2" s="217"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="218"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="216" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="217"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="218"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="216" t="s">
+        <v>365</v>
+      </c>
+      <c r="B4" s="217"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="218"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="219" t="str">
+        <f>"- Load: Value of subjected surface load (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"/"&amp;'User Defined Units'!$B$11&amp;"2)"</f>
+        <v>- Load: Value of subjected surface load (Input as Float) (kN/m2)</v>
+      </c>
+      <c r="B5" s="220"/>
+      <c r="C5" s="220"/>
+      <c r="D5" s="220"/>
+      <c r="E5" s="221"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="211"/>
+      <c r="B6" s="211"/>
+      <c r="C6" s="211"/>
+      <c r="D6" s="211"/>
+    </row>
+    <row r="7" spans="1:5" s="196" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="212" t="s">
+        <v>361</v>
+      </c>
+      <c r="B7" s="212" t="s">
+        <v>349</v>
+      </c>
+      <c r="C7" s="212" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="212" t="s">
+        <v>363</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B8:B1048576" xr:uid="{1512AF2D-8ABF-408B-A5A3-341A7F908033}">
+      <formula1>LC_Type</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A8:A1048576" xr:uid="{0FB351FE-4722-4B30-B2C7-F77C6F4CB4C8}">
+      <formula1>Surface_ID</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="D8:D1048576" xr:uid="{5938BB6D-6A18-4E94-99C8-7CE9A4B4114A}">
+      <formula1>-1000000000000</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C8:C1048576" xr:uid="{A58E8B81-98B3-44AB-B60D-4C93D87E3A91}">
+      <formula1>"Global-X, Global-Y, Gravity, Local-x, Local-y, Local-z"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B39FACB-756A-E348-83BC-C70442772EC8}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:E7"/>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC49BA5-A280-48C0-8943-34D8AAB5876D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3F47C7-71F3-4B79-BDD4-B8C61CAEF0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="15" activeTab="21" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="19" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="375">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1169,9 +1169,6 @@
     </r>
   </si>
   <si>
-    <t>- Material: Material 1 of fiber section, if fiber section is concrete, set this column with material of concrete core (Choose from the list)</t>
-  </si>
-  <si>
     <t>- Material: Material of slab section (Choose from the list)</t>
   </si>
   <si>
@@ -1214,7 +1211,7 @@
     <t>Line</t>
   </si>
   <si>
-    <t>Location</t>
+    <t>Gravity</t>
   </si>
   <si>
     <t>Direction</t>
@@ -1232,18 +1229,6 @@
     <t>- Load Case: Load case of subjected line point load (Choose from the list)</t>
   </si>
   <si>
-    <t>- Direction: Direction of subjected line point load (Choose from the list)</t>
-  </si>
-  <si>
-    <t>- Line: Line name to be subjected line distributed load (Choose from the list)</t>
-  </si>
-  <si>
-    <t>- Load Case: Load case of subjected line distributed load (Choose from the list)</t>
-  </si>
-  <si>
-    <t>- Direction: Direction of subjected line distributed load (Choose from the list)</t>
-  </si>
-  <si>
     <t>Surface</t>
   </si>
   <si>
@@ -1257,6 +1242,48 @@
   </si>
   <si>
     <t>- Direction: Direction of subjected surface load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>Load 1</t>
+  </si>
+  <si>
+    <t>Load 2</t>
+  </si>
+  <si>
+    <t>Load 3</t>
+  </si>
+  <si>
+    <t>Load 4</t>
+  </si>
+  <si>
+    <t>Location 1</t>
+  </si>
+  <si>
+    <t>Location 2</t>
+  </si>
+  <si>
+    <t>Location 3</t>
+  </si>
+  <si>
+    <t>Location 4</t>
+  </si>
+  <si>
+    <t>Uniform Load</t>
+  </si>
+  <si>
+    <t>- Line: Line name to be subjected distributed line load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Load Case: Load case of subjected distributed line load (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Direction: Direction of all subjected line point load (Load 1 - Load 4) (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Direction: Direction of all subjected distributed line load (Uniform, Load 1 - Load 4) (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Material: Material 1 of fiber section (main material), if fiber section is concrete, set this column with material of concrete core (Choose from the list)</t>
   </si>
 </sst>
 </file>
@@ -20097,7 +20124,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="192" t="s">
-        <v>336</v>
+        <v>374</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
@@ -20471,10 +20498,6 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="184"/>
-      <c r="G22" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G23" s="38" t="str">
@@ -26479,7 +26502,7 @@
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="D21:F1048576" xr:uid="{60D51DB4-00C7-4BA3-BEC6-0396076C386E}">
       <formula1>NL_Mat_Name</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="H21:H1048576 L21:O1048576" xr:uid="{22D892CF-00E0-4386-A561-F8E7B2F43520}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="L21:O1048576 H21:H1048576" xr:uid="{22D892CF-00E0-4386-A561-F8E7B2F43520}">
       <formula1>0</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
@@ -32787,7 +32810,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="192" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B3" s="38"/>
       <c r="C3" s="55"/>
@@ -34768,7 +34791,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="188" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B3" s="89"/>
       <c r="C3" s="89"/>
@@ -34782,7 +34805,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="188" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B4" s="89"/>
       <c r="C4" s="89"/>
@@ -34824,7 +34847,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="188" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B7" s="89"/>
       <c r="C7" s="89"/>
@@ -34949,7 +34972,7 @@
         <v>206</v>
       </c>
       <c r="F15" s="82" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G15" s="100" t="s">
         <v>204</v>
@@ -45739,7 +45762,7 @@
         <v>8</v>
       </c>
       <c r="C1" s="198" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D1" s="198" t="s">
         <v>10</v>
@@ -46112,7 +46135,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8BF8F5-8B72-4F82-8AD5-2105268CD711}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="222" customWidth="1"/>
@@ -46134,7 +46157,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="216" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B2" s="217"/>
       <c r="C2" s="217"/>
@@ -46146,7 +46169,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="216" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B3" s="217"/>
       <c r="C3" s="217"/>
@@ -46249,25 +46272,30 @@
         <v>298</v>
       </c>
       <c r="B11" s="212" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C11" s="212" t="s">
+        <v>342</v>
+      </c>
+      <c r="D11" s="212" t="s">
         <v>343</v>
       </c>
-      <c r="D11" s="212" t="s">
+      <c r="E11" s="212" t="s">
         <v>344</v>
       </c>
-      <c r="E11" s="212" t="s">
+      <c r="F11" s="212" t="s">
         <v>345</v>
       </c>
-      <c r="F11" s="212" t="s">
+      <c r="G11" s="212" t="s">
         <v>346</v>
       </c>
-      <c r="G11" s="212" t="s">
+      <c r="H11" s="212" t="s">
         <v>347</v>
       </c>
-      <c r="H11" s="212" t="s">
-        <v>348</v>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="222">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -46289,108 +46317,268 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105CF277-1F6A-492D-8E1A-EC3101EF3425}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="223" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="223" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="211"/>
+    <col min="4" max="11" width="10.7109375" style="223" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="211"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="213" t="s">
         <v>181</v>
       </c>
       <c r="B1" s="214"/>
       <c r="C1" s="214"/>
       <c r="D1" s="214"/>
-      <c r="E1" s="215"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="215"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="216" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B2" s="217"/>
       <c r="C2" s="217"/>
       <c r="D2" s="217"/>
-      <c r="E2" s="218"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="217"/>
+      <c r="J2" s="217"/>
+      <c r="K2" s="218"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="216" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B3" s="217"/>
       <c r="C3" s="217"/>
       <c r="D3" s="217"/>
-      <c r="E3" s="218"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="217"/>
+      <c r="F3" s="217"/>
+      <c r="G3" s="217"/>
+      <c r="H3" s="217"/>
+      <c r="I3" s="217"/>
+      <c r="J3" s="217"/>
+      <c r="K3" s="218"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="216" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="B4" s="217"/>
       <c r="C4" s="217"/>
       <c r="D4" s="217"/>
-      <c r="E4" s="218"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="217"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="217"/>
+      <c r="I4" s="217"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="216" t="str">
-        <f>"- Load: Value of subjected line point load (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
-        <v>- Load: Value of subjected line point load (Input as Float) (kN)</v>
+        <f>"- Load 1: Value of subjected line point load 1 (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
+        <v>- Load 1: Value of subjected line point load 1 (Input as Float) (kN)</v>
       </c>
       <c r="B5" s="217"/>
       <c r="C5" s="217"/>
       <c r="D5" s="217"/>
-      <c r="E5" s="218"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="219" t="str">
-        <f>"- Location: Location of subjected line point load (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
-        <v>- Location: Location of subjected line point load (Input as Float) (m)</v>
-      </c>
-      <c r="B6" s="220"/>
-      <c r="C6" s="220"/>
-      <c r="D6" s="220"/>
-      <c r="E6" s="221"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="211"/>
-      <c r="B7" s="211"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-    </row>
-    <row r="8" spans="1:5" s="196" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="212" t="s">
-        <v>350</v>
-      </c>
-      <c r="B8" s="212" t="s">
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="218"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="216" t="str">
+        <f>"- Location 1: Location of subjected line point load 1 (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location 1: Location of subjected line point load 1 (Input as Float) (m)</v>
+      </c>
+      <c r="B6" s="217"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="217"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="217"/>
+      <c r="K6" s="218"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="216" t="str">
+        <f>"- Load 2: Value of subjected line point load 2 (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
+        <v>- Load 2: Value of subjected line point load 2 (Input as Float) (kN)</v>
+      </c>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="217"/>
+      <c r="I7" s="217"/>
+      <c r="J7" s="217"/>
+      <c r="K7" s="218"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="216" t="str">
+        <f>"- Location 2: Location of subjected line point load 2 (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location 2: Location of subjected line point load 2 (Input as Float) (m)</v>
+      </c>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="217"/>
+      <c r="F8" s="217"/>
+      <c r="G8" s="217"/>
+      <c r="H8" s="217"/>
+      <c r="I8" s="217"/>
+      <c r="J8" s="217"/>
+      <c r="K8" s="218"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="216" t="str">
+        <f>"- Load 3: Value of subjected line point load 3 (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
+        <v>- Load 3: Value of subjected line point load 3 (Input as Float) (kN)</v>
+      </c>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
+      <c r="D9" s="217"/>
+      <c r="E9" s="217"/>
+      <c r="F9" s="217"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="217"/>
+      <c r="I9" s="217"/>
+      <c r="J9" s="217"/>
+      <c r="K9" s="218"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="216" t="str">
+        <f>"- Location 3: Location of subjected line point load 3 (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location 3: Location of subjected line point load 3 (Input as Float) (m)</v>
+      </c>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
+      <c r="D10" s="217"/>
+      <c r="E10" s="217"/>
+      <c r="F10" s="217"/>
+      <c r="G10" s="217"/>
+      <c r="H10" s="217"/>
+      <c r="I10" s="217"/>
+      <c r="J10" s="217"/>
+      <c r="K10" s="218"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="216" t="str">
+        <f>"- Load 4: Value of subjected line point load 4 (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
+        <v>- Load 4: Value of subjected line point load 4 (Input as Float) (kN)</v>
+      </c>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
+      <c r="D11" s="217"/>
+      <c r="E11" s="217"/>
+      <c r="F11" s="217"/>
+      <c r="G11" s="217"/>
+      <c r="H11" s="217"/>
+      <c r="I11" s="217"/>
+      <c r="J11" s="217"/>
+      <c r="K11" s="218"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="219" t="str">
+        <f>"- Location 4: Location of subjected line point load 4 (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location 4: Location of subjected line point load 4 (Input as Float) (m)</v>
+      </c>
+      <c r="B12" s="220"/>
+      <c r="C12" s="220"/>
+      <c r="D12" s="220"/>
+      <c r="E12" s="220"/>
+      <c r="F12" s="220"/>
+      <c r="G12" s="220"/>
+      <c r="H12" s="220"/>
+      <c r="I12" s="220"/>
+      <c r="J12" s="220"/>
+      <c r="K12" s="221"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="211"/>
+      <c r="B13" s="211"/>
+      <c r="C13" s="211"/>
+      <c r="D13" s="211"/>
+      <c r="E13" s="211"/>
+      <c r="F13" s="211"/>
+      <c r="G13" s="211"/>
+      <c r="H13" s="211"/>
+      <c r="I13" s="211"/>
+      <c r="J13" s="211"/>
+      <c r="K13" s="211"/>
+    </row>
+    <row r="14" spans="1:11" s="196" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="212" t="s">
         <v>349</v>
       </c>
-      <c r="C8" s="212" t="s">
-        <v>352</v>
-      </c>
-      <c r="D8" s="212" t="s">
+      <c r="B14" s="212" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="212" t="s">
+        <v>351</v>
+      </c>
+      <c r="D14" s="212" t="s">
+        <v>361</v>
+      </c>
+      <c r="E14" s="212" t="s">
+        <v>365</v>
+      </c>
+      <c r="F14" s="212" t="s">
+        <v>362</v>
+      </c>
+      <c r="G14" s="212" t="s">
+        <v>366</v>
+      </c>
+      <c r="H14" s="212" t="s">
         <v>363</v>
       </c>
-      <c r="E8" s="212" t="s">
-        <v>351</v>
+      <c r="I14" s="212" t="s">
+        <v>367</v>
+      </c>
+      <c r="J14" s="212" t="s">
+        <v>364</v>
+      </c>
+      <c r="K14" s="212" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="222">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B9:B1048576" xr:uid="{8399D4E5-15D3-44EB-BAF5-D4D9376E21A9}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B15:B1048576" xr:uid="{8399D4E5-15D3-44EB-BAF5-D4D9376E21A9}">
       <formula1>LC_Type</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A9:A1048576" xr:uid="{E806BA54-F03E-4170-B409-665005B7362E}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A15:A1048576" xr:uid="{E806BA54-F03E-4170-B409-665005B7362E}">
       <formula1>Line_ID</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="D9:E1048576" xr:uid="{6DEDB52A-6E32-4CDB-9BBB-C36A5BFBDF1F}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="D15:K1048576" xr:uid="{6DEDB52A-6E32-4CDB-9BBB-C36A5BFBDF1F}">
       <formula1>-1000000000000</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C9:C1048576" xr:uid="{C69DB190-B0B4-41DC-BB24-EADCC7640530}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C15:C1048576" xr:uid="{C69DB190-B0B4-41DC-BB24-EADCC7640530}">
       <formula1>"Global-X, Global-Y, Gravity, Local-x, Local-y, Local-z"</formula1>
     </dataValidation>
   </dataValidations>
@@ -46400,108 +46588,1193 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAB727D-5FF3-4C5E-99AD-1C31CEAF2053}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="196" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="196" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="211"/>
+    <col min="4" max="4" width="15.7109375" style="223" customWidth="1"/>
+    <col min="5" max="12" width="10.7109375" style="223" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="211"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="213" t="s">
         <v>181</v>
       </c>
       <c r="B1" s="214"/>
       <c r="C1" s="214"/>
       <c r="D1" s="214"/>
-      <c r="E1" s="215"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="215"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="216" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B2" s="217"/>
       <c r="C2" s="217"/>
       <c r="D2" s="217"/>
-      <c r="E2" s="218"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="217"/>
+      <c r="J2" s="217"/>
+      <c r="K2" s="217"/>
+      <c r="L2" s="218"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="216" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B3" s="217"/>
       <c r="C3" s="217"/>
       <c r="D3" s="217"/>
-      <c r="E3" s="218"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="217"/>
+      <c r="F3" s="217"/>
+      <c r="G3" s="217"/>
+      <c r="H3" s="217"/>
+      <c r="I3" s="217"/>
+      <c r="J3" s="217"/>
+      <c r="K3" s="217"/>
+      <c r="L3" s="218"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="216" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="B4" s="217"/>
       <c r="C4" s="217"/>
       <c r="D4" s="217"/>
-      <c r="E4" s="218"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="217"/>
+      <c r="F4" s="217"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="217"/>
+      <c r="I4" s="217"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="217"/>
+      <c r="L4" s="218"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="216" t="str">
-        <f>"- Load: Value of subjected line distributed load (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"/"&amp;'User Defined Units'!$B$11&amp;")"</f>
-        <v>- Load: Value of subjected line distributed load (Input as Float) (kN/m)</v>
+        <f>"- Uniform Load: Value of subjected uniform distributed line load (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"/"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Uniform Load: Value of subjected uniform distributed line load (Input as Float) (kN/m)</v>
       </c>
       <c r="B5" s="217"/>
       <c r="C5" s="217"/>
       <c r="D5" s="217"/>
-      <c r="E5" s="218"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="219" t="str">
-        <f>"- Location: Location of subjected line distributed load (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
-        <v>- Location: Location of subjected line distributed load (Input as Float) (m)</v>
-      </c>
-      <c r="B6" s="220"/>
-      <c r="C6" s="220"/>
-      <c r="D6" s="220"/>
-      <c r="E6" s="221"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="211"/>
-      <c r="B7" s="211"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-    </row>
-    <row r="8" spans="1:5" s="196" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="212" t="s">
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="218"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="216" t="str">
+        <f>"- Load 1: Value of subjected distributed line load 1 (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"/"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Load 1: Value of subjected distributed line load 1 (Input as Float) (kN/m)</v>
+      </c>
+      <c r="B6" s="217"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="217"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="217"/>
+      <c r="K6" s="217"/>
+      <c r="L6" s="218"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="216" t="str">
+        <f>"- Location 1: Location of subjected distributed line load 1 (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location 1: Location of subjected distributed line load 1 (Input as Float) (m)</v>
+      </c>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="217"/>
+      <c r="I7" s="217"/>
+      <c r="J7" s="217"/>
+      <c r="K7" s="217"/>
+      <c r="L7" s="218"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="216" t="str">
+        <f>"- Load 2: Value of subjected distributed line load 2 (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"/"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Load 2: Value of subjected distributed line load 2 (Input as Float) (kN/m)</v>
+      </c>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="217"/>
+      <c r="F8" s="217"/>
+      <c r="G8" s="217"/>
+      <c r="H8" s="217"/>
+      <c r="I8" s="217"/>
+      <c r="J8" s="217"/>
+      <c r="K8" s="217"/>
+      <c r="L8" s="218"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="216" t="str">
+        <f>"- Location 2: Location of subjected distributed line load 2 (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location 2: Location of subjected distributed line load 2 (Input as Float) (m)</v>
+      </c>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
+      <c r="D9" s="217"/>
+      <c r="E9" s="217"/>
+      <c r="F9" s="217"/>
+      <c r="G9" s="217"/>
+      <c r="H9" s="217"/>
+      <c r="I9" s="217"/>
+      <c r="J9" s="217"/>
+      <c r="K9" s="217"/>
+      <c r="L9" s="218"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="216" t="str">
+        <f>"- Load 3: Value of subjected distributed line load 3 (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"/"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Load 3: Value of subjected distributed line load 3 (Input as Float) (kN/m)</v>
+      </c>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
+      <c r="D10" s="217"/>
+      <c r="E10" s="217"/>
+      <c r="F10" s="217"/>
+      <c r="G10" s="217"/>
+      <c r="H10" s="217"/>
+      <c r="I10" s="217"/>
+      <c r="J10" s="217"/>
+      <c r="K10" s="217"/>
+      <c r="L10" s="218"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="216" t="str">
+        <f>"- Location 3: Location of subjected distributed line load 3 (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location 3: Location of subjected distributed line load 3 (Input as Float) (m)</v>
+      </c>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
+      <c r="D11" s="217"/>
+      <c r="E11" s="217"/>
+      <c r="F11" s="217"/>
+      <c r="G11" s="217"/>
+      <c r="H11" s="217"/>
+      <c r="I11" s="217"/>
+      <c r="J11" s="217"/>
+      <c r="K11" s="217"/>
+      <c r="L11" s="218"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="216" t="str">
+        <f>"- Load 4: Value of subjected distributed line load 4 (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"/"&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Load 4: Value of subjected distributed line load 4 (Input as Float) (kN/m)</v>
+      </c>
+      <c r="B12" s="217"/>
+      <c r="C12" s="217"/>
+      <c r="D12" s="217"/>
+      <c r="E12" s="217"/>
+      <c r="F12" s="217"/>
+      <c r="G12" s="217"/>
+      <c r="H12" s="217"/>
+      <c r="I12" s="217"/>
+      <c r="J12" s="217"/>
+      <c r="K12" s="217"/>
+      <c r="L12" s="218"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="219" t="str">
+        <f>"- Location 4: Location of subjected distributed line load 4 (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
+        <v>- Location 4: Location of subjected distributed line load 4 (Input as Float) (m)</v>
+      </c>
+      <c r="B13" s="220"/>
+      <c r="C13" s="220"/>
+      <c r="D13" s="220"/>
+      <c r="E13" s="220"/>
+      <c r="F13" s="220"/>
+      <c r="G13" s="220"/>
+      <c r="H13" s="220"/>
+      <c r="I13" s="220"/>
+      <c r="J13" s="220"/>
+      <c r="K13" s="220"/>
+      <c r="L13" s="221"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="211"/>
+      <c r="B14" s="211"/>
+      <c r="C14" s="211"/>
+      <c r="D14" s="211"/>
+      <c r="E14" s="211"/>
+      <c r="F14" s="211"/>
+      <c r="G14" s="211"/>
+      <c r="H14" s="211"/>
+      <c r="I14" s="211"/>
+      <c r="J14" s="211"/>
+      <c r="K14" s="211"/>
+      <c r="L14" s="211"/>
+    </row>
+    <row r="15" spans="1:12" s="196" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="212" t="s">
+        <v>349</v>
+      </c>
+      <c r="B15" s="212" t="s">
+        <v>348</v>
+      </c>
+      <c r="C15" s="212" t="s">
+        <v>351</v>
+      </c>
+      <c r="D15" s="212" t="s">
+        <v>369</v>
+      </c>
+      <c r="E15" s="212" t="s">
+        <v>361</v>
+      </c>
+      <c r="F15" s="212" t="s">
+        <v>365</v>
+      </c>
+      <c r="G15" s="212" t="s">
+        <v>362</v>
+      </c>
+      <c r="H15" s="212" t="s">
+        <v>366</v>
+      </c>
+      <c r="I15" s="212" t="s">
+        <v>363</v>
+      </c>
+      <c r="J15" s="212" t="s">
+        <v>367</v>
+      </c>
+      <c r="K15" s="212" t="s">
+        <v>364</v>
+      </c>
+      <c r="L15" s="212" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="222">
+        <v>101</v>
+      </c>
+      <c r="B16" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="222" t="s">
         <v>350</v>
       </c>
-      <c r="B8" s="212" t="s">
-        <v>349</v>
-      </c>
-      <c r="C8" s="212" t="s">
-        <v>352</v>
-      </c>
-      <c r="D8" s="212" t="s">
-        <v>363</v>
-      </c>
-      <c r="E8" s="212" t="s">
-        <v>351</v>
+      <c r="D16" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="222">
+        <v>102</v>
+      </c>
+      <c r="B17" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D17" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="222">
+        <v>103</v>
+      </c>
+      <c r="B18" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D18" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="222">
+        <v>104</v>
+      </c>
+      <c r="B19" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D19" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="222">
+        <v>117</v>
+      </c>
+      <c r="B20" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D20" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="222">
+        <v>118</v>
+      </c>
+      <c r="B21" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="222">
+        <v>119</v>
+      </c>
+      <c r="B22" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D22" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="222">
+        <v>120</v>
+      </c>
+      <c r="B23" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D23" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="222">
+        <v>181</v>
+      </c>
+      <c r="B24" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D24" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="222">
+        <v>185</v>
+      </c>
+      <c r="B25" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D25" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="222">
+        <v>186</v>
+      </c>
+      <c r="B26" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D26" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="222">
+        <v>190</v>
+      </c>
+      <c r="B27" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D27" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="222">
+        <v>191</v>
+      </c>
+      <c r="B28" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D28" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="222">
+        <v>195</v>
+      </c>
+      <c r="B29" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D29" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="222">
+        <v>196</v>
+      </c>
+      <c r="B30" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D30" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="222">
+        <v>200</v>
+      </c>
+      <c r="B31" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D31" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="222">
+        <v>121</v>
+      </c>
+      <c r="B32" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D32" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="222">
+        <v>122</v>
+      </c>
+      <c r="B33" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D33" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="222">
+        <v>123</v>
+      </c>
+      <c r="B34" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D34" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="222">
+        <v>124</v>
+      </c>
+      <c r="B35" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D35" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="222">
+        <v>137</v>
+      </c>
+      <c r="B36" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D36" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="222">
+        <v>138</v>
+      </c>
+      <c r="B37" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D37" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="222">
+        <v>139</v>
+      </c>
+      <c r="B38" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D38" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="222">
+        <v>140</v>
+      </c>
+      <c r="B39" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D39" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="222">
+        <v>201</v>
+      </c>
+      <c r="B40" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D40" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="222">
+        <v>205</v>
+      </c>
+      <c r="B41" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D41" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="222">
+        <v>206</v>
+      </c>
+      <c r="B42" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D42" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="222">
+        <v>210</v>
+      </c>
+      <c r="B43" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D43" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="222">
+        <v>211</v>
+      </c>
+      <c r="B44" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D44" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="222">
+        <v>215</v>
+      </c>
+      <c r="B45" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D45" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="222">
+        <v>216</v>
+      </c>
+      <c r="B46" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D46" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="222">
+        <v>220</v>
+      </c>
+      <c r="B47" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D47" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="222">
+        <v>141</v>
+      </c>
+      <c r="B48" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D48" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="222">
+        <v>142</v>
+      </c>
+      <c r="B49" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D49" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="222">
+        <v>143</v>
+      </c>
+      <c r="B50" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D50" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="222">
+        <v>144</v>
+      </c>
+      <c r="B51" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D51" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="222">
+        <v>157</v>
+      </c>
+      <c r="B52" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D52" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="222">
+        <v>158</v>
+      </c>
+      <c r="B53" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D53" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="222">
+        <v>159</v>
+      </c>
+      <c r="B54" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D54" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="222">
+        <v>160</v>
+      </c>
+      <c r="B55" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D55" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="222">
+        <v>221</v>
+      </c>
+      <c r="B56" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D56" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="222">
+        <v>225</v>
+      </c>
+      <c r="B57" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D57" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="222">
+        <v>226</v>
+      </c>
+      <c r="B58" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D58" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="222">
+        <v>230</v>
+      </c>
+      <c r="B59" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D59" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="222">
+        <v>231</v>
+      </c>
+      <c r="B60" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D60" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="222">
+        <v>235</v>
+      </c>
+      <c r="B61" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D61" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="222">
+        <v>236</v>
+      </c>
+      <c r="B62" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D62" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="222">
+        <v>240</v>
+      </c>
+      <c r="B63" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D63" s="223">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="222">
+        <v>161</v>
+      </c>
+      <c r="B64" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D64" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="222">
+        <v>162</v>
+      </c>
+      <c r="B65" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D65" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="222">
+        <v>163</v>
+      </c>
+      <c r="B66" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D66" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="222">
+        <v>164</v>
+      </c>
+      <c r="B67" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D67" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="222">
+        <v>177</v>
+      </c>
+      <c r="B68" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D68" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="222">
+        <v>178</v>
+      </c>
+      <c r="B69" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D69" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="222">
+        <v>179</v>
+      </c>
+      <c r="B70" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D70" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="222">
+        <v>180</v>
+      </c>
+      <c r="B71" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D71" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="222">
+        <v>241</v>
+      </c>
+      <c r="B72" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D72" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="222">
+        <v>245</v>
+      </c>
+      <c r="B73" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D73" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="222">
+        <v>246</v>
+      </c>
+      <c r="B74" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C74" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D74" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="222">
+        <v>250</v>
+      </c>
+      <c r="B75" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D75" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="222">
+        <v>251</v>
+      </c>
+      <c r="B76" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D76" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="222">
+        <v>255</v>
+      </c>
+      <c r="B77" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D77" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="222">
+        <v>256</v>
+      </c>
+      <c r="B78" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D78" s="223">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="222">
+        <v>260</v>
+      </c>
+      <c r="B79" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C79" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D79" s="223">
+        <v>2.41</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="4">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C9:C1048576" xr:uid="{A06960A0-574A-4091-89DC-3EAC93A1B00B}">
+  <dataValidations count="4">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C16:C1048576" xr:uid="{A06960A0-574A-4091-89DC-3EAC93A1B00B}">
       <formula1>"Global-X, Global-Y, Gravity, Local-x, Local-y, Local-z"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="D9:E1048576" xr:uid="{DF4D0C80-0563-4CC2-B0A8-6B52582B452C}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="D16:L1048576" xr:uid="{DF4D0C80-0563-4CC2-B0A8-6B52582B452C}">
       <formula1>-1000000000000</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A9:A1048576" xr:uid="{CFFEC136-BD4D-41A8-9172-2C735BE136D8}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A16:A1048576" xr:uid="{CFFEC136-BD4D-41A8-9172-2C735BE136D8}">
       <formula1>Line_ID</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B9:B1048576" xr:uid="{E3D690A9-3459-485B-9D38-6E5066FAA865}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B16:B1048576" xr:uid="{E3D690A9-3459-485B-9D38-6E5066FAA865}">
       <formula1>LC_Type</formula1>
     </dataValidation>
   </dataValidations>
@@ -46511,11 +47784,11 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10204173-8D21-44EB-9119-A6BC046B304C}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="196" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="223" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="211"/>
   </cols>
   <sheetData>
@@ -46530,7 +47803,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="216" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B2" s="217"/>
       <c r="C2" s="217"/>
@@ -46539,7 +47812,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="216" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B3" s="217"/>
       <c r="C3" s="217"/>
@@ -46548,7 +47821,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="216" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B4" s="217"/>
       <c r="C4" s="217"/>
@@ -46573,16 +47846,1808 @@
     </row>
     <row r="7" spans="1:5" s="196" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="212" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B7" s="212" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C7" s="212" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D7" s="212" t="s">
-        <v>363</v>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="222">
+        <v>1</v>
+      </c>
+      <c r="B8" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D8" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="222">
+        <v>2</v>
+      </c>
+      <c r="B9" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D9" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="222">
+        <v>3</v>
+      </c>
+      <c r="B10" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D10" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="222">
+        <v>4</v>
+      </c>
+      <c r="B11" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D11" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="222">
+        <v>5</v>
+      </c>
+      <c r="B12" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D12" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="222">
+        <v>6</v>
+      </c>
+      <c r="B13" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D13" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="222">
+        <v>7</v>
+      </c>
+      <c r="B14" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="222">
+        <v>8</v>
+      </c>
+      <c r="B15" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D15" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="222">
+        <v>9</v>
+      </c>
+      <c r="B16" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D16" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="222">
+        <v>10</v>
+      </c>
+      <c r="B17" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D17" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="222">
+        <v>11</v>
+      </c>
+      <c r="B18" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D18" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="222">
+        <v>12</v>
+      </c>
+      <c r="B19" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D19" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="222">
+        <v>13</v>
+      </c>
+      <c r="B20" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D20" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="222">
+        <v>14</v>
+      </c>
+      <c r="B21" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="222">
+        <v>15</v>
+      </c>
+      <c r="B22" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D22" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="222">
+        <v>16</v>
+      </c>
+      <c r="B23" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D23" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="222">
+        <v>17</v>
+      </c>
+      <c r="B24" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D24" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="222">
+        <v>18</v>
+      </c>
+      <c r="B25" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D25" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="222">
+        <v>19</v>
+      </c>
+      <c r="B26" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D26" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="222">
+        <v>20</v>
+      </c>
+      <c r="B27" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D27" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="222">
+        <v>21</v>
+      </c>
+      <c r="B28" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D28" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="222">
+        <v>22</v>
+      </c>
+      <c r="B29" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D29" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="222">
+        <v>23</v>
+      </c>
+      <c r="B30" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D30" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="222">
+        <v>24</v>
+      </c>
+      <c r="B31" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D31" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="222">
+        <v>25</v>
+      </c>
+      <c r="B32" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D32" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="222">
+        <v>26</v>
+      </c>
+      <c r="B33" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D33" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="222">
+        <v>27</v>
+      </c>
+      <c r="B34" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D34" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="222">
+        <v>28</v>
+      </c>
+      <c r="B35" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D35" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="222">
+        <v>29</v>
+      </c>
+      <c r="B36" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D36" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="222">
+        <v>30</v>
+      </c>
+      <c r="B37" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D37" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="222">
+        <v>31</v>
+      </c>
+      <c r="B38" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D38" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="222">
+        <v>32</v>
+      </c>
+      <c r="B39" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D39" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="222">
+        <v>33</v>
+      </c>
+      <c r="B40" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D40" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="222">
+        <v>34</v>
+      </c>
+      <c r="B41" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D41" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="222">
+        <v>35</v>
+      </c>
+      <c r="B42" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D42" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="222">
+        <v>36</v>
+      </c>
+      <c r="B43" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D43" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="222">
+        <v>37</v>
+      </c>
+      <c r="B44" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D44" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="222">
+        <v>38</v>
+      </c>
+      <c r="B45" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D45" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="222">
+        <v>39</v>
+      </c>
+      <c r="B46" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D46" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="222">
+        <v>40</v>
+      </c>
+      <c r="B47" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D47" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="222">
+        <v>41</v>
+      </c>
+      <c r="B48" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D48" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="222">
+        <v>42</v>
+      </c>
+      <c r="B49" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D49" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="222">
+        <v>43</v>
+      </c>
+      <c r="B50" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D50" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="222">
+        <v>44</v>
+      </c>
+      <c r="B51" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D51" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="222">
+        <v>45</v>
+      </c>
+      <c r="B52" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D52" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="222">
+        <v>46</v>
+      </c>
+      <c r="B53" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D53" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="222">
+        <v>47</v>
+      </c>
+      <c r="B54" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D54" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="222">
+        <v>48</v>
+      </c>
+      <c r="B55" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D55" s="223">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="222">
+        <v>49</v>
+      </c>
+      <c r="B56" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D56" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="222">
+        <v>50</v>
+      </c>
+      <c r="B57" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D57" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="222">
+        <v>51</v>
+      </c>
+      <c r="B58" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D58" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="222">
+        <v>52</v>
+      </c>
+      <c r="B59" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D59" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="222">
+        <v>53</v>
+      </c>
+      <c r="B60" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D60" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="222">
+        <v>54</v>
+      </c>
+      <c r="B61" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D61" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="222">
+        <v>55</v>
+      </c>
+      <c r="B62" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D62" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="222">
+        <v>56</v>
+      </c>
+      <c r="B63" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D63" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="222">
+        <v>57</v>
+      </c>
+      <c r="B64" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D64" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="222">
+        <v>58</v>
+      </c>
+      <c r="B65" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D65" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="222">
+        <v>59</v>
+      </c>
+      <c r="B66" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D66" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="222">
+        <v>60</v>
+      </c>
+      <c r="B67" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D67" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="222">
+        <v>61</v>
+      </c>
+      <c r="B68" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D68" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="222">
+        <v>62</v>
+      </c>
+      <c r="B69" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D69" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="222">
+        <v>63</v>
+      </c>
+      <c r="B70" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D70" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="222">
+        <v>64</v>
+      </c>
+      <c r="B71" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D71" s="223">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="222">
+        <v>1</v>
+      </c>
+      <c r="B72" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C72" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D72" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="222">
+        <v>2</v>
+      </c>
+      <c r="B73" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D73" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="222">
+        <v>3</v>
+      </c>
+      <c r="B74" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D74" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="222">
+        <v>4</v>
+      </c>
+      <c r="B75" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C75" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D75" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="222">
+        <v>5</v>
+      </c>
+      <c r="B76" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C76" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D76" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="222">
+        <v>6</v>
+      </c>
+      <c r="B77" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D77" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="222">
+        <v>7</v>
+      </c>
+      <c r="B78" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C78" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D78" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="222">
+        <v>8</v>
+      </c>
+      <c r="B79" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C79" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D79" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="222">
+        <v>9</v>
+      </c>
+      <c r="B80" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C80" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D80" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="222">
+        <v>10</v>
+      </c>
+      <c r="B81" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C81" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D81" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="222">
+        <v>11</v>
+      </c>
+      <c r="B82" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D82" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="222">
+        <v>12</v>
+      </c>
+      <c r="B83" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D83" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="222">
+        <v>13</v>
+      </c>
+      <c r="B84" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D84" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="222">
+        <v>14</v>
+      </c>
+      <c r="B85" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C85" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D85" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="222">
+        <v>15</v>
+      </c>
+      <c r="B86" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C86" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D86" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="222">
+        <v>16</v>
+      </c>
+      <c r="B87" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C87" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D87" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="222">
+        <v>17</v>
+      </c>
+      <c r="B88" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C88" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D88" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="222">
+        <v>18</v>
+      </c>
+      <c r="B89" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D89" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="222">
+        <v>19</v>
+      </c>
+      <c r="B90" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C90" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D90" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="222">
+        <v>20</v>
+      </c>
+      <c r="B91" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C91" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D91" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="222">
+        <v>21</v>
+      </c>
+      <c r="B92" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C92" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D92" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="222">
+        <v>22</v>
+      </c>
+      <c r="B93" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C93" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D93" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="222">
+        <v>23</v>
+      </c>
+      <c r="B94" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C94" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D94" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="222">
+        <v>24</v>
+      </c>
+      <c r="B95" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C95" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D95" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="222">
+        <v>25</v>
+      </c>
+      <c r="B96" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C96" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D96" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="222">
+        <v>26</v>
+      </c>
+      <c r="B97" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C97" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D97" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="222">
+        <v>27</v>
+      </c>
+      <c r="B98" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D98" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="222">
+        <v>28</v>
+      </c>
+      <c r="B99" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C99" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D99" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="222">
+        <v>29</v>
+      </c>
+      <c r="B100" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C100" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D100" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="222">
+        <v>30</v>
+      </c>
+      <c r="B101" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C101" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D101" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="222">
+        <v>31</v>
+      </c>
+      <c r="B102" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C102" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D102" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="222">
+        <v>32</v>
+      </c>
+      <c r="B103" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C103" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D103" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="222">
+        <v>33</v>
+      </c>
+      <c r="B104" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C104" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D104" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="222">
+        <v>34</v>
+      </c>
+      <c r="B105" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C105" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D105" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="222">
+        <v>35</v>
+      </c>
+      <c r="B106" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C106" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D106" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="222">
+        <v>36</v>
+      </c>
+      <c r="B107" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C107" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D107" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="222">
+        <v>37</v>
+      </c>
+      <c r="B108" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C108" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D108" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="222">
+        <v>38</v>
+      </c>
+      <c r="B109" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C109" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D109" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="222">
+        <v>39</v>
+      </c>
+      <c r="B110" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C110" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D110" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="222">
+        <v>40</v>
+      </c>
+      <c r="B111" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C111" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D111" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="222">
+        <v>41</v>
+      </c>
+      <c r="B112" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C112" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D112" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="222">
+        <v>42</v>
+      </c>
+      <c r="B113" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C113" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D113" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="222">
+        <v>43</v>
+      </c>
+      <c r="B114" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C114" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D114" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="222">
+        <v>44</v>
+      </c>
+      <c r="B115" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C115" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D115" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="222">
+        <v>45</v>
+      </c>
+      <c r="B116" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C116" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D116" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="222">
+        <v>46</v>
+      </c>
+      <c r="B117" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C117" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D117" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="222">
+        <v>47</v>
+      </c>
+      <c r="B118" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C118" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D118" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="222">
+        <v>48</v>
+      </c>
+      <c r="B119" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C119" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D119" s="223">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="222">
+        <v>49</v>
+      </c>
+      <c r="B120" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C120" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D120" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="222">
+        <v>50</v>
+      </c>
+      <c r="B121" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C121" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D121" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="222">
+        <v>51</v>
+      </c>
+      <c r="B122" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C122" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D122" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="222">
+        <v>52</v>
+      </c>
+      <c r="B123" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C123" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D123" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="222">
+        <v>53</v>
+      </c>
+      <c r="B124" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C124" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D124" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="222">
+        <v>54</v>
+      </c>
+      <c r="B125" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C125" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D125" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="222">
+        <v>55</v>
+      </c>
+      <c r="B126" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C126" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D126" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="222">
+        <v>56</v>
+      </c>
+      <c r="B127" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C127" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D127" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="222">
+        <v>57</v>
+      </c>
+      <c r="B128" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C128" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D128" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="222">
+        <v>58</v>
+      </c>
+      <c r="B129" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C129" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D129" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="222">
+        <v>59</v>
+      </c>
+      <c r="B130" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C130" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D130" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="222">
+        <v>60</v>
+      </c>
+      <c r="B131" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C131" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D131" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="222">
+        <v>61</v>
+      </c>
+      <c r="B132" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C132" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D132" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="222">
+        <v>62</v>
+      </c>
+      <c r="B133" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C133" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D133" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="222">
+        <v>63</v>
+      </c>
+      <c r="B134" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C134" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D134" s="223">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="222">
+        <v>64</v>
+      </c>
+      <c r="B135" s="222" t="s">
+        <v>74</v>
+      </c>
+      <c r="C135" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D135" s="223">
+        <v>0.57999999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3F47C7-71F3-4B79-BDD4-B8C61CAEF0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D34032-FF54-4C1E-8335-7F9D8E7B9C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="19" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -46135,7 +46135,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8BF8F5-8B72-4F82-8AD5-2105268CD711}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="222" customWidth="1"/>
@@ -46291,11 +46291,6 @@
       </c>
       <c r="H11" s="212" t="s">
         <v>347</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="222">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -46317,7 +46312,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105CF277-1F6A-492D-8E1A-EC3101EF3425}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
@@ -46559,11 +46554,6 @@
       </c>
       <c r="K14" s="212" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="222">
-        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D34032-FF54-4C1E-8335-7F9D8E7B9C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03612A6E-CD8B-4D48-980C-CC3E302BF2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="20" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="376">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1284,6 +1284,9 @@
   </si>
   <si>
     <t>- Material: Material 1 of fiber section (main material), if fiber section is concrete, set this column with material of concrete core (Choose from the list)</t>
+  </si>
+  <si>
+    <t>Global-Y</t>
   </si>
 </sst>
 </file>
@@ -46312,7 +46315,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105CF277-1F6A-492D-8E1A-EC3101EF3425}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
@@ -46554,6 +46557,86 @@
       </c>
       <c r="K14" s="212" t="s">
         <v>368</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="222">
+        <v>251</v>
+      </c>
+      <c r="B15" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D15" s="223">
+        <v>56</v>
+      </c>
+      <c r="E15" s="223">
+        <v>0</v>
+      </c>
+      <c r="F15" s="223">
+        <v>13</v>
+      </c>
+      <c r="G15" s="223">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="222">
+        <v>212</v>
+      </c>
+      <c r="B16" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D16" s="223">
+        <v>14</v>
+      </c>
+      <c r="E16" s="223">
+        <v>0</v>
+      </c>
+      <c r="F16" s="223">
+        <v>-12</v>
+      </c>
+      <c r="G16" s="223">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="222">
+        <v>212</v>
+      </c>
+      <c r="B17" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="222" t="s">
+        <v>375</v>
+      </c>
+      <c r="D17" s="223">
+        <v>-15</v>
+      </c>
+      <c r="E17" s="223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="222">
+        <v>212</v>
+      </c>
+      <c r="B18" s="222" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="222" t="s">
+        <v>350</v>
+      </c>
+      <c r="D18" s="223">
+        <v>20</v>
+      </c>
+      <c r="E18" s="223">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03612A6E-CD8B-4D48-980C-CC3E302BF2E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49983AFC-EA07-4912-892D-041C24192395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="20" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="11" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="375">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1284,9 +1284,6 @@
   </si>
   <si>
     <t>- Material: Material 1 of fiber section (main material), if fiber section is concrete, set this column with material of concrete core (Choose from the list)</t>
-  </si>
-  <si>
-    <t>Global-Y</t>
   </si>
 </sst>
 </file>
@@ -46315,7 +46312,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105CF277-1F6A-492D-8E1A-EC3101EF3425}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="222" customWidth="1"/>
@@ -46557,86 +46554,6 @@
       </c>
       <c r="K14" s="212" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="222">
-        <v>251</v>
-      </c>
-      <c r="B15" s="222" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="222" t="s">
-        <v>350</v>
-      </c>
-      <c r="D15" s="223">
-        <v>56</v>
-      </c>
-      <c r="E15" s="223">
-        <v>0</v>
-      </c>
-      <c r="F15" s="223">
-        <v>13</v>
-      </c>
-      <c r="G15" s="223">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="222">
-        <v>212</v>
-      </c>
-      <c r="B16" s="222" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="222" t="s">
-        <v>350</v>
-      </c>
-      <c r="D16" s="223">
-        <v>14</v>
-      </c>
-      <c r="E16" s="223">
-        <v>0</v>
-      </c>
-      <c r="F16" s="223">
-        <v>-12</v>
-      </c>
-      <c r="G16" s="223">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="222">
-        <v>212</v>
-      </c>
-      <c r="B17" s="222" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="222" t="s">
-        <v>375</v>
-      </c>
-      <c r="D17" s="223">
-        <v>-15</v>
-      </c>
-      <c r="E17" s="223">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="222">
-        <v>212</v>
-      </c>
-      <c r="B18" s="222" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="222" t="s">
-        <v>350</v>
-      </c>
-      <c r="D18" s="223">
-        <v>20</v>
-      </c>
-      <c r="E18" s="223">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -46951,6 +46868,30 @@
       </c>
       <c r="D16" s="223">
         <v>7.04</v>
+      </c>
+      <c r="E16" s="223">
+        <v>0</v>
+      </c>
+      <c r="F16" s="223">
+        <v>0</v>
+      </c>
+      <c r="G16" s="223">
+        <v>-12</v>
+      </c>
+      <c r="H16" s="223">
+        <v>3</v>
+      </c>
+      <c r="I16" s="223">
+        <v>-12</v>
+      </c>
+      <c r="J16" s="223">
+        <v>5</v>
+      </c>
+      <c r="K16" s="223">
+        <v>0</v>
+      </c>
+      <c r="L16" s="223">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D727544F-FB08-4490-82B0-1C3D2B6A06EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB66706-8941-4177-A3AF-1BFC440FD3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="10" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
@@ -8070,7 +8070,7 @@
         <v>32</v>
       </c>
       <c r="J116" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
@@ -8102,7 +8102,7 @@
         <v>32</v>
       </c>
       <c r="J117" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
@@ -8134,7 +8134,7 @@
         <v>32</v>
       </c>
       <c r="J118" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
@@ -8166,7 +8166,7 @@
         <v>32</v>
       </c>
       <c r="J119" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
@@ -8198,7 +8198,7 @@
         <v>32</v>
       </c>
       <c r="J120" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
@@ -8230,7 +8230,7 @@
         <v>32</v>
       </c>
       <c r="J121" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
@@ -8262,7 +8262,7 @@
         <v>32</v>
       </c>
       <c r="J122" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.25">
@@ -8294,7 +8294,7 @@
         <v>32</v>
       </c>
       <c r="J123" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
@@ -8326,7 +8326,7 @@
         <v>32</v>
       </c>
       <c r="J124" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
@@ -8358,7 +8358,7 @@
         <v>32</v>
       </c>
       <c r="J125" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
@@ -8390,7 +8390,7 @@
         <v>32</v>
       </c>
       <c r="J126" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
@@ -8422,7 +8422,7 @@
         <v>32</v>
       </c>
       <c r="J127" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
@@ -8454,7 +8454,7 @@
         <v>32</v>
       </c>
       <c r="J128" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -8486,7 +8486,7 @@
         <v>32</v>
       </c>
       <c r="J129" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -8518,7 +8518,7 @@
         <v>32</v>
       </c>
       <c r="J130" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -8550,7 +8550,7 @@
         <v>32</v>
       </c>
       <c r="J131" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -8582,7 +8582,7 @@
         <v>32</v>
       </c>
       <c r="J132" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -8614,7 +8614,7 @@
         <v>32</v>
       </c>
       <c r="J133" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -8646,7 +8646,7 @@
         <v>32</v>
       </c>
       <c r="J134" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -8678,7 +8678,7 @@
         <v>32</v>
       </c>
       <c r="J135" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -8710,7 +8710,7 @@
         <v>32</v>
       </c>
       <c r="J136" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -8742,7 +8742,7 @@
         <v>32</v>
       </c>
       <c r="J137" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -8774,7 +8774,7 @@
         <v>32</v>
       </c>
       <c r="J138" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -8806,7 +8806,7 @@
         <v>32</v>
       </c>
       <c r="J139" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -8838,7 +8838,7 @@
         <v>32</v>
       </c>
       <c r="J140" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -8870,7 +8870,7 @@
         <v>32</v>
       </c>
       <c r="J141" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -8902,7 +8902,7 @@
         <v>32</v>
       </c>
       <c r="J142" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -8934,7 +8934,7 @@
         <v>32</v>
       </c>
       <c r="J143" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -8966,7 +8966,7 @@
         <v>32</v>
       </c>
       <c r="J144" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -8998,7 +8998,7 @@
         <v>32</v>
       </c>
       <c r="J145" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -9030,7 +9030,7 @@
         <v>32</v>
       </c>
       <c r="J146" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -9062,7 +9062,7 @@
         <v>32</v>
       </c>
       <c r="J147" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -9094,7 +9094,7 @@
         <v>32</v>
       </c>
       <c r="J148" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
@@ -9126,7 +9126,7 @@
         <v>32</v>
       </c>
       <c r="J149" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -9158,7 +9158,7 @@
         <v>32</v>
       </c>
       <c r="J150" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -9190,7 +9190,7 @@
         <v>32</v>
       </c>
       <c r="J151" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -9222,7 +9222,7 @@
         <v>32</v>
       </c>
       <c r="J152" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
@@ -9254,7 +9254,7 @@
         <v>32</v>
       </c>
       <c r="J153" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -9286,7 +9286,7 @@
         <v>32</v>
       </c>
       <c r="J154" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
@@ -9318,7 +9318,7 @@
         <v>32</v>
       </c>
       <c r="J155" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
@@ -9350,7 +9350,7 @@
         <v>32</v>
       </c>
       <c r="J156" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -9382,7 +9382,7 @@
         <v>32</v>
       </c>
       <c r="J157" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -9414,7 +9414,7 @@
         <v>32</v>
       </c>
       <c r="J158" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -9446,7 +9446,7 @@
         <v>32</v>
       </c>
       <c r="J159" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -9478,7 +9478,7 @@
         <v>32</v>
       </c>
       <c r="J160" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -9510,7 +9510,7 @@
         <v>32</v>
       </c>
       <c r="J161" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -9542,7 +9542,7 @@
         <v>32</v>
       </c>
       <c r="J162" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -9574,7 +9574,7 @@
         <v>32</v>
       </c>
       <c r="J163" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -9606,7 +9606,7 @@
         <v>32</v>
       </c>
       <c r="J164" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -9638,7 +9638,7 @@
         <v>32</v>
       </c>
       <c r="J165" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -9670,7 +9670,7 @@
         <v>32</v>
       </c>
       <c r="J166" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -9702,7 +9702,7 @@
         <v>32</v>
       </c>
       <c r="J167" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -9734,7 +9734,7 @@
         <v>32</v>
       </c>
       <c r="J168" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -9766,7 +9766,7 @@
         <v>32</v>
       </c>
       <c r="J169" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -9798,7 +9798,7 @@
         <v>32</v>
       </c>
       <c r="J170" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -9830,7 +9830,7 @@
         <v>32</v>
       </c>
       <c r="J171" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>32</v>
       </c>
       <c r="J172" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -9894,7 +9894,7 @@
         <v>32</v>
       </c>
       <c r="J173" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -9926,7 +9926,7 @@
         <v>32</v>
       </c>
       <c r="J174" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -9958,7 +9958,7 @@
         <v>32</v>
       </c>
       <c r="J175" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -9990,7 +9990,7 @@
         <v>32</v>
       </c>
       <c r="J176" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -10022,7 +10022,7 @@
         <v>32</v>
       </c>
       <c r="J177" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -10054,7 +10054,7 @@
         <v>32</v>
       </c>
       <c r="J178" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -10086,7 +10086,7 @@
         <v>32</v>
       </c>
       <c r="J179" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -10118,7 +10118,7 @@
         <v>32</v>
       </c>
       <c r="J180" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -10150,7 +10150,7 @@
         <v>32</v>
       </c>
       <c r="J181" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -10182,7 +10182,7 @@
         <v>32</v>
       </c>
       <c r="J182" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -10214,7 +10214,7 @@
         <v>32</v>
       </c>
       <c r="J183" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -10246,7 +10246,7 @@
         <v>32</v>
       </c>
       <c r="J184" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -10278,7 +10278,7 @@
         <v>32</v>
       </c>
       <c r="J185" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -10310,7 +10310,7 @@
         <v>32</v>
       </c>
       <c r="J186" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -10342,7 +10342,7 @@
         <v>32</v>
       </c>
       <c r="J187" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -10374,7 +10374,7 @@
         <v>32</v>
       </c>
       <c r="J188" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
@@ -10406,7 +10406,7 @@
         <v>32</v>
       </c>
       <c r="J189" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
@@ -10438,7 +10438,7 @@
         <v>32</v>
       </c>
       <c r="J190" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -10470,7 +10470,7 @@
         <v>32</v>
       </c>
       <c r="J191" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -10502,7 +10502,7 @@
         <v>32</v>
       </c>
       <c r="J192" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -10534,7 +10534,7 @@
         <v>32</v>
       </c>
       <c r="J193" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -10566,7 +10566,7 @@
         <v>32</v>
       </c>
       <c r="J194" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -10598,7 +10598,7 @@
         <v>32</v>
       </c>
       <c r="J195" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -10630,7 +10630,7 @@
         <v>32</v>
       </c>
       <c r="J196" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -10662,7 +10662,7 @@
         <v>32</v>
       </c>
       <c r="J197" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -10694,7 +10694,7 @@
         <v>32</v>
       </c>
       <c r="J198" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -10726,7 +10726,7 @@
         <v>32</v>
       </c>
       <c r="J199" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -10758,7 +10758,7 @@
         <v>32</v>
       </c>
       <c r="J200" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -10790,7 +10790,7 @@
         <v>32</v>
       </c>
       <c r="J201" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
@@ -10822,7 +10822,7 @@
         <v>32</v>
       </c>
       <c r="J202" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -10854,7 +10854,7 @@
         <v>32</v>
       </c>
       <c r="J203" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -10886,7 +10886,7 @@
         <v>32</v>
       </c>
       <c r="J204" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -10918,7 +10918,7 @@
         <v>32</v>
       </c>
       <c r="J205" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -10950,7 +10950,7 @@
         <v>32</v>
       </c>
       <c r="J206" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -10982,7 +10982,7 @@
         <v>32</v>
       </c>
       <c r="J207" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -11014,7 +11014,7 @@
         <v>32</v>
       </c>
       <c r="J208" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -11046,7 +11046,7 @@
         <v>32</v>
       </c>
       <c r="J209" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -11078,7 +11078,7 @@
         <v>32</v>
       </c>
       <c r="J210" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -11110,7 +11110,7 @@
         <v>32</v>
       </c>
       <c r="J211" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -11142,7 +11142,7 @@
         <v>32</v>
       </c>
       <c r="J212" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
         <v>32</v>
       </c>
       <c r="J213" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -11206,7 +11206,7 @@
         <v>32</v>
       </c>
       <c r="J214" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -11238,7 +11238,7 @@
         <v>32</v>
       </c>
       <c r="J215" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -11270,7 +11270,7 @@
         <v>32</v>
       </c>
       <c r="J216" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -11302,7 +11302,7 @@
         <v>32</v>
       </c>
       <c r="J217" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -11334,7 +11334,7 @@
         <v>32</v>
       </c>
       <c r="J218" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -11366,7 +11366,7 @@
         <v>32</v>
       </c>
       <c r="J219" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
@@ -11398,7 +11398,7 @@
         <v>32</v>
       </c>
       <c r="J220" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
@@ -11430,7 +11430,7 @@
         <v>32</v>
       </c>
       <c r="J221" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
@@ -11462,7 +11462,7 @@
         <v>32</v>
       </c>
       <c r="J222" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
@@ -11494,7 +11494,7 @@
         <v>32</v>
       </c>
       <c r="J223" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
@@ -11526,7 +11526,7 @@
         <v>32</v>
       </c>
       <c r="J224" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
@@ -11558,7 +11558,7 @@
         <v>32</v>
       </c>
       <c r="J225" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.25">
@@ -11590,7 +11590,7 @@
         <v>32</v>
       </c>
       <c r="J226" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.25">
@@ -11622,7 +11622,7 @@
         <v>32</v>
       </c>
       <c r="J227" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.25">
@@ -11654,7 +11654,7 @@
         <v>32</v>
       </c>
       <c r="J228" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.25">
@@ -11686,7 +11686,7 @@
         <v>32</v>
       </c>
       <c r="J229" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.25">
@@ -11718,7 +11718,7 @@
         <v>32</v>
       </c>
       <c r="J230" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
@@ -11750,7 +11750,7 @@
         <v>32</v>
       </c>
       <c r="J231" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.25">
@@ -11782,7 +11782,7 @@
         <v>32</v>
       </c>
       <c r="J232" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.25">
@@ -11814,7 +11814,7 @@
         <v>32</v>
       </c>
       <c r="J233" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.25">
@@ -11846,7 +11846,7 @@
         <v>32</v>
       </c>
       <c r="J234" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.25">
@@ -11878,7 +11878,7 @@
         <v>32</v>
       </c>
       <c r="J235" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
@@ -11910,7 +11910,7 @@
         <v>32</v>
       </c>
       <c r="J236" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.25">
@@ -11942,7 +11942,7 @@
         <v>32</v>
       </c>
       <c r="J237" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
@@ -11974,7 +11974,7 @@
         <v>32</v>
       </c>
       <c r="J238" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.25">
@@ -12006,7 +12006,7 @@
         <v>32</v>
       </c>
       <c r="J239" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.25">
@@ -12038,7 +12038,7 @@
         <v>32</v>
       </c>
       <c r="J240" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -12070,7 +12070,7 @@
         <v>32</v>
       </c>
       <c r="J241" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -12102,7 +12102,7 @@
         <v>32</v>
       </c>
       <c r="J242" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -12134,7 +12134,7 @@
         <v>32</v>
       </c>
       <c r="J243" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
@@ -12166,7 +12166,7 @@
         <v>32</v>
       </c>
       <c r="J244" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
@@ -12198,7 +12198,7 @@
         <v>32</v>
       </c>
       <c r="J245" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
@@ -12230,7 +12230,7 @@
         <v>32</v>
       </c>
       <c r="J246" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
@@ -12262,7 +12262,7 @@
         <v>32</v>
       </c>
       <c r="J247" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
@@ -12294,7 +12294,7 @@
         <v>32</v>
       </c>
       <c r="J248" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
@@ -12326,7 +12326,7 @@
         <v>32</v>
       </c>
       <c r="J249" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
@@ -12358,7 +12358,7 @@
         <v>32</v>
       </c>
       <c r="J250" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.25">
@@ -12390,7 +12390,7 @@
         <v>32</v>
       </c>
       <c r="J251" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.25">
@@ -12422,7 +12422,7 @@
         <v>32</v>
       </c>
       <c r="J252" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
@@ -12454,7 +12454,7 @@
         <v>32</v>
       </c>
       <c r="J253" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.25">
@@ -12486,7 +12486,7 @@
         <v>32</v>
       </c>
       <c r="J254" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.25">
@@ -12518,7 +12518,7 @@
         <v>32</v>
       </c>
       <c r="J255" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.25">
@@ -12550,7 +12550,7 @@
         <v>32</v>
       </c>
       <c r="J256" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
@@ -12582,7 +12582,7 @@
         <v>32</v>
       </c>
       <c r="J257" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.25">
@@ -12614,7 +12614,7 @@
         <v>32</v>
       </c>
       <c r="J258" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.25">
@@ -12646,7 +12646,7 @@
         <v>32</v>
       </c>
       <c r="J259" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.25">
@@ -12678,7 +12678,7 @@
         <v>32</v>
       </c>
       <c r="J260" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.25">
@@ -12710,7 +12710,7 @@
         <v>32</v>
       </c>
       <c r="J261" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.25">
@@ -12742,7 +12742,7 @@
         <v>32</v>
       </c>
       <c r="J262" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.25">
@@ -12774,7 +12774,7 @@
         <v>32</v>
       </c>
       <c r="J263" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.25">
@@ -12806,7 +12806,7 @@
         <v>32</v>
       </c>
       <c r="J264" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
@@ -12838,7 +12838,7 @@
         <v>32</v>
       </c>
       <c r="J265" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.25">
@@ -12870,7 +12870,7 @@
         <v>32</v>
       </c>
       <c r="J266" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
@@ -12902,7 +12902,7 @@
         <v>32</v>
       </c>
       <c r="J267" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
@@ -12934,7 +12934,7 @@
         <v>32</v>
       </c>
       <c r="J268" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.25">
@@ -12966,7 +12966,7 @@
         <v>32</v>
       </c>
       <c r="J269" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.25">
@@ -12998,7 +12998,7 @@
         <v>32</v>
       </c>
       <c r="J270" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.25">
@@ -13030,7 +13030,7 @@
         <v>32</v>
       </c>
       <c r="J271" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
@@ -13062,7 +13062,7 @@
         <v>32</v>
       </c>
       <c r="J272" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
@@ -13094,7 +13094,7 @@
         <v>32</v>
       </c>
       <c r="J273" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
@@ -13126,7 +13126,7 @@
         <v>32</v>
       </c>
       <c r="J274" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.25">
@@ -13158,7 +13158,7 @@
         <v>32</v>
       </c>
       <c r="J275" s="50" t="s">
-        <v>70</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jwiciardo/Projects/SadProPy/src/sadpropy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A030AA32-3E9C-CB4F-ABA0-732F0E762981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DA8038D-4F92-7F4C-AD97-2F1926528B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" firstSheet="10" activeTab="16" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18860" firstSheet="1" activeTab="10" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -4554,7 +4554,7 @@
     <col min="5" max="5" width="25.6640625" style="49" customWidth="1"/>
     <col min="6" max="6" width="20.6640625" style="49" customWidth="1"/>
     <col min="7" max="8" width="20.6640625" style="88" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" style="49" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" style="49" customWidth="1"/>
     <col min="10" max="10" width="20.6640625" style="49" customWidth="1"/>
     <col min="11" max="16384" width="10.83203125" style="79"/>
   </cols>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jwiciardo/Projects/SadProPy/src/sadpropy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4361D749-A83C-2E40-9CDA-C2DE39B76BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D560CF-5221-F042-BD95-2988C4378C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" firstSheet="4" activeTab="14" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" firstSheet="5" activeTab="15" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -16000,7 +16000,7 @@
         <v>256</v>
       </c>
       <c r="B16" s="139" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C16" s="139" t="s">
         <v>237</v>
@@ -16342,6 +16342,24 @@
       </c>
       <c r="D16" s="140">
         <v>7.04</v>
+      </c>
+      <c r="E16" s="140">
+        <v>0</v>
+      </c>
+      <c r="F16" s="140">
+        <v>0</v>
+      </c>
+      <c r="G16" s="140">
+        <v>10</v>
+      </c>
+      <c r="H16" s="140">
+        <v>4</v>
+      </c>
+      <c r="I16" s="140">
+        <v>0</v>
+      </c>
+      <c r="J16" s="140">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jwiciardo/Projects/SadProPy/src/sadpropy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D560CF-5221-F042-BD95-2988C4378C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{650CACB7-09B6-604D-95AE-1DC312EC413F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" firstSheet="5" activeTab="15" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18860" firstSheet="5" activeTab="15" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="352">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -15716,7 +15716,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105CF277-1F6A-492D-8E1A-EC3101EF3425}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="15.6640625" style="139" customWidth="1"/>
@@ -15958,76 +15958,6 @@
       </c>
       <c r="K14" s="129" t="s">
         <v>255</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="139">
-        <v>177</v>
-      </c>
-      <c r="B15" s="139" t="s">
-        <v>346</v>
-      </c>
-      <c r="C15" s="139" t="s">
-        <v>237</v>
-      </c>
-      <c r="D15" s="140">
-        <v>10</v>
-      </c>
-      <c r="E15" s="140">
-        <v>2</v>
-      </c>
-      <c r="F15" s="140">
-        <v>20</v>
-      </c>
-      <c r="G15" s="140">
-        <v>4</v>
-      </c>
-      <c r="H15" s="140">
-        <v>30</v>
-      </c>
-      <c r="I15" s="140">
-        <v>6</v>
-      </c>
-      <c r="J15" s="140">
-        <v>40</v>
-      </c>
-      <c r="K15" s="140">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="139">
-        <v>256</v>
-      </c>
-      <c r="B16" s="139" t="s">
-        <v>347</v>
-      </c>
-      <c r="C16" s="139" t="s">
-        <v>237</v>
-      </c>
-      <c r="D16" s="140">
-        <v>-10</v>
-      </c>
-      <c r="E16" s="140">
-        <v>2</v>
-      </c>
-      <c r="F16" s="140">
-        <v>-20</v>
-      </c>
-      <c r="G16" s="140">
-        <v>4</v>
-      </c>
-      <c r="H16" s="140">
-        <v>-30</v>
-      </c>
-      <c r="I16" s="140">
-        <v>6</v>
-      </c>
-      <c r="J16" s="140">
-        <v>-40</v>
-      </c>
-      <c r="K16" s="140">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -16342,24 +16272,6 @@
       </c>
       <c r="D16" s="140">
         <v>7.04</v>
-      </c>
-      <c r="E16" s="140">
-        <v>0</v>
-      </c>
-      <c r="F16" s="140">
-        <v>0</v>
-      </c>
-      <c r="G16" s="140">
-        <v>10</v>
-      </c>
-      <c r="H16" s="140">
-        <v>4</v>
-      </c>
-      <c r="I16" s="140">
-        <v>0</v>
-      </c>
-      <c r="J16" s="140">
-        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01406B4A-F6A0-417F-ADDF-66428A029E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF64522F-7B59-4A1B-B471-91E4ABB2F1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="14" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="14" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="354">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1166,6 +1166,12 @@
   </si>
   <si>
     <t>Wind-Y</t>
+  </si>
+  <si>
+    <t>Global-X</t>
+  </si>
+  <si>
+    <t>Global-Y</t>
   </si>
 </sst>
 </file>
@@ -15539,7 +15545,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8BF8F5-8B72-4F82-8AD5-2105268CD711}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.7109375" style="139" customWidth="1"/>
@@ -15695,6 +15701,76 @@
       </c>
       <c r="H11" s="129" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="139">
+        <v>101</v>
+      </c>
+      <c r="B12" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="C12" s="140">
+        <v>-100</v>
+      </c>
+      <c r="D12" s="140">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="139">
+        <v>106</v>
+      </c>
+      <c r="B13" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="C13" s="140">
+        <v>100</v>
+      </c>
+      <c r="D13" s="140">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="139">
+        <v>111</v>
+      </c>
+      <c r="B14" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="C14" s="140">
+        <v>100</v>
+      </c>
+      <c r="D14" s="140">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="139">
+        <v>116</v>
+      </c>
+      <c r="B15" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="C15" s="140">
+        <v>100</v>
+      </c>
+      <c r="D15" s="140">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="139">
+        <v>121</v>
+      </c>
+      <c r="B16" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="C16" s="140">
+        <v>100</v>
+      </c>
+      <c r="D16" s="140">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -15716,7 +15792,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105CF277-1F6A-492D-8E1A-EC3101EF3425}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="139" customWidth="1"/>
@@ -15965,15 +16041,49 @@
         <v>161</v>
       </c>
       <c r="B15" s="139" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C15" s="139" t="s">
         <v>237</v>
       </c>
       <c r="D15" s="140">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E15" s="140">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="139">
+        <v>162</v>
+      </c>
+      <c r="B16" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="C16" s="139" t="s">
+        <v>352</v>
+      </c>
+      <c r="D16" s="140">
+        <v>150</v>
+      </c>
+      <c r="E16" s="140">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="139">
+        <v>163</v>
+      </c>
+      <c r="B17" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="C17" s="139" t="s">
+        <v>353</v>
+      </c>
+      <c r="D17" s="140">
+        <v>150</v>
+      </c>
+      <c r="E17" s="140">
         <v>4</v>
       </c>
     </row>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AB8437-295D-4700-AF96-F9C3CA859B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC124375-3A5A-4D1B-8DE3-1B08BC685562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2015" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="364">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1178,6 +1178,9 @@
     <t>C1FiberShear</t>
   </si>
   <si>
+    <t>ShearY</t>
+  </si>
+  <si>
     <t>ElasticShearY</t>
   </si>
   <si>
@@ -1185,6 +1188,21 @@
   </si>
   <si>
     <t>- Properties of Aggregator + Elastic: 1=EA, 2=EIz, 3=GAvy, 4=EIy, 5=GAvz, 6=GJxx</t>
+  </si>
+  <si>
+    <t>Axial</t>
+  </si>
+  <si>
+    <t>FlexuralZ</t>
+  </si>
+  <si>
+    <t>FlexuralY</t>
+  </si>
+  <si>
+    <t>ShearZ</t>
+  </si>
+  <si>
+    <t>Torsional</t>
   </si>
 </sst>
 </file>
@@ -2177,7 +2195,117 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -13175,12 +13303,12 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="G16:G1048576">
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="23" priority="2">
       <formula>OR(E16="Auto from Connectivity")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H1048576">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>OR(E16="Auto from Connectivity")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19353,14 +19481,14 @@
         <v>241</v>
       </c>
       <c r="F2" s="228" t="s">
-        <v>235</v>
+        <v>359</v>
       </c>
       <c r="G2" s="122" t="str" cm="1">
         <f t="array" ref="G2">_xlfn._xlws.FILTER(Materials!A33:A1032,(Materials!B33:B1032="Spring")*(Materials!A33:A1032&lt;&gt;""))</f>
         <v>Rotational Spring</v>
       </c>
       <c r="H2" s="122" t="str" cm="1">
-        <f t="array" ref="H2:H8">_xlfn._xlws.FILTER(Materials!A33:A1032,((Materials!C33:C1032="Elastic")+(Materials!C33:C1032="Concrete04")+(Materials!C33:C1032="Concrete04+MinMax")+(Materials!C33:C1032="Steel02")+(Materials!C33:C1032="Steel02+MinMax"))*(Materials!A33:A1032&lt;&gt;""))</f>
+        <f t="array" ref="H2:H6">_xlfn._xlws.FILTER(Materials!A33:A1032,((Materials!C33:C1032="Elastic")+(Materials!C33:C1032="Concrete04")+(Materials!C33:C1032="Concrete04+MinMax")+(Materials!C33:C1032="Steel02")+(Materials!C33:C1032="Steel02+MinMax"))*(Materials!A33:A1032&lt;&gt;""))</f>
         <v>RC30</v>
       </c>
       <c r="I2" s="122" t="str" cm="1">
@@ -19372,7 +19500,7 @@
         <v>Rebar420</v>
       </c>
       <c r="K2" s="122" t="str" cm="1">
-        <f t="array" ref="K2:K5">_xlfn._xlws.FILTER(Materials!A33:A1032,(Materials!C33:C1032="Elastic")*(Materials!A33:A1032&lt;&gt;""))</f>
+        <f t="array" ref="K2:K3">_xlfn._xlws.FILTER(Materials!A33:A1032,(Materials!C33:C1032="Elastic")*(Materials!A33:A1032&lt;&gt;""))</f>
         <v>RC30</v>
       </c>
       <c r="L2" s="122" t="str" cm="1">
@@ -19440,7 +19568,9 @@
       <c r="E3" s="140" t="s">
         <v>187</v>
       </c>
-      <c r="F3" s="140"/>
+      <c r="F3" s="228" t="s">
+        <v>360</v>
+      </c>
       <c r="G3" s="122"/>
       <c r="H3" s="122" t="str">
         <v>Rebar420</v>
@@ -19510,7 +19640,9 @@
       <c r="E4" s="140" t="s">
         <v>242</v>
       </c>
-      <c r="F4" s="140"/>
+      <c r="F4" s="228" t="s">
+        <v>355</v>
+      </c>
       <c r="G4" s="122"/>
       <c r="H4" s="122" t="str">
         <v>RC Unconfined</v>
@@ -19519,9 +19651,7 @@
         <v>RC Confined</v>
       </c>
       <c r="J4" s="122"/>
-      <c r="K4" s="122" t="str">
-        <v>ElasticShearY</v>
-      </c>
+      <c r="K4" s="122"/>
       <c r="L4" s="122" t="str">
         <v>Rebar420NL</v>
       </c>
@@ -19566,16 +19696,16 @@
       <c r="C5" s="140"/>
       <c r="D5" s="140"/>
       <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
+      <c r="F5" s="228" t="s">
+        <v>361</v>
+      </c>
       <c r="G5" s="122"/>
       <c r="H5" s="122" t="str">
         <v>RC Confined</v>
       </c>
       <c r="I5" s="122"/>
       <c r="J5" s="122"/>
-      <c r="K5" s="122" t="str">
-        <v>ElasticShearZ</v>
-      </c>
+      <c r="K5" s="122"/>
       <c r="L5" s="122"/>
       <c r="M5" s="101"/>
       <c r="N5" s="101"/>
@@ -19614,7 +19744,9 @@
       <c r="C6" s="101"/>
       <c r="D6" s="101"/>
       <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
+      <c r="F6" s="228" t="s">
+        <v>362</v>
+      </c>
       <c r="G6" s="122"/>
       <c r="H6" s="122" t="str">
         <v>Rebar420NL</v>
@@ -19656,11 +19788,11 @@
       <c r="C7" s="101"/>
       <c r="D7" s="101"/>
       <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
+      <c r="F7" s="228" t="s">
+        <v>363</v>
+      </c>
       <c r="G7" s="122"/>
-      <c r="H7" s="122" t="str">
-        <v>ElasticShearY</v>
-      </c>
+      <c r="H7" s="122"/>
       <c r="I7" s="122"/>
       <c r="J7" s="122"/>
       <c r="K7" s="122"/>
@@ -19694,9 +19826,7 @@
       <c r="E8" s="101"/>
       <c r="F8" s="101"/>
       <c r="G8" s="122"/>
-      <c r="H8" s="122" t="str">
-        <v>ElasticShearZ</v>
-      </c>
+      <c r="H8" s="122"/>
       <c r="I8" s="122"/>
       <c r="J8" s="122"/>
       <c r="K8" s="122"/>
@@ -21388,7 +21518,7 @@
       <c r="Y26" s="143"/>
       <c r="Z26" s="143"/>
       <c r="AA26" s="237" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AB26" s="241"/>
       <c r="AC26" s="241"/>
@@ -22339,13 +22469,13 @@
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A39" s="220" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B39" s="90" t="s">
         <v>313</v>
       </c>
       <c r="C39" s="90" t="s">
-        <v>235</v>
+        <v>355</v>
       </c>
       <c r="D39" s="168">
         <v>0</v>
@@ -22444,13 +22574,13 @@
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A40" s="220" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B40" s="90" t="s">
         <v>313</v>
       </c>
       <c r="C40" s="90" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="D40" s="168">
         <v>0</v>
@@ -22561,53 +22691,53 @@
     <mergeCell ref="AA11:AH11"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:F1048576">
-    <cfRule type="expression" dxfId="10" priority="6">
+    <cfRule type="expression" dxfId="21" priority="6">
       <formula>OR($B33="Spring")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>OR($B33="Aggregator")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:AH1048576">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="19" priority="9">
       <formula>AND($B33="Concrete",$C33="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33:AH1048576">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="18" priority="8">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:AH1048576">
-    <cfRule type="expression" dxfId="6" priority="20">
+    <cfRule type="expression" dxfId="17" priority="20">
       <formula>AND($B33="Concrete",$C33="Concrete04")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($B33="Aggregator",$C33="Elastic")</formula>
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>AND($B33="Aggregator",$C33="ElasticAggregator")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O33:AH1048576">
-    <cfRule type="expression" dxfId="5" priority="11">
+    <cfRule type="expression" dxfId="16" priority="11">
       <formula>AND($B33="Concrete",$C33="Concrete04+MinMax")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:AH1048576">
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="15" priority="7">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Steel02")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33:AH1048576">
-    <cfRule type="expression" dxfId="3" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Steel02+MinMax")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF33:AH1048576">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="13" priority="4">
       <formula>AND($B33="Spring",$C33="IMKPeakOriented")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG33:AH1048576">
-    <cfRule type="expression" dxfId="1" priority="5">
+    <cfRule type="expression" dxfId="12" priority="5">
       <formula>AND($B33="Spring",$C33="IMKBilinear")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23560,10 +23690,10 @@
         <v>313</v>
       </c>
       <c r="F23" s="192" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H23" s="192" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L23" s="192" t="s">
         <v>291</v>
@@ -29603,22 +29733,22 @@
     <mergeCell ref="A8:J8"/>
   </mergeCells>
   <conditionalFormatting sqref="E20:K1048576 U20:AB1048576">
-    <cfRule type="expression" dxfId="16" priority="6">
+    <cfRule type="expression" dxfId="27" priority="6">
       <formula>OR($C20="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J20:K1048576">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>OR($C20="Aggregator")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20:L1048576">
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="25" priority="3">
       <formula>OR($C20="Elastic",$C20="Fiber")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M20:AB1048576">
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="24" priority="2">
       <formula>OR($C20="Aggregator")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC124375-3A5A-4D1B-8DE3-1B08BC685562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D784348C-EA11-4018-B0D7-F29F232CCDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
@@ -33,12 +33,14 @@
   </sheets>
   <definedNames>
     <definedName name="Base_Sec">'Frame Sections'!$A$20:$A$1019</definedName>
+    <definedName name="Blank">ListDB!$FB$2:$FB$1001</definedName>
     <definedName name="Elastic_Mat_Name">ListDB!$K$2:$K$1001</definedName>
-    <definedName name="Ele_Type">ListDB!$O$2:$O$1001</definedName>
+    <definedName name="Ele_Type">ListDB!$P$2:$P$1001</definedName>
     <definedName name="Element_ID">'Element Objects'!$A$16:$A$1048576</definedName>
-    <definedName name="Int_Type_Con">ListDB!$N$2:$N$1001</definedName>
-    <definedName name="Int_Type_Dist">ListDB!$M$2:$M$1001</definedName>
-    <definedName name="LC_Type">ListDB!$T$2:$T$1001</definedName>
+    <definedName name="Int_Type">ListDB!$M$2:$M$1001</definedName>
+    <definedName name="Int_Type_Con">ListDB!$O$2:$O$1001</definedName>
+    <definedName name="Int_Type_Dist">ListDB!$N$2:$N$1001</definedName>
+    <definedName name="LC_Type">ListDB!$U$2:$U$1001</definedName>
     <definedName name="Mat_Concrete">ListDB!$I$2:$I$1001</definedName>
     <definedName name="Mat_Model_Agg">ListDB!$F$2:$F$1001</definedName>
     <definedName name="Mat_Model_Concrete">ListDB!$C$2:$C$1001</definedName>
@@ -49,21 +51,21 @@
     <definedName name="Mat_Type">ListDB!$B$2:$B$1001</definedName>
     <definedName name="NL_Mat_Name">ListDB!$L$2:$L$1001</definedName>
     <definedName name="Node_ID">'Node Objects'!$A$8:$A$1048576</definedName>
-    <definedName name="Sec_Model">ListDB!$Q$2:$Q$1001</definedName>
-    <definedName name="Sec_Name">ListDB!$S$2:$S$1001</definedName>
-    <definedName name="Sec_name_wo_agg">ListDB!$R$2:$R$1001</definedName>
-    <definedName name="Sec_Shape">ListDB!$P$2:$P$1001</definedName>
-    <definedName name="SecDB">'Frame Sections'!$A$20:$T$1019</definedName>
+    <definedName name="Sec_Model">ListDB!$R$2:$R$1001</definedName>
+    <definedName name="Sec_Name">ListDB!$T$2:$T$1001</definedName>
+    <definedName name="Sec_name_wo_agg">ListDB!$S$2:$S$1001</definedName>
+    <definedName name="Sec_Shape">ListDB!$Q$2:$Q$1001</definedName>
+    <definedName name="SecDB">'Frame Sections'!$A$20:$U$1019</definedName>
     <definedName name="SecFiberDB">#REF!</definedName>
     <definedName name="Shell_ID">'Shell Objects'!$A$11:$A$1048576</definedName>
     <definedName name="Slab_Sec">'Slab Sections'!$A$7:$A$1006</definedName>
     <definedName name="Spring_Mat_Name">ListDB!$G$2:$G$1048576</definedName>
-    <definedName name="Unit_Angle">ListDB!$Z$2:$Z$3</definedName>
-    <definedName name="Unit_Force">ListDB!$U$2:$U$8</definedName>
-    <definedName name="Unit_Length">ListDB!$V$2:$V$6</definedName>
-    <definedName name="Unit_Mass">ListDB!$W$2:$W$6</definedName>
-    <definedName name="Unit_Stress">ListDB!$X$2:$X$9</definedName>
-    <definedName name="Unit_Time">ListDB!$Y$2:$Y$3</definedName>
+    <definedName name="Unit_Angle">ListDB!$AA$2:$AA$3</definedName>
+    <definedName name="Unit_Force">ListDB!$V$2:$V$8</definedName>
+    <definedName name="Unit_Length">ListDB!$W$2:$W$6</definedName>
+    <definedName name="Unit_Mass">ListDB!$X$2:$X$6</definedName>
+    <definedName name="Unit_Stress">ListDB!$Y$2:$Y$9</definedName>
+    <definedName name="Unit_Time">ListDB!$Z$2:$Z$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -89,7 +91,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -111,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="364">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1463,7 +1465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2191,11 +2193,787 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="105">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -13303,12 +14081,12 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="G16:G1048576">
-    <cfRule type="expression" dxfId="23" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>OR(E16="Auto from Connectivity")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H1048576">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>OR(E16="Auto from Connectivity")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19371,20 +20149,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC83A73-50DB-4818-AD57-9D1D23C8BA8A}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="99" customWidth="1"/>
     <col min="2" max="6" width="20.7109375" style="49" customWidth="1"/>
     <col min="7" max="12" width="20.7109375" style="79" customWidth="1"/>
-    <col min="13" max="17" width="20.7109375" style="49" customWidth="1"/>
-    <col min="18" max="19" width="20.7109375" style="79" customWidth="1"/>
-    <col min="20" max="20" width="15.7109375" style="49" customWidth="1"/>
-    <col min="21" max="26" width="10.7109375" style="49" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="49"/>
+    <col min="13" max="13" width="20.7109375" style="244" customWidth="1"/>
+    <col min="14" max="18" width="20.7109375" style="49" customWidth="1"/>
+    <col min="19" max="20" width="20.7109375" style="79" customWidth="1"/>
+    <col min="21" max="21" width="15.7109375" style="49" customWidth="1"/>
+    <col min="22" max="27" width="10.7109375" style="49" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="99" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="99" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="123" t="s">
         <v>176</v>
       </c>
@@ -19422,49 +20201,52 @@
         <v>19</v>
       </c>
       <c r="M1" s="123" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="123" t="s">
+      <c r="O1" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="123" t="s">
+      <c r="P1" s="123" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="123" t="s">
+      <c r="Q1" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="123" t="s">
+      <c r="R1" s="123" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="123" t="s">
+      <c r="S1" s="123" t="s">
         <v>209</v>
       </c>
-      <c r="S1" s="123" t="s">
+      <c r="T1" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="123" t="s">
+      <c r="U1" s="123" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="123" t="s">
+      <c r="V1" s="123" t="s">
         <v>62</v>
       </c>
-      <c r="V1" s="123" t="s">
+      <c r="W1" s="123" t="s">
         <v>63</v>
       </c>
-      <c r="W1" s="123" t="s">
+      <c r="X1" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="X1" s="123" t="s">
+      <c r="Y1" s="123" t="s">
         <v>65</v>
       </c>
-      <c r="Y1" s="123" t="s">
+      <c r="Z1" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="Z1" s="123" t="s">
+      <c r="AA1" s="123" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="100" t="s">
         <v>178</v>
       </c>
@@ -19488,7 +20270,7 @@
         <v>Rotational Spring</v>
       </c>
       <c r="H2" s="122" t="str" cm="1">
-        <f t="array" ref="H2:H6">_xlfn._xlws.FILTER(Materials!A33:A1032,((Materials!C33:C1032="Elastic")+(Materials!C33:C1032="Concrete04")+(Materials!C33:C1032="Concrete04+MinMax")+(Materials!C33:C1032="Steel02")+(Materials!C33:C1032="Steel02+MinMax"))*(Materials!A33:A1032&lt;&gt;""))</f>
+        <f t="array" ref="H2:H8">_xlfn._xlws.FILTER(Materials!A33:A1032,((Materials!C33:C1032="Elastic")+(Materials!C33:C1032="Concrete04")+(Materials!C33:C1032="Concrete04+MinMax")+(Materials!C33:C1032="Steel02")+(Materials!C33:C1032="Steel02+MinMax")+(Materials!C33:C1032="Axial")+(Materials!C33:C1032="FlexuralZ")+(Materials!C33:C1032="ShearY")+(Materials!C33:C1032="FlexuralY")+(Materials!C33:C1032="ShearZ")+(Materials!C33:C1032="Torsional"))*(Materials!A33:A1032&lt;&gt;""))</f>
         <v>RC30</v>
       </c>
       <c r="I2" s="122" t="str" cm="1">
@@ -19507,52 +20289,58 @@
         <f t="array" ref="L2:L4">_xlfn._xlws.FILTER(Materials!A33:A1032,((Materials!C33:C1032="Concrete04")+(Materials!C33:C1032="Concrete04+MinMax")+(Materials!C33:C1032="Steel02")+(Materials!C33:C1032="Steel02+MinMax"))*(Materials!A33:A1032&lt;&gt;""))</f>
         <v>RC Unconfined</v>
       </c>
-      <c r="M2" s="101" t="s">
+      <c r="M2" s="243" t="str" cm="1">
+        <f t="array" ref="M2:M3">_xlfn.VSTACK(
+_xlfn._xlws.FILTER(N2:N1001,N2:N1001&lt;&gt;""),
+_xlfn._xlws.FILTER(O2:O1001,N2:N1001&lt;&gt;""))</f>
+        <v>Lobatto</v>
+      </c>
+      <c r="N2" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="165" t="s">
+      <c r="O2" s="165" t="s">
         <v>301</v>
       </c>
-      <c r="O2" s="121" t="s">
+      <c r="P2" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="101" t="s">
+      <c r="Q2" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" s="165" t="s">
+      <c r="R2" s="165" t="s">
         <v>235</v>
       </c>
-      <c r="R2" s="122" t="str" cm="1">
-        <f t="array" ref="R2:R4">_xlfn._xlws.FILTER('Frame Sections'!A20:A1019,(('Frame Sections'!C20:C1019="Elastic")+('Frame Sections'!C20:C1019="Fiber"))*('Frame Sections'!A20:A1019&lt;&gt;""))</f>
+      <c r="S2" s="122" t="str" cm="1">
+        <f t="array" ref="S2:S4">_xlfn._xlws.FILTER('Frame Sections'!A20:A1019,(('Frame Sections'!C20:C1019="Elastic")+('Frame Sections'!C20:C1019="Fiber"))*('Frame Sections'!A20:A1019&lt;&gt;""))</f>
         <v>C1</v>
       </c>
-      <c r="S2" s="122" t="str" cm="1">
-        <f t="array" ref="S2:S5">_xlfn._xlws.FILTER('Frame Sections'!A20:A1019,(('Frame Sections'!C20:C1019="Elastic")+('Frame Sections'!C20:C1019="Fiber")+('Frame Sections'!C20:C1019="Aggregator"))*('Frame Sections'!A20:A1019&lt;&gt;""))</f>
+      <c r="T2" s="122" t="str" cm="1">
+        <f t="array" ref="T2:T5">_xlfn._xlws.FILTER('Frame Sections'!A20:A1019,(('Frame Sections'!C20:C1019="Elastic")+('Frame Sections'!C20:C1019="Fiber")+('Frame Sections'!C20:C1019="Aggregator"))*('Frame Sections'!A20:A1019&lt;&gt;""))</f>
         <v>C1</v>
       </c>
-      <c r="T2" s="213" t="s">
+      <c r="U2" s="213" t="s">
         <v>317</v>
       </c>
-      <c r="U2" s="102" t="s">
+      <c r="V2" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="V2" s="102" t="s">
+      <c r="W2" s="102" t="s">
         <v>75</v>
       </c>
-      <c r="W2" s="102" t="s">
+      <c r="X2" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="X2" s="102" t="s">
+      <c r="Y2" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="Y2" s="102" t="s">
+      <c r="Z2" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="Z2" s="102" t="s">
+      <c r="AA2" s="102" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="100" t="s">
         <v>179</v>
       </c>
@@ -19587,44 +20375,47 @@
       <c r="L3" s="122" t="str">
         <v>RC Confined</v>
       </c>
-      <c r="M3" s="101"/>
+      <c r="M3" s="243" t="str">
+        <v>Hinge Radau</v>
+      </c>
       <c r="N3" s="101"/>
-      <c r="O3" s="121" t="s">
+      <c r="O3" s="101"/>
+      <c r="P3" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="165" t="s">
+      <c r="Q3" s="101"/>
+      <c r="R3" s="165" t="s">
         <v>284</v>
-      </c>
-      <c r="R3" s="122" t="str">
-        <v>B1</v>
       </c>
       <c r="S3" s="122" t="str">
         <v>B1</v>
       </c>
-      <c r="T3" s="213" t="s">
+      <c r="T3" s="122" t="str">
+        <v>B1</v>
+      </c>
+      <c r="U3" s="213" t="s">
         <v>318</v>
       </c>
-      <c r="U3" s="102" t="s">
+      <c r="V3" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="V3" s="102" t="s">
+      <c r="W3" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="W3" s="102" t="s">
+      <c r="X3" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="X3" s="102" t="s">
+      <c r="Y3" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="Y3" s="102" t="s">
+      <c r="Z3" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="Z3" s="102" t="s">
+      <c r="AA3" s="102" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="100" t="s">
         <v>180</v>
       </c>
@@ -19655,40 +20446,41 @@
       <c r="L4" s="122" t="str">
         <v>Rebar420NL</v>
       </c>
-      <c r="M4" s="101"/>
+      <c r="M4" s="243"/>
       <c r="N4" s="101"/>
-      <c r="O4" s="121" t="s">
+      <c r="O4" s="101"/>
+      <c r="P4" s="121" t="s">
         <v>210</v>
       </c>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="213" t="s">
+      <c r="Q4" s="101"/>
+      <c r="R4" s="213" t="s">
         <v>313</v>
-      </c>
-      <c r="R4" s="122" t="str">
-        <v>C1Fiber</v>
       </c>
       <c r="S4" s="122" t="str">
         <v>C1Fiber</v>
       </c>
-      <c r="T4" s="213" t="s">
+      <c r="T4" s="122" t="str">
+        <v>C1Fiber</v>
+      </c>
+      <c r="U4" s="213" t="s">
         <v>319</v>
       </c>
-      <c r="U4" s="102" t="s">
+      <c r="V4" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="V4" s="102" t="s">
+      <c r="W4" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="W4" s="102" t="s">
+      <c r="X4" s="102" t="s">
         <v>82</v>
       </c>
-      <c r="X4" s="102" t="s">
+      <c r="Y4" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="Y4" s="101"/>
       <c r="Z4" s="101"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA4" s="101"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="140" t="s">
         <v>243</v>
@@ -19707,36 +20499,37 @@
       <c r="J5" s="122"/>
       <c r="K5" s="122"/>
       <c r="L5" s="122"/>
-      <c r="M5" s="101"/>
+      <c r="M5" s="243"/>
       <c r="N5" s="101"/>
-      <c r="O5" s="213" t="s">
+      <c r="O5" s="101"/>
+      <c r="P5" s="213" t="s">
         <v>315</v>
       </c>
-      <c r="P5" s="101"/>
       <c r="Q5" s="101"/>
-      <c r="R5" s="122"/>
-      <c r="S5" s="122" t="str">
+      <c r="R5" s="101"/>
+      <c r="S5" s="122"/>
+      <c r="T5" s="122" t="str">
         <v>C1FiberShear</v>
       </c>
-      <c r="T5" s="213" t="s">
+      <c r="U5" s="213" t="s">
         <v>46</v>
       </c>
-      <c r="U5" s="102" t="s">
+      <c r="V5" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="V5" s="102" t="s">
+      <c r="W5" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="W5" s="102" t="s">
+      <c r="X5" s="102" t="s">
         <v>83</v>
       </c>
-      <c r="X5" s="102" t="s">
+      <c r="Y5" s="102" t="s">
         <v>88</v>
       </c>
-      <c r="Y5" s="101"/>
       <c r="Z5" s="101"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA5" s="101"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="103"/>
       <c r="B6" s="228" t="s">
         <v>313</v>
@@ -19755,34 +20548,35 @@
       <c r="J6" s="122"/>
       <c r="K6" s="122"/>
       <c r="L6" s="122"/>
-      <c r="M6" s="101"/>
+      <c r="M6" s="243"/>
       <c r="N6" s="101"/>
-      <c r="O6" s="213" t="s">
+      <c r="O6" s="101"/>
+      <c r="P6" s="213" t="s">
         <v>316</v>
       </c>
-      <c r="P6" s="101"/>
       <c r="Q6" s="101"/>
-      <c r="R6" s="122"/>
+      <c r="R6" s="101"/>
       <c r="S6" s="122"/>
-      <c r="T6" s="213" t="s">
+      <c r="T6" s="122"/>
+      <c r="U6" s="213" t="s">
         <v>320</v>
       </c>
-      <c r="U6" s="102" t="s">
+      <c r="V6" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="V6" s="102" t="s">
+      <c r="W6" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="W6" s="102" t="s">
+      <c r="X6" s="102" t="s">
         <v>84</v>
       </c>
-      <c r="X6" s="102" t="s">
+      <c r="Y6" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="Y6" s="101"/>
       <c r="Z6" s="101"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA6" s="101"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="103"/>
       <c r="B7" s="101"/>
       <c r="C7" s="101"/>
@@ -19792,33 +20586,36 @@
         <v>363</v>
       </c>
       <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
+      <c r="H7" s="122" t="str">
+        <v>ElasticShearY</v>
+      </c>
       <c r="I7" s="122"/>
       <c r="J7" s="122"/>
       <c r="K7" s="122"/>
       <c r="L7" s="122"/>
-      <c r="M7" s="101"/>
+      <c r="M7" s="243"/>
       <c r="N7" s="101"/>
       <c r="O7" s="101"/>
       <c r="P7" s="101"/>
       <c r="Q7" s="101"/>
-      <c r="R7" s="122"/>
+      <c r="R7" s="101"/>
       <c r="S7" s="122"/>
-      <c r="T7" s="213" t="s">
+      <c r="T7" s="122"/>
+      <c r="U7" s="213" t="s">
         <v>321</v>
       </c>
-      <c r="U7" s="102" t="s">
+      <c r="V7" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="V7" s="101"/>
       <c r="W7" s="101"/>
-      <c r="X7" s="102" t="s">
+      <c r="X7" s="101"/>
+      <c r="Y7" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="Y7" s="101"/>
       <c r="Z7" s="101"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA7" s="101"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="103"/>
       <c r="B8" s="101"/>
       <c r="C8" s="101"/>
@@ -19826,33 +20623,36 @@
       <c r="E8" s="101"/>
       <c r="F8" s="101"/>
       <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
+      <c r="H8" s="122" t="str">
+        <v>ElasticShearZ</v>
+      </c>
       <c r="I8" s="122"/>
       <c r="J8" s="122"/>
       <c r="K8" s="122"/>
       <c r="L8" s="122"/>
-      <c r="M8" s="101"/>
+      <c r="M8" s="243"/>
       <c r="N8" s="101"/>
       <c r="O8" s="101"/>
       <c r="P8" s="101"/>
       <c r="Q8" s="101"/>
-      <c r="R8" s="122"/>
+      <c r="R8" s="101"/>
       <c r="S8" s="122"/>
-      <c r="T8" s="213" t="s">
+      <c r="T8" s="122"/>
+      <c r="U8" s="213" t="s">
         <v>322</v>
       </c>
-      <c r="U8" s="102" t="s">
+      <c r="V8" s="102" t="s">
         <v>74</v>
       </c>
-      <c r="V8" s="101"/>
       <c r="W8" s="101"/>
-      <c r="X8" s="102" t="s">
+      <c r="X8" s="101"/>
+      <c r="Y8" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="Y8" s="101"/>
       <c r="Z8" s="101"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA8" s="101"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="103"/>
       <c r="B9" s="101"/>
       <c r="C9" s="101"/>
@@ -19865,24 +20665,25 @@
       <c r="J9" s="122"/>
       <c r="K9" s="122"/>
       <c r="L9" s="122"/>
-      <c r="M9" s="101"/>
+      <c r="M9" s="243"/>
       <c r="N9" s="101"/>
       <c r="O9" s="101"/>
       <c r="P9" s="101"/>
       <c r="Q9" s="101"/>
-      <c r="R9" s="122"/>
+      <c r="R9" s="101"/>
       <c r="S9" s="122"/>
-      <c r="T9" s="213" t="s">
+      <c r="T9" s="122"/>
+      <c r="U9" s="213" t="s">
         <v>323</v>
       </c>
-      <c r="U9" s="101"/>
       <c r="V9" s="101"/>
       <c r="W9" s="101"/>
-      <c r="X9" s="102" t="s">
+      <c r="X9" s="101"/>
+      <c r="Y9" s="102" t="s">
         <v>92</v>
       </c>
-      <c r="Y9" s="101"/>
       <c r="Z9" s="101"/>
+      <c r="AA9" s="101"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22691,53 +23492,53 @@
     <mergeCell ref="AA11:AH11"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:F1048576">
-    <cfRule type="expression" dxfId="21" priority="6">
+    <cfRule type="expression" dxfId="17" priority="2">
+      <formula>OR($B33="Aggregator")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="6">
       <formula>OR($B33="Spring")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="2">
-      <formula>OR($B33="Aggregator")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:AH1048576">
-    <cfRule type="expression" dxfId="19" priority="9">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>AND($B33="Concrete",$C33="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33:AH1048576">
-    <cfRule type="expression" dxfId="18" priority="8">
+    <cfRule type="expression" dxfId="14" priority="8">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:AH1048576">
-    <cfRule type="expression" dxfId="17" priority="20">
+    <cfRule type="expression" dxfId="13" priority="1">
+      <formula>AND($B33="Aggregator",$C33="ElasticAggregator")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="20">
       <formula>AND($B33="Concrete",$C33="Concrete04")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="1">
-      <formula>AND($B33="Aggregator",$C33="ElasticAggregator")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O33:AH1048576">
-    <cfRule type="expression" dxfId="16" priority="11">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>AND($B33="Concrete",$C33="Concrete04+MinMax")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:AH1048576">
-    <cfRule type="expression" dxfId="15" priority="7">
+    <cfRule type="expression" dxfId="10" priority="7">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Steel02")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33:AH1048576">
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Steel02+MinMax")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF33:AH1048576">
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>AND($B33="Spring",$C33="IMKPeakOriented")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG33:AH1048576">
-    <cfRule type="expression" dxfId="12" priority="5">
+    <cfRule type="expression" dxfId="7" priority="5">
       <formula>AND($B33="Spring",$C33="IMKBilinear")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22754,7 +23555,7 @@
       <formula2>1000000000000</formula2>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C33:C1048576" xr:uid="{0CFE9A7D-744C-0049-9CE5-4AAAE6F48C9C}">
-      <formula1>IF($B33="Concrete",Mat_Model_Concrete,IF(OR($B33="Rebar",$B33="Steel"),Mat_Model_Steel,IF($B33="Spring",Mat_Model_Hysteretic,IF($B33="Aggregator",Mat_Model_Agg,""))))</formula1>
+      <formula1>IF($B33="Concrete",Mat_Model_Concrete,IF(OR($B33="Rebar",$B33="Steel"),Mat_Model_Steel,IF($B33="Spring",Mat_Model_Hysteretic,IF($B33="Aggregator",Mat_Model_Agg,Blank))))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22764,20 +23565,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A450D375-DBFA-4947-9799-8505849C9E0A}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:AB1019"/>
+  <dimension ref="A1:AC1019"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="10" width="20.7109375" style="192" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="229" customWidth="1"/>
-    <col min="12" max="12" width="20.7109375" style="192" customWidth="1"/>
-    <col min="13" max="18" width="10.7109375" style="193" customWidth="1"/>
-    <col min="19" max="20" width="15.7109375" style="193" customWidth="1"/>
-    <col min="21" max="25" width="15.7109375" style="194" customWidth="1"/>
-    <col min="26" max="28" width="15.7109375" style="195" customWidth="1"/>
-    <col min="29" max="16384" width="10.85546875" style="180"/>
+    <col min="11" max="12" width="20.7109375" style="229" customWidth="1"/>
+    <col min="13" max="13" width="20.7109375" style="192" customWidth="1"/>
+    <col min="14" max="19" width="10.7109375" style="193" customWidth="1"/>
+    <col min="20" max="21" width="15.7109375" style="193" customWidth="1"/>
+    <col min="22" max="26" width="15.7109375" style="194" customWidth="1"/>
+    <col min="27" max="29" width="15.7109375" style="195" customWidth="1"/>
+    <col min="30" max="16384" width="10.85546875" style="180"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="175" t="s">
         <v>101</v>
       </c>
@@ -22791,25 +23592,26 @@
       <c r="I1" s="176"/>
       <c r="J1" s="176"/>
       <c r="K1" s="176"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="178"/>
+      <c r="L1" s="176"/>
+      <c r="M1" s="177"/>
       <c r="N1" s="178"/>
       <c r="O1" s="178"/>
       <c r="P1" s="178"/>
       <c r="Q1" s="178"/>
-      <c r="R1" s="179"/>
-      <c r="S1" s="178"/>
+      <c r="R1" s="178"/>
+      <c r="S1" s="179"/>
       <c r="T1" s="178"/>
-      <c r="U1" s="197"/>
+      <c r="U1" s="178"/>
       <c r="V1" s="197"/>
       <c r="W1" s="197"/>
       <c r="X1" s="197"/>
       <c r="Y1" s="197"/>
       <c r="Z1" s="197"/>
       <c r="AA1" s="197"/>
-      <c r="AB1" s="198"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB1" s="197"/>
+      <c r="AC1" s="198"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="181" t="s">
         <v>170</v>
       </c>
@@ -22823,29 +23625,30 @@
       <c r="I2" s="122"/>
       <c r="J2" s="206"/>
       <c r="K2" s="206"/>
-      <c r="L2" s="183" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="183" t="s">
         <v>203</v>
       </c>
-      <c r="M2" s="209"/>
       <c r="N2" s="209"/>
       <c r="O2" s="209"/>
-      <c r="P2" s="210"/>
-      <c r="Q2" s="209"/>
-      <c r="R2" s="215"/>
-      <c r="S2" s="210" t="s">
+      <c r="P2" s="209"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="209"/>
+      <c r="S2" s="215"/>
+      <c r="T2" s="210" t="s">
         <v>303</v>
       </c>
-      <c r="T2" s="210"/>
-      <c r="U2" s="211"/>
+      <c r="U2" s="210"/>
       <c r="V2" s="211"/>
       <c r="W2" s="211"/>
       <c r="X2" s="211"/>
       <c r="Y2" s="211"/>
       <c r="Z2" s="211"/>
       <c r="AA2" s="211"/>
-      <c r="AB2" s="199"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="199"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="181" t="s">
         <v>171</v>
       </c>
@@ -22859,29 +23662,30 @@
       <c r="I3" s="122"/>
       <c r="J3" s="206"/>
       <c r="K3" s="206"/>
-      <c r="L3" s="183" t="s">
+      <c r="L3" s="206"/>
+      <c r="M3" s="183" t="s">
         <v>204</v>
       </c>
-      <c r="M3" s="209"/>
       <c r="N3" s="209"/>
       <c r="O3" s="209"/>
-      <c r="P3" s="210"/>
-      <c r="Q3" s="209"/>
-      <c r="R3" s="215"/>
-      <c r="S3" s="210" t="s">
+      <c r="P3" s="209"/>
+      <c r="Q3" s="210"/>
+      <c r="R3" s="209"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="210" t="s">
         <v>302</v>
       </c>
-      <c r="T3" s="210"/>
-      <c r="U3" s="211"/>
+      <c r="U3" s="210"/>
       <c r="V3" s="211"/>
       <c r="W3" s="211"/>
       <c r="X3" s="211"/>
       <c r="Y3" s="211"/>
       <c r="Z3" s="211"/>
       <c r="AA3" s="211"/>
-      <c r="AB3" s="199"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB3" s="211"/>
+      <c r="AC3" s="199"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="174" t="s">
         <v>285</v>
       </c>
@@ -22895,27 +23699,28 @@
       <c r="I4" s="122"/>
       <c r="J4" s="206"/>
       <c r="K4" s="206"/>
-      <c r="L4" s="183" t="s">
+      <c r="L4" s="206"/>
+      <c r="M4" s="183" t="s">
         <v>205</v>
       </c>
-      <c r="M4" s="209"/>
       <c r="N4" s="209"/>
       <c r="O4" s="209"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="209"/>
-      <c r="R4" s="182"/>
-      <c r="S4" s="209"/>
+      <c r="P4" s="209"/>
+      <c r="Q4" s="206"/>
+      <c r="R4" s="209"/>
+      <c r="S4" s="182"/>
       <c r="T4" s="209"/>
-      <c r="U4" s="211"/>
+      <c r="U4" s="209"/>
       <c r="V4" s="211"/>
       <c r="W4" s="211"/>
       <c r="X4" s="211"/>
       <c r="Y4" s="211"/>
       <c r="Z4" s="211"/>
       <c r="AA4" s="211"/>
-      <c r="AB4" s="199"/>
-    </row>
-    <row r="5" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB4" s="211"/>
+      <c r="AC4" s="199"/>
+    </row>
+    <row r="5" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="221" t="s">
         <v>307</v>
       </c>
@@ -22929,27 +23734,28 @@
       <c r="I5" s="222"/>
       <c r="J5" s="222"/>
       <c r="K5" s="219"/>
-      <c r="L5" s="183" t="s">
+      <c r="L5" s="219"/>
+      <c r="M5" s="183" t="s">
         <v>206</v>
       </c>
-      <c r="M5" s="203"/>
       <c r="N5" s="203"/>
       <c r="O5" s="203"/>
-      <c r="P5" s="206"/>
-      <c r="Q5" s="209"/>
-      <c r="R5" s="182"/>
-      <c r="S5" s="209"/>
+      <c r="P5" s="203"/>
+      <c r="Q5" s="206"/>
+      <c r="R5" s="209"/>
+      <c r="S5" s="182"/>
       <c r="T5" s="209"/>
-      <c r="U5" s="211"/>
+      <c r="U5" s="209"/>
       <c r="V5" s="211"/>
       <c r="W5" s="211"/>
       <c r="X5" s="211"/>
       <c r="Y5" s="211"/>
       <c r="Z5" s="211"/>
       <c r="AA5" s="211"/>
-      <c r="AB5" s="199"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB5" s="211"/>
+      <c r="AC5" s="199"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="221"/>
       <c r="B6" s="222"/>
       <c r="C6" s="222"/>
@@ -22961,27 +23767,28 @@
       <c r="I6" s="222"/>
       <c r="J6" s="222"/>
       <c r="K6" s="219"/>
-      <c r="L6" s="183" t="s">
+      <c r="L6" s="219"/>
+      <c r="M6" s="183" t="s">
         <v>207</v>
       </c>
-      <c r="M6" s="203"/>
       <c r="N6" s="203"/>
       <c r="O6" s="203"/>
-      <c r="P6" s="206"/>
-      <c r="Q6" s="209"/>
-      <c r="R6" s="182"/>
-      <c r="S6" s="209"/>
+      <c r="P6" s="203"/>
+      <c r="Q6" s="206"/>
+      <c r="R6" s="209"/>
+      <c r="S6" s="182"/>
       <c r="T6" s="209"/>
-      <c r="U6" s="211"/>
+      <c r="U6" s="209"/>
       <c r="V6" s="211"/>
       <c r="W6" s="211"/>
       <c r="X6" s="211"/>
       <c r="Y6" s="211"/>
       <c r="Z6" s="211"/>
       <c r="AA6" s="211"/>
-      <c r="AB6" s="199"/>
-    </row>
-    <row r="7" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB6" s="211"/>
+      <c r="AC6" s="199"/>
+    </row>
+    <row r="7" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="221" t="s">
         <v>309</v>
       </c>
@@ -22995,27 +23802,28 @@
       <c r="I7" s="222"/>
       <c r="J7" s="222"/>
       <c r="K7" s="219"/>
-      <c r="L7" s="183" t="s">
+      <c r="L7" s="219"/>
+      <c r="M7" s="183" t="s">
         <v>208</v>
       </c>
-      <c r="M7" s="203"/>
       <c r="N7" s="203"/>
       <c r="O7" s="203"/>
-      <c r="P7" s="206"/>
-      <c r="Q7" s="209"/>
-      <c r="R7" s="182"/>
-      <c r="S7" s="209"/>
+      <c r="P7" s="203"/>
+      <c r="Q7" s="206"/>
+      <c r="R7" s="209"/>
+      <c r="S7" s="182"/>
       <c r="T7" s="209"/>
-      <c r="U7" s="211"/>
+      <c r="U7" s="209"/>
       <c r="V7" s="211"/>
       <c r="W7" s="211"/>
       <c r="X7" s="211"/>
       <c r="Y7" s="211"/>
       <c r="Z7" s="211"/>
       <c r="AA7" s="211"/>
-      <c r="AB7" s="199"/>
-    </row>
-    <row r="8" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB7" s="211"/>
+      <c r="AC7" s="199"/>
+    </row>
+    <row r="8" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="221" t="s">
         <v>310</v>
       </c>
@@ -23029,28 +23837,29 @@
       <c r="I8" s="222"/>
       <c r="J8" s="222"/>
       <c r="K8" s="219"/>
-      <c r="L8" s="181" t="str">
+      <c r="L8" s="219"/>
+      <c r="M8" s="181" t="str">
         <f>"- h: Height of rectangular section (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- h: Height of rectangular section (Input as Float) (m)</v>
       </c>
-      <c r="M8" s="203"/>
       <c r="N8" s="203"/>
       <c r="O8" s="203"/>
-      <c r="P8" s="207"/>
-      <c r="Q8" s="209"/>
-      <c r="R8" s="182"/>
-      <c r="S8" s="209"/>
+      <c r="P8" s="203"/>
+      <c r="Q8" s="207"/>
+      <c r="R8" s="209"/>
+      <c r="S8" s="182"/>
       <c r="T8" s="209"/>
-      <c r="U8" s="211"/>
+      <c r="U8" s="209"/>
       <c r="V8" s="211"/>
       <c r="W8" s="211"/>
       <c r="X8" s="211"/>
       <c r="Y8" s="211"/>
       <c r="Z8" s="211"/>
       <c r="AA8" s="211"/>
-      <c r="AB8" s="199"/>
-    </row>
-    <row r="9" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB8" s="211"/>
+      <c r="AC8" s="199"/>
+    </row>
+    <row r="9" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="221" t="s">
         <v>308</v>
       </c>
@@ -23064,28 +23873,29 @@
       <c r="I9" s="222"/>
       <c r="J9" s="222"/>
       <c r="K9" s="219"/>
-      <c r="L9" s="181" t="str">
+      <c r="L9" s="219"/>
+      <c r="M9" s="181" t="str">
         <f>"- b: Width of rectangular section (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- b: Width of rectangular section (Input as Float) (m)</v>
       </c>
-      <c r="M9" s="203"/>
       <c r="N9" s="203"/>
       <c r="O9" s="203"/>
-      <c r="P9" s="207"/>
-      <c r="Q9" s="209"/>
-      <c r="R9" s="182"/>
-      <c r="S9" s="209"/>
+      <c r="P9" s="203"/>
+      <c r="Q9" s="207"/>
+      <c r="R9" s="209"/>
+      <c r="S9" s="182"/>
       <c r="T9" s="209"/>
-      <c r="U9" s="211"/>
+      <c r="U9" s="209"/>
       <c r="V9" s="211"/>
       <c r="W9" s="211"/>
       <c r="X9" s="211"/>
       <c r="Y9" s="211"/>
       <c r="Z9" s="211"/>
       <c r="AA9" s="211"/>
-      <c r="AB9" s="199"/>
-    </row>
-    <row r="10" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB9" s="211"/>
+      <c r="AC9" s="199"/>
+    </row>
+    <row r="10" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="221" t="s">
         <v>311</v>
       </c>
@@ -23099,28 +23909,29 @@
       <c r="I10" s="222"/>
       <c r="J10" s="222"/>
       <c r="K10" s="219"/>
-      <c r="L10" s="174" t="str">
+      <c r="L10" s="219"/>
+      <c r="M10" s="174" t="str">
         <f>"- c: Concrete cover (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- c: Concrete cover (Input as Float) (m)</v>
       </c>
-      <c r="M10" s="203"/>
       <c r="N10" s="203"/>
       <c r="O10" s="203"/>
-      <c r="P10" s="208"/>
-      <c r="Q10" s="209"/>
-      <c r="R10" s="182"/>
-      <c r="S10" s="209"/>
+      <c r="P10" s="203"/>
+      <c r="Q10" s="208"/>
+      <c r="R10" s="209"/>
+      <c r="S10" s="182"/>
       <c r="T10" s="209"/>
-      <c r="U10" s="211"/>
+      <c r="U10" s="209"/>
       <c r="V10" s="211"/>
       <c r="W10" s="211"/>
       <c r="X10" s="211"/>
       <c r="Y10" s="211"/>
       <c r="Z10" s="211"/>
       <c r="AA10" s="211"/>
-      <c r="AB10" s="199"/>
-    </row>
-    <row r="11" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB10" s="211"/>
+      <c r="AC10" s="199"/>
+    </row>
+    <row r="11" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="221" t="s">
         <v>312</v>
       </c>
@@ -23134,28 +23945,29 @@
       <c r="I11" s="222"/>
       <c r="J11" s="222"/>
       <c r="K11" s="219"/>
-      <c r="L11" s="181" t="str">
+      <c r="L11" s="219"/>
+      <c r="M11" s="181" t="str">
         <f>"- barDiaHoop: Diameter of hoops (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- barDiaHoop: Diameter of hoops (Input as Float) (m)</v>
       </c>
-      <c r="M11" s="203"/>
       <c r="N11" s="203"/>
       <c r="O11" s="203"/>
-      <c r="P11" s="207"/>
-      <c r="Q11" s="209"/>
-      <c r="R11" s="182"/>
-      <c r="S11" s="209"/>
+      <c r="P11" s="203"/>
+      <c r="Q11" s="207"/>
+      <c r="R11" s="209"/>
+      <c r="S11" s="182"/>
       <c r="T11" s="209"/>
-      <c r="U11" s="211"/>
+      <c r="U11" s="209"/>
       <c r="V11" s="211"/>
       <c r="W11" s="211"/>
       <c r="X11" s="211"/>
       <c r="Y11" s="211"/>
       <c r="Z11" s="211"/>
       <c r="AA11" s="211"/>
-      <c r="AB11" s="199"/>
-    </row>
-    <row r="12" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB11" s="211"/>
+      <c r="AC11" s="199"/>
+    </row>
+    <row r="12" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="226" t="s">
         <v>347</v>
       </c>
@@ -23169,28 +23981,29 @@
       <c r="I12" s="203"/>
       <c r="J12" s="207"/>
       <c r="K12" s="207"/>
-      <c r="L12" s="181" t="str">
+      <c r="L12" s="207"/>
+      <c r="M12" s="181" t="str">
         <f>"- barDiaTop: Diameter of top reinforcements (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- barDiaTop: Diameter of top reinforcements (Input as Float) (m)</v>
       </c>
-      <c r="M12" s="209"/>
       <c r="N12" s="209"/>
       <c r="O12" s="209"/>
-      <c r="P12" s="207"/>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="182"/>
-      <c r="S12" s="209"/>
+      <c r="P12" s="209"/>
+      <c r="Q12" s="207"/>
+      <c r="R12" s="209"/>
+      <c r="S12" s="182"/>
       <c r="T12" s="209"/>
-      <c r="U12" s="211"/>
+      <c r="U12" s="209"/>
       <c r="V12" s="211"/>
       <c r="W12" s="211"/>
       <c r="X12" s="211"/>
       <c r="Y12" s="211"/>
       <c r="Z12" s="211"/>
       <c r="AA12" s="211"/>
-      <c r="AB12" s="199"/>
-    </row>
-    <row r="13" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB12" s="211"/>
+      <c r="AC12" s="199"/>
+    </row>
+    <row r="13" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="226" t="s">
         <v>348</v>
       </c>
@@ -23204,28 +24017,29 @@
       <c r="I13" s="205"/>
       <c r="J13" s="207"/>
       <c r="K13" s="207"/>
-      <c r="L13" s="181" t="str">
+      <c r="L13" s="207"/>
+      <c r="M13" s="181" t="str">
         <f>"- barDiaBot: Diameter of bottom reinforcements (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- barDiaBot: Diameter of bottom reinforcements (Input as Float) (m)</v>
       </c>
-      <c r="M13" s="209"/>
       <c r="N13" s="209"/>
       <c r="O13" s="209"/>
-      <c r="P13" s="207"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="182"/>
-      <c r="S13" s="209"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="207"/>
+      <c r="R13" s="209"/>
+      <c r="S13" s="182"/>
       <c r="T13" s="209"/>
-      <c r="U13" s="211"/>
+      <c r="U13" s="209"/>
       <c r="V13" s="211"/>
       <c r="W13" s="211"/>
       <c r="X13" s="211"/>
       <c r="Y13" s="211"/>
       <c r="Z13" s="211"/>
       <c r="AA13" s="211"/>
-      <c r="AB13" s="199"/>
-    </row>
-    <row r="14" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB13" s="211"/>
+      <c r="AC13" s="199"/>
+    </row>
+    <row r="14" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="202" t="s">
         <v>314</v>
       </c>
@@ -23239,28 +24053,29 @@
       <c r="I14" s="205"/>
       <c r="J14" s="207"/>
       <c r="K14" s="207"/>
-      <c r="L14" s="181" t="str">
+      <c r="L14" s="207"/>
+      <c r="M14" s="181" t="str">
         <f>"- barDiaInt: Diameter of intermediate reinforcements (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- barDiaInt: Diameter of intermediate reinforcements (Input as Float) (m)</v>
       </c>
-      <c r="M14" s="209"/>
       <c r="N14" s="209"/>
       <c r="O14" s="209"/>
-      <c r="P14" s="207"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="182"/>
-      <c r="S14" s="209"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="207"/>
+      <c r="R14" s="209"/>
+      <c r="S14" s="182"/>
       <c r="T14" s="209"/>
-      <c r="U14" s="211"/>
+      <c r="U14" s="209"/>
       <c r="V14" s="211"/>
       <c r="W14" s="211"/>
       <c r="X14" s="211"/>
       <c r="Y14" s="211"/>
       <c r="Z14" s="211"/>
       <c r="AA14" s="211"/>
-      <c r="AB14" s="199"/>
-    </row>
-    <row r="15" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB14" s="211"/>
+      <c r="AC14" s="199"/>
+    </row>
+    <row r="15" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="204"/>
       <c r="B15" s="205"/>
       <c r="C15" s="205"/>
@@ -23272,27 +24087,28 @@
       <c r="I15" s="205"/>
       <c r="J15" s="207"/>
       <c r="K15" s="207"/>
-      <c r="L15" s="181" t="s">
+      <c r="L15" s="207"/>
+      <c r="M15" s="181" t="s">
         <v>173</v>
       </c>
-      <c r="M15" s="209"/>
       <c r="N15" s="209"/>
       <c r="O15" s="209"/>
-      <c r="P15" s="207"/>
-      <c r="Q15" s="209"/>
-      <c r="R15" s="182"/>
-      <c r="S15" s="209"/>
+      <c r="P15" s="209"/>
+      <c r="Q15" s="207"/>
+      <c r="R15" s="209"/>
+      <c r="S15" s="182"/>
       <c r="T15" s="209"/>
-      <c r="U15" s="211"/>
+      <c r="U15" s="209"/>
       <c r="V15" s="211"/>
       <c r="W15" s="211"/>
       <c r="X15" s="211"/>
       <c r="Y15" s="211"/>
       <c r="Z15" s="211"/>
       <c r="AA15" s="211"/>
-      <c r="AB15" s="199"/>
-    </row>
-    <row r="16" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB15" s="211"/>
+      <c r="AC15" s="199"/>
+    </row>
+    <row r="16" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="184" t="s">
         <v>119</v>
       </c>
@@ -23306,27 +24122,28 @@
       <c r="I16" s="205"/>
       <c r="J16" s="207"/>
       <c r="K16" s="207"/>
-      <c r="L16" s="181" t="s">
+      <c r="L16" s="207"/>
+      <c r="M16" s="181" t="s">
         <v>174</v>
       </c>
-      <c r="M16" s="209"/>
       <c r="N16" s="209"/>
       <c r="O16" s="209"/>
-      <c r="P16" s="207"/>
-      <c r="Q16" s="209"/>
-      <c r="R16" s="182"/>
-      <c r="S16" s="209"/>
+      <c r="P16" s="209"/>
+      <c r="Q16" s="207"/>
+      <c r="R16" s="209"/>
+      <c r="S16" s="182"/>
       <c r="T16" s="209"/>
-      <c r="U16" s="211"/>
+      <c r="U16" s="209"/>
       <c r="V16" s="211"/>
       <c r="W16" s="211"/>
       <c r="X16" s="211"/>
       <c r="Y16" s="211"/>
       <c r="Z16" s="211"/>
       <c r="AA16" s="211"/>
-      <c r="AB16" s="199"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB16" s="211"/>
+      <c r="AC16" s="199"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="185" t="s">
         <v>300</v>
       </c>
@@ -23340,27 +24157,28 @@
       <c r="I17" s="186"/>
       <c r="J17" s="212"/>
       <c r="K17" s="212"/>
-      <c r="L17" s="214" t="s">
+      <c r="L17" s="212"/>
+      <c r="M17" s="214" t="s">
         <v>175</v>
       </c>
-      <c r="M17" s="187"/>
       <c r="N17" s="187"/>
       <c r="O17" s="187"/>
-      <c r="P17" s="212"/>
-      <c r="Q17" s="187"/>
-      <c r="R17" s="188"/>
-      <c r="S17" s="187"/>
+      <c r="P17" s="187"/>
+      <c r="Q17" s="212"/>
+      <c r="R17" s="187"/>
+      <c r="S17" s="188"/>
       <c r="T17" s="187"/>
-      <c r="U17" s="200"/>
+      <c r="U17" s="187"/>
       <c r="V17" s="200"/>
       <c r="W17" s="200"/>
       <c r="X17" s="200"/>
       <c r="Y17" s="200"/>
       <c r="Z17" s="200"/>
       <c r="AA17" s="200"/>
-      <c r="AB17" s="201"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB17" s="200"/>
+      <c r="AC17" s="201"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="189"/>
       <c r="B18" s="101"/>
       <c r="C18" s="101"/>
@@ -23373,7 +24191,7 @@
       <c r="J18" s="101"/>
       <c r="K18" s="101"/>
       <c r="L18" s="101"/>
-      <c r="M18" s="190"/>
+      <c r="M18" s="101"/>
       <c r="N18" s="190"/>
       <c r="O18" s="190"/>
       <c r="P18" s="190"/>
@@ -23381,7 +24199,7 @@
       <c r="R18" s="190"/>
       <c r="S18" s="190"/>
       <c r="T18" s="190"/>
-      <c r="U18" s="180"/>
+      <c r="U18" s="190"/>
       <c r="V18" s="180"/>
       <c r="W18" s="180"/>
       <c r="X18" s="180"/>
@@ -23389,8 +24207,9 @@
       <c r="Z18" s="180"/>
       <c r="AA18" s="180"/>
       <c r="AB18" s="180"/>
-    </row>
-    <row r="19" spans="1:28" s="191" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AC18" s="180"/>
+    </row>
+    <row r="19" spans="1:29" s="191" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="126" t="s">
         <v>24</v>
       </c>
@@ -23424,59 +24243,60 @@
       <c r="K19" s="126" t="s">
         <v>346</v>
       </c>
-      <c r="L19" s="126" t="s">
+      <c r="L19" s="126"/>
+      <c r="M19" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="M19" s="126" t="s">
+      <c r="N19" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="N19" s="126" t="s">
+      <c r="O19" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="O19" s="126" t="s">
+      <c r="P19" s="126" t="s">
         <v>199</v>
       </c>
-      <c r="P19" s="126" t="s">
+      <c r="Q19" s="126" t="s">
         <v>200</v>
       </c>
-      <c r="Q19" s="126" t="s">
+      <c r="R19" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="R19" s="126" t="s">
+      <c r="S19" s="126" t="s">
         <v>202</v>
       </c>
-      <c r="S19" s="126" t="s">
+      <c r="T19" s="126" t="s">
         <v>287</v>
       </c>
-      <c r="T19" s="126" t="s">
+      <c r="U19" s="126" t="s">
         <v>288</v>
       </c>
-      <c r="U19" s="126" t="s">
+      <c r="V19" s="126" t="s">
         <v>292</v>
       </c>
-      <c r="V19" s="126" t="s">
+      <c r="W19" s="126" t="s">
         <v>293</v>
       </c>
-      <c r="W19" s="126" t="s">
+      <c r="X19" s="126" t="s">
         <v>294</v>
       </c>
-      <c r="X19" s="126" t="s">
+      <c r="Y19" s="126" t="s">
         <v>295</v>
       </c>
-      <c r="Y19" s="126" t="s">
+      <c r="Z19" s="126" t="s">
         <v>296</v>
       </c>
-      <c r="Z19" s="126" t="s">
+      <c r="AA19" s="126" t="s">
         <v>297</v>
       </c>
-      <c r="AA19" s="126" t="s">
+      <c r="AB19" s="126" t="s">
         <v>298</v>
       </c>
-      <c r="AB19" s="126" t="s">
+      <c r="AC19" s="126" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="192" t="s">
         <v>28</v>
       </c>
@@ -23489,9 +24309,6 @@
       <c r="D20" s="192" t="s">
         <v>13</v>
       </c>
-      <c r="M20" s="193">
-        <v>1</v>
-      </c>
       <c r="N20" s="193">
         <v>1</v>
       </c>
@@ -23499,22 +24316,22 @@
         <v>1</v>
       </c>
       <c r="P20" s="193">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="193">
         <v>0.7</v>
       </c>
       <c r="R20" s="193">
+        <v>0.7</v>
+      </c>
+      <c r="S20" s="193">
         <v>1</v>
-      </c>
-      <c r="S20" s="193">
-        <v>0.7</v>
       </c>
       <c r="T20" s="193">
         <v>0.7</v>
       </c>
-      <c r="U20" s="194">
-        <v>0</v>
+      <c r="U20" s="193">
+        <v>0.7</v>
       </c>
       <c r="V20" s="194">
         <v>0</v>
@@ -23528,7 +24345,7 @@
       <c r="Y20" s="194">
         <v>0</v>
       </c>
-      <c r="Z20" s="195">
+      <c r="Z20" s="194">
         <v>0</v>
       </c>
       <c r="AA20" s="195">
@@ -23537,8 +24354,11 @@
       <c r="AB20" s="195">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC20" s="195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="192" t="s">
         <v>29</v>
       </c>
@@ -23551,9 +24371,6 @@
       <c r="D21" s="192" t="s">
         <v>13</v>
       </c>
-      <c r="M21" s="193">
-        <v>1</v>
-      </c>
       <c r="N21" s="193">
         <v>1</v>
       </c>
@@ -23561,23 +24378,23 @@
         <v>1</v>
       </c>
       <c r="P21" s="193">
-        <v>0.35</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="193">
         <v>0.35</v>
       </c>
       <c r="R21" s="193">
+        <v>0.35</v>
+      </c>
+      <c r="S21" s="193">
         <v>1</v>
       </c>
-      <c r="S21" s="193">
+      <c r="T21" s="193">
         <v>0.6</v>
       </c>
-      <c r="T21" s="193">
+      <c r="U21" s="193">
         <v>0.3</v>
       </c>
-      <c r="U21" s="194">
-        <v>0</v>
-      </c>
       <c r="V21" s="194">
         <v>0</v>
       </c>
@@ -23590,7 +24407,7 @@
       <c r="Y21" s="194">
         <v>0</v>
       </c>
-      <c r="Z21" s="195">
+      <c r="Z21" s="194">
         <v>0</v>
       </c>
       <c r="AA21" s="195">
@@ -23599,8 +24416,11 @@
       <c r="AB21" s="195">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC21" s="195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="196" t="s">
         <v>291</v>
       </c>
@@ -23619,15 +24439,6 @@
       <c r="F22" s="192" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="192" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="229">
-        <v>5</v>
-      </c>
-      <c r="M22" s="193">
-        <v>1</v>
-      </c>
       <c r="N22" s="193">
         <v>1</v>
       </c>
@@ -23644,22 +24455,21 @@
         <v>1</v>
       </c>
       <c r="S22" s="193">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="T22" s="193">
         <v>0.7</v>
       </c>
-      <c r="U22" s="194">
+      <c r="U22" s="193">
+        <v>0.7</v>
+      </c>
+      <c r="V22" s="194">
         <f>40/1000</f>
         <v>0.04</v>
       </c>
-      <c r="V22" s="194">
+      <c r="W22" s="194">
         <f>13/1000</f>
         <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="W22" s="194">
-        <f>22/1000</f>
-        <v>2.1999999999999999E-2</v>
       </c>
       <c r="X22" s="194">
         <f>22/1000</f>
@@ -23669,17 +24479,21 @@
         <f>22/1000</f>
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="Z22" s="195">
-        <v>7</v>
+      <c r="Z22" s="194">
+        <f>22/1000</f>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="AA22" s="195">
         <v>7</v>
       </c>
       <c r="AB22" s="195">
+        <v>7</v>
+      </c>
+      <c r="AC22" s="195">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="230" t="s">
         <v>354</v>
       </c>
@@ -23695,12 +24509,15 @@
       <c r="H23" s="192" t="s">
         <v>357</v>
       </c>
-      <c r="L23" s="192" t="s">
+      <c r="J23" s="192" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" s="229">
+        <v>5</v>
+      </c>
+      <c r="M23" s="192" t="s">
         <v>291</v>
       </c>
-      <c r="M23" s="193">
-        <v>0</v>
-      </c>
       <c r="N23" s="193">
         <v>0</v>
       </c>
@@ -23722,7 +24539,7 @@
       <c r="T23" s="193">
         <v>0</v>
       </c>
-      <c r="U23" s="194">
+      <c r="U23" s="193">
         <v>0</v>
       </c>
       <c r="V23" s="194">
@@ -23737,7 +24554,7 @@
       <c r="Y23" s="194">
         <v>0</v>
       </c>
-      <c r="Z23" s="195">
+      <c r="Z23" s="194">
         <v>0</v>
       </c>
       <c r="AA23" s="195">
@@ -23746,56 +24563,59 @@
       <c r="AB23" s="195">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC23" s="195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C24" s="192" t="str">
         <f t="shared" ref="C24:C86" si="0">IF(A24=0,"","Elastic")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C25" s="192" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C26" s="192" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C27" s="192" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C28" s="192" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C29" s="192" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C30" s="192" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C31" s="192" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C32" s="192" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -29732,27 +30552,32 @@
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A8:J8"/>
   </mergeCells>
-  <conditionalFormatting sqref="E20:K1048576 U20:AB1048576">
-    <cfRule type="expression" dxfId="27" priority="6">
+  <conditionalFormatting sqref="E20:I1048576 V20:AC1048576">
+    <cfRule type="expression" dxfId="6" priority="11">
       <formula>OR($C20="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J20:K1048576">
-    <cfRule type="expression" dxfId="26" priority="1">
+  <conditionalFormatting sqref="M20:M1048576">
+    <cfRule type="expression" dxfId="5" priority="8">
+      <formula>OR($C20="Elastic",$C20="Fiber")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N20:AC1048576">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>OR($C20="Aggregator")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20:L1048576">
-    <cfRule type="expression" dxfId="25" priority="3">
-      <formula>OR($C20="Elastic",$C20="Fiber")</formula>
+  <conditionalFormatting sqref="K20:L1048576">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>OR(AND($A20&lt;&gt;"",$J20=""),$J20="Hinge Radau")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M20:AB1048576">
-    <cfRule type="expression" dxfId="24" priority="2">
-      <formula>OR($C20="Aggregator")</formula>
+  <conditionalFormatting sqref="J20:J1048576">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>OR($C20="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter maximum 32 characters only." sqref="A20:A1048576" xr:uid="{A6951AF9-403B-4235-97E8-ED51DE5D0D5B}">
       <formula1>1</formula1>
       <formula2>32</formula2>
@@ -29763,26 +30588,29 @@
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="C20:C1048576" xr:uid="{D70A793A-6AD6-4B04-AE0C-A13C3FB3C5EA}">
       <formula1>Sec_Model</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="M20:Y1048576" xr:uid="{86CFDFF3-56AA-47EF-8107-3860F2D02E07}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="N20:Z1048576" xr:uid="{86CFDFF3-56AA-47EF-8107-3860F2D02E07}">
       <formula1>0</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="J20:J1048576" xr:uid="{A6F874AE-4C0F-402F-B580-DEC24F8CCDCA}">
-      <formula1>Int_Type_Dist</formula1>
+      <formula1>IF($C20="Aggregator",Int_Type_Dist,IF($C20="Fiber",Int_Type,Blank))</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter an integer value only." sqref="Z20:AB1048576" xr:uid="{9E7E1E85-07CA-4166-9E90-B8217F2A4E1E}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter an integer value only." sqref="AA20:AC1048576" xr:uid="{9E7E1E85-07CA-4166-9E90-B8217F2A4E1E}">
       <formula1>0</formula1>
       <formula2>1000000000000</formula2>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="D20:I1048576" xr:uid="{A8355B54-42F1-4EFA-9077-D2579C7DD321}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="D20:D1048576" xr:uid="{A8355B54-42F1-4EFA-9077-D2579C7DD321}">
       <formula1>IF($C20="Elastic",Elastic_Mat_Name,IF(OR($C20="Fiber",$C20="Aggregator"),Mat_Name,""))</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="L20:L1048576" xr:uid="{3F4AD803-8899-594D-BE04-1E356DCDC571}">
-      <formula1>Sec_name_wo_agg</formula1>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="M20:M1048576" xr:uid="{3F4AD803-8899-594D-BE04-1E356DCDC571}">
+      <formula1>IF($C20="Aggregator",Sec_name_wo_agg,Blank)</formula1>
     </dataValidation>
-    <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter an integer value only." sqref="K20:K1048576" xr:uid="{4D077BD2-8C90-4BB5-9BC4-DB59553BB1F7}">
+    <dataValidation type="whole" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter an integer value only." sqref="K20:L1048576" xr:uid="{4D077BD2-8C90-4BB5-9BC4-DB59553BB1F7}">
       <formula1>0</formula1>
       <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="E20:I1048576" xr:uid="{9540A3D0-5003-4BA5-BF00-28B466291CC4}">
+      <formula1>IF(OR($C20="Fiber",$C20="Aggregator"),Mat_Name,Blank)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BACA04F-352C-4FD2-9C25-787800F02463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086A3448-84C9-48FD-BFB4-4C8E99590FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="13" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -22835,10 +22835,10 @@
         <v>1</v>
       </c>
       <c r="U20" s="192">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="V20" s="192">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="W20" s="193">
         <v>0</v>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086A3448-84C9-48FD-BFB4-4C8E99590FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1B1D65-A165-4F88-89A1-E771BCFCD352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="16" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1B1D65-A165-4F88-89A1-E771BCFCD352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FFCC10-122B-49E7-852B-5FB9E744AFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="11" activeTab="16" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="836" firstSheet="1" activeTab="6" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -26,21 +26,26 @@
     <sheet name="Element Objects" sheetId="28" r:id="rId11"/>
     <sheet name="Shell Objects" sheetId="29" r:id="rId12"/>
     <sheet name="Restraints" sheetId="18" r:id="rId13"/>
-    <sheet name="Nodal Loads" sheetId="32" r:id="rId14"/>
-    <sheet name="Concentrated Elemental Loads" sheetId="33" r:id="rId15"/>
-    <sheet name="Distributed Elemental Loads" sheetId="34" r:id="rId16"/>
-    <sheet name="Shell to Elemental Loads" sheetId="36" r:id="rId17"/>
+    <sheet name="Load Cases" sheetId="38" r:id="rId14"/>
+    <sheet name="Load Combinations" sheetId="37" r:id="rId15"/>
+    <sheet name="Nodal Loads" sheetId="32" r:id="rId16"/>
+    <sheet name="Concentrated Elemental Loads" sheetId="33" r:id="rId17"/>
+    <sheet name="Distributed Elemental Loads" sheetId="34" r:id="rId18"/>
+    <sheet name="Shell to Elemental Loads" sheetId="36" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="Base_Sec">'Frame Sections'!$A$20:$A$1019</definedName>
-    <definedName name="Blank">ListDB!$FC$2:$FC$1001</definedName>
+    <definedName name="Basic_Load_Case_Name">ListDB!$W$2:$W$1001</definedName>
+    <definedName name="Blank">ListDB!$FJ$2:$FJ$1001</definedName>
+    <definedName name="Directional_Comb">ListDB!$AC$2:$AC$1001</definedName>
     <definedName name="Elastic_Mat_Name">ListDB!$L$2:$L$1001</definedName>
     <definedName name="Ele_Type">ListDB!$Q$2:$Q$1001</definedName>
     <definedName name="Element_ID">'Element Objects'!$A$16:$A$1048576</definedName>
     <definedName name="Int_Type">ListDB!$N$2:$N$1001</definedName>
     <definedName name="Int_Type_Con">ListDB!$P$2:$P$1001</definedName>
     <definedName name="Int_Type_Dist">ListDB!$O$2:$O$1001</definedName>
-    <definedName name="LC_Type">ListDB!$V$2:$V$1001</definedName>
+    <definedName name="Load_Case_Name">ListDB!$V$2:$V$1001</definedName>
+    <definedName name="Load_Case_Type">ListDB!$X$2:$X$1001</definedName>
     <definedName name="Mat_Concrete">ListDB!$J$2:$J$1001</definedName>
     <definedName name="Mat_Model_Agg">ListDB!$G$2:$G$1001</definedName>
     <definedName name="Mat_Model_Concrete">ListDB!$D$2:$D$1001</definedName>
@@ -49,8 +54,12 @@
     <definedName name="Mat_Name">ListDB!$I$2:$I$1001</definedName>
     <definedName name="Mat_Steel">ListDB!$K$2:$K$1001</definedName>
     <definedName name="Mat_Type">ListDB!$C$2:$C$1001</definedName>
+    <definedName name="Modal_Comb">ListDB!$AB$2:$AB$1001</definedName>
+    <definedName name="Modal_Load_Type">ListDB!$Z$2:$Z$1001</definedName>
     <definedName name="NL_Mat_Name">ListDB!$M$2:$M$1001</definedName>
     <definedName name="Node_ID">'Node Objects'!$A$8:$A$1048576</definedName>
+    <definedName name="Normal_Load_Type">ListDB!$AA$2:$AA$1001</definedName>
+    <definedName name="RS_Load_Type">ListDB!$Y$2:$Y$1001</definedName>
     <definedName name="Sec_Model">ListDB!$S$2:$S$1001</definedName>
     <definedName name="Sec_Name">ListDB!$U$2:$U$1001</definedName>
     <definedName name="Sec_name_wo_agg">ListDB!$T$2:$T$1001</definedName>
@@ -61,12 +70,12 @@
     <definedName name="Shell_ID">'Shell Objects'!$A$11:$A$1048576</definedName>
     <definedName name="Slab_Sec">'Slab Sections'!$A$7:$A$1006</definedName>
     <definedName name="Spring_Mat_Name">ListDB!$H$2:$H$1048576</definedName>
-    <definedName name="Unit_Angle">ListDB!$AB$2:$AB$3</definedName>
-    <definedName name="Unit_Force">ListDB!$W$2:$W$8</definedName>
-    <definedName name="Unit_Length">ListDB!$X$2:$X$6</definedName>
-    <definedName name="Unit_Mass">ListDB!$Y$2:$Y$6</definedName>
-    <definedName name="Unit_Stress">ListDB!$Z$2:$Z$9</definedName>
-    <definedName name="Unit_Time">ListDB!$AA$2:$AA$3</definedName>
+    <definedName name="Unit_Angle">ListDB!$AI$2:$AI$3</definedName>
+    <definedName name="Unit_Force">ListDB!$AD$2:$AD$8</definedName>
+    <definedName name="Unit_Length">ListDB!$AE$2:$AE$6</definedName>
+    <definedName name="Unit_Mass">ListDB!$AF$2:$AF$6</definedName>
+    <definedName name="Unit_Stress">ListDB!$AG$2:$AG$9</definedName>
+    <definedName name="Unit_Time">ListDB!$AH$2:$AH$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -129,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="445">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1043,27 +1052,12 @@
     <t>Zero Length</t>
   </si>
   <si>
-    <t>Selfweight</t>
-  </si>
-  <si>
     <t>Dead</t>
   </si>
   <si>
     <t>Live</t>
   </si>
   <si>
-    <t>Earthquake-X</t>
-  </si>
-  <si>
-    <t>Earthquake-Y</t>
-  </si>
-  <si>
-    <t>Wind-X</t>
-  </si>
-  <si>
-    <t>Wind-Y</t>
-  </si>
-  <si>
     <t>- Unique Name: Name used as unique identification for each node (Input as String, Max. 15 characters)</t>
   </si>
   <si>
@@ -1215,6 +1209,270 @@
   </si>
   <si>
     <t>- Mass Source: Source (seimic code) in computing structural mass (Choose from the list)</t>
+  </si>
+  <si>
+    <t>Load Case Name</t>
+  </si>
+  <si>
+    <t>Linear Static</t>
+  </si>
+  <si>
+    <t>Nonlinear Static</t>
+  </si>
+  <si>
+    <t>Modal</t>
+  </si>
+  <si>
+    <t>Response Spectrum</t>
+  </si>
+  <si>
+    <t>Linear Time History</t>
+  </si>
+  <si>
+    <t>Nonlinear Time History</t>
+  </si>
+  <si>
+    <t>Self Weight</t>
+  </si>
+  <si>
+    <t>- Load Case Name: Name of load case as identifictaion of each load case (Input as String, Max. 32 characters)</t>
+  </si>
+  <si>
+    <t>- Load Case Type:Type of load case (Choose from the list)</t>
+  </si>
+  <si>
+    <t>Eigenvalue</t>
+  </si>
+  <si>
+    <t>Param1</t>
+  </si>
+  <si>
+    <t>Param2</t>
+  </si>
+  <si>
+    <t>Param3</t>
+  </si>
+  <si>
+    <t>Param4</t>
+  </si>
+  <si>
+    <t>Param5</t>
+  </si>
+  <si>
+    <t>Seismic</t>
+  </si>
+  <si>
+    <t>Wind</t>
+  </si>
+  <si>
+    <t>RespX</t>
+  </si>
+  <si>
+    <t>Normal Load Type</t>
+  </si>
+  <si>
+    <t>Modal Load Type</t>
+  </si>
+  <si>
+    <t>Response Spectrum Load Type</t>
+  </si>
+  <si>
+    <t>- Keep red-colored cells with blank or a value of 0.0</t>
+  </si>
+  <si>
+    <t>Load Type 1</t>
+  </si>
+  <si>
+    <t>Load Type 2</t>
+  </si>
+  <si>
+    <t>Load Type 3</t>
+  </si>
+  <si>
+    <t>Load Type 4</t>
+  </si>
+  <si>
+    <t>Load Type 5</t>
+  </si>
+  <si>
+    <t>Load Type 6</t>
+  </si>
+  <si>
+    <t>Function Name 1</t>
+  </si>
+  <si>
+    <t>Function Name 2</t>
+  </si>
+  <si>
+    <t>Function Name 3</t>
+  </si>
+  <si>
+    <t>Function Name 4</t>
+  </si>
+  <si>
+    <t>Function Name 5</t>
+  </si>
+  <si>
+    <t>Function Name 6</t>
+  </si>
+  <si>
+    <t>Scale Factor 1</t>
+  </si>
+  <si>
+    <t>Scale Factor 2</t>
+  </si>
+  <si>
+    <t>Scale Factor 3</t>
+  </si>
+  <si>
+    <t>Scale Factor 4</t>
+  </si>
+  <si>
+    <t>Scale Factor 5</t>
+  </si>
+  <si>
+    <t>Scale Factor 6</t>
+  </si>
+  <si>
+    <t>Accel UX</t>
+  </si>
+  <si>
+    <t>Accel UY</t>
+  </si>
+  <si>
+    <t>Accel UZ</t>
+  </si>
+  <si>
+    <t>Accel RX</t>
+  </si>
+  <si>
+    <t>Accel RY</t>
+  </si>
+  <si>
+    <t>Accel RZ</t>
+  </si>
+  <si>
+    <t>- Number of Modes: Number of modes on modal (Input as Float)</t>
+  </si>
+  <si>
+    <t>Modal Combination Method</t>
+  </si>
+  <si>
+    <t>CQC</t>
+  </si>
+  <si>
+    <t>SRSS</t>
+  </si>
+  <si>
+    <t>Directional Combination Type</t>
+  </si>
+  <si>
+    <t>- Modal Combination Method: Method of modal combination on Response Spectrum (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Directional Combination Type: Type of directional combination on Response Spectrum (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Modal damping: Value of modal damping (Input as Float)</t>
+  </si>
+  <si>
+    <t>- Load case parameters of modal: 1=Number of Modes</t>
+  </si>
+  <si>
+    <t>- Diaphragm eccentricity: Eccentricity ratio of diaphragm (Input as Float)</t>
+  </si>
+  <si>
+    <t>- Load Type 1-6: Type of load applied on load case 1-6 (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Function Name 1-6: Filename of function as input function on response spectrum and Time History. Associate to load case 1-6 (Input as String, Max. 64 characters)</t>
+  </si>
+  <si>
+    <t>- Scale Factor 1-6: A factor to be applied on load case 1-6 (Input as Float)</t>
+  </si>
+  <si>
+    <t>Param6</t>
+  </si>
+  <si>
+    <t>Param7</t>
+  </si>
+  <si>
+    <t>Param8</t>
+  </si>
+  <si>
+    <t>- Load case parameters of linear static: 1=Scale Factor 1, 2=Scale Factor 2, 3=Scale Factor 3, 4=Scale Factor 4, 5=Scale Factor 5, 6=Scale Factor 6</t>
+  </si>
+  <si>
+    <t>- Load case parameters of response spectrum: 1=Scale Factor 1, 2=Scale Factor 2, 3=Scale Factor 3, 4=Scale Factor 4, 5=Scale Factor 5, 6=Scale Factor 6, 7=Modal damping, 8=Diaphragm eccentricity</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Load Combination Name</t>
+  </si>
+  <si>
+    <t>Load Name 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal Load Case Name </t>
+  </si>
+  <si>
+    <t>Comb1</t>
+  </si>
+  <si>
+    <t>Comb2</t>
+  </si>
+  <si>
+    <t>Comb3</t>
+  </si>
+  <si>
+    <t>Load Name 2</t>
+  </si>
+  <si>
+    <t>Load Name 3</t>
+  </si>
+  <si>
+    <t>Load Name 4</t>
+  </si>
+  <si>
+    <t>Load Name 5</t>
+  </si>
+  <si>
+    <t>Load Name 6</t>
+  </si>
+  <si>
+    <t>- Load Combination Name: Name of load combination as identifictaion of each load combination (Input as String, Max. 32 characters)</t>
+  </si>
+  <si>
+    <t>Load Name 7</t>
+  </si>
+  <si>
+    <t>Scale Factor 7</t>
+  </si>
+  <si>
+    <t>Load Name 8</t>
+  </si>
+  <si>
+    <t>Scale Factor 8</t>
+  </si>
+  <si>
+    <t>Load Name 9</t>
+  </si>
+  <si>
+    <t>Scale Factor 9</t>
+  </si>
+  <si>
+    <t>Load Name 10</t>
+  </si>
+  <si>
+    <t>Scale Factor 10</t>
+  </si>
+  <si>
+    <t>- Load Name 1-10: Name of load applied on load combiantion 1-10 (Choose from the list)</t>
+  </si>
+  <si>
+    <t>- Scale Factor 1-10: A factor to be applied on load combination. Associate to load name 1-10 (Input as Float)</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1485,7 @@
     <numFmt numFmtId="166" formatCode="0.#####"/>
     <numFmt numFmtId="167" formatCode="0.####"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1354,8 +1612,22 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1374,8 +1646,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14996795556505021"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1478,11 +1762,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="10">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="280">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2061,10 +2366,6 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2173,6 +2474,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2209,27 +2526,132 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Button" xfId="2" xr:uid="{519C59DD-8EA1-42FB-9ADD-C661AB23375A}"/>
+    <cellStyle name="Header" xfId="1" xr:uid="{C680F4A0-C721-4337-A625-6F2BD6BE23C6}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2424,8 +2846,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFC7CE"/>
       <color rgb="FF9C0006"/>
-      <color rgb="FFFFC7CE"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2894,8 +3316,8 @@
       <c r="I1" s="61"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="215" t="s">
-        <v>311</v>
+      <c r="A2" s="230" t="s">
+        <v>306</v>
       </c>
       <c r="B2" s="110"/>
       <c r="C2" s="110"/>
@@ -4771,8 +5193,8 @@
       <c r="J1" s="113"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="215" t="s">
-        <v>314</v>
+      <c r="A2" s="214" t="s">
+        <v>309</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
@@ -4785,8 +5207,8 @@
       <c r="J2" s="114"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="215" t="s">
-        <v>316</v>
+      <c r="A3" s="214" t="s">
+        <v>311</v>
       </c>
       <c r="B3" s="78"/>
       <c r="C3" s="78"/>
@@ -4799,8 +5221,8 @@
       <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="215" t="s">
-        <v>315</v>
+      <c r="A4" s="214" t="s">
+        <v>310</v>
       </c>
       <c r="B4" s="78"/>
       <c r="C4" s="78"/>
@@ -4885,8 +5307,8 @@
       <c r="J9" s="114"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="215" t="s">
-        <v>317</v>
+      <c r="A10" s="214" t="s">
+        <v>312</v>
       </c>
       <c r="B10" s="78"/>
       <c r="C10" s="78"/>
@@ -13305,12 +13727,12 @@
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="G16:G1048576">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>OR(E16="Auto from Connectivity")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16:H1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>OR(E16="Auto from Connectivity")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13376,8 +13798,8 @@
       <c r="J1" s="76"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="215" t="s">
-        <v>318</v>
+      <c r="A2" s="214" t="s">
+        <v>313</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
@@ -13390,8 +13812,8 @@
       <c r="J2" s="80"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="221" t="s">
-        <v>336</v>
+      <c r="A3" s="220" t="s">
+        <v>331</v>
       </c>
       <c r="B3" s="78"/>
       <c r="C3" s="78"/>
@@ -13404,8 +13826,8 @@
       <c r="J3" s="80"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="243" t="s">
-        <v>354</v>
+      <c r="A4" s="230" t="s">
+        <v>349</v>
       </c>
       <c r="B4" s="78"/>
       <c r="C4" s="78"/>
@@ -13418,8 +13840,8 @@
       <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="243" t="s">
-        <v>355</v>
+      <c r="A5" s="230" t="s">
+        <v>350</v>
       </c>
       <c r="B5" s="78"/>
       <c r="C5" s="78"/>
@@ -13432,8 +13854,8 @@
       <c r="J5" s="80"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="243" t="s">
-        <v>356</v>
+      <c r="A6" s="230" t="s">
+        <v>351</v>
       </c>
       <c r="B6" s="78"/>
       <c r="C6" s="78"/>
@@ -13460,8 +13882,8 @@
       <c r="J7" s="80"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="217" t="s">
-        <v>319</v>
+      <c r="A8" s="216" t="s">
+        <v>314</v>
       </c>
       <c r="B8" s="84"/>
       <c r="C8" s="84"/>
@@ -15030,8 +15452,8 @@
       <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="216" t="s">
-        <v>313</v>
+      <c r="A2" s="215" t="s">
+        <v>308</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -15125,7 +15547,7 @@
     </row>
     <row r="10" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>37</v>
@@ -15735,7 +16157,874 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F06F806-B35D-4DC5-A819-F2CA4AA0ACD3}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:X19"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="20.7109375" style="135" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="135" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="135" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" style="135" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="135" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="135" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" style="135" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="135" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="135" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="135" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" style="135" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" style="135" customWidth="1"/>
+    <col min="14" max="14" width="20.7109375" style="135" customWidth="1"/>
+    <col min="15" max="16" width="30.7109375" style="135" customWidth="1"/>
+    <col min="17" max="24" width="15.7109375" style="261" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="124"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A1" s="126" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="247"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="273" t="s">
+        <v>422</v>
+      </c>
+      <c r="P1" s="253"/>
+      <c r="Q1" s="253"/>
+      <c r="R1" s="253"/>
+      <c r="S1" s="253"/>
+      <c r="T1" s="253"/>
+      <c r="U1" s="253"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="253"/>
+      <c r="X1" s="254"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="252" t="s">
+        <v>365</v>
+      </c>
+      <c r="B2" s="248"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="271"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="268" t="s">
+        <v>416</v>
+      </c>
+      <c r="K2" s="272"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="267" t="s">
+        <v>420</v>
+      </c>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="272"/>
+      <c r="R2" s="268"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="255"/>
+      <c r="U2" s="255"/>
+      <c r="V2" s="255"/>
+      <c r="W2" s="255"/>
+      <c r="X2" s="256"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="252" t="s">
+        <v>366</v>
+      </c>
+      <c r="B3" s="248"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="271"/>
+      <c r="H3" s="268"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="268" t="s">
+        <v>404</v>
+      </c>
+      <c r="K3" s="272"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="267" t="s">
+        <v>412</v>
+      </c>
+      <c r="P3" s="270"/>
+      <c r="Q3" s="272"/>
+      <c r="R3" s="269"/>
+      <c r="S3" s="255"/>
+      <c r="T3" s="255"/>
+      <c r="U3" s="255"/>
+      <c r="V3" s="255"/>
+      <c r="W3" s="255"/>
+      <c r="X3" s="256"/>
+    </row>
+    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="252" t="s">
+        <v>414</v>
+      </c>
+      <c r="B4" s="249"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="269" t="s">
+        <v>411</v>
+      </c>
+      <c r="K4" s="271"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
+      <c r="O4" s="252" t="s">
+        <v>421</v>
+      </c>
+      <c r="P4" s="277"/>
+      <c r="Q4" s="277"/>
+      <c r="R4" s="277"/>
+      <c r="S4" s="277"/>
+      <c r="T4" s="277"/>
+      <c r="U4" s="277"/>
+      <c r="V4" s="277"/>
+      <c r="W4" s="277"/>
+      <c r="X4" s="278"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="252" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="249"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="G5" s="271"/>
+      <c r="H5" s="268"/>
+      <c r="I5" s="131"/>
+      <c r="J5" s="268" t="s">
+        <v>413</v>
+      </c>
+      <c r="K5" s="271"/>
+      <c r="L5" s="130"/>
+      <c r="M5" s="130"/>
+      <c r="N5" s="130"/>
+      <c r="O5" s="276"/>
+      <c r="P5" s="277"/>
+      <c r="Q5" s="277"/>
+      <c r="R5" s="277"/>
+      <c r="S5" s="277"/>
+      <c r="T5" s="277"/>
+      <c r="U5" s="277"/>
+      <c r="V5" s="277"/>
+      <c r="W5" s="277"/>
+      <c r="X5" s="278"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="264" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="249"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="G6" s="271"/>
+      <c r="H6" s="271"/>
+      <c r="I6" s="131"/>
+      <c r="J6" s="130"/>
+      <c r="K6" s="271"/>
+      <c r="L6" s="130"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="130"/>
+      <c r="O6" s="265"/>
+      <c r="P6" s="270"/>
+      <c r="Q6" s="270"/>
+      <c r="R6" s="270"/>
+      <c r="S6" s="255"/>
+      <c r="T6" s="255"/>
+      <c r="U6" s="255"/>
+      <c r="V6" s="255"/>
+      <c r="W6" s="255"/>
+      <c r="X6" s="256"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="264" t="s">
+        <v>410</v>
+      </c>
+      <c r="B7" s="249"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="271"/>
+      <c r="H7" s="271"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="271"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
+      <c r="O7" s="265"/>
+      <c r="P7" s="270"/>
+      <c r="Q7" s="270"/>
+      <c r="R7" s="270"/>
+      <c r="S7" s="255"/>
+      <c r="T7" s="255"/>
+      <c r="U7" s="255"/>
+      <c r="V7" s="255"/>
+      <c r="W7" s="255"/>
+      <c r="X7" s="256"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="129"/>
+      <c r="B8" s="249"/>
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="G8" s="271"/>
+      <c r="H8" s="271"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="271"/>
+      <c r="L8" s="130"/>
+      <c r="M8" s="130"/>
+      <c r="N8" s="130"/>
+      <c r="O8" s="265"/>
+      <c r="P8" s="270"/>
+      <c r="Q8" s="270"/>
+      <c r="R8" s="270"/>
+      <c r="S8" s="255"/>
+      <c r="T8" s="255"/>
+      <c r="U8" s="255"/>
+      <c r="V8" s="255"/>
+      <c r="W8" s="255"/>
+      <c r="X8" s="256"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="249"/>
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="131"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="271"/>
+      <c r="L9" s="130"/>
+      <c r="M9" s="130"/>
+      <c r="N9" s="130"/>
+      <c r="O9" s="265"/>
+      <c r="P9" s="270"/>
+      <c r="Q9" s="270"/>
+      <c r="R9" s="270"/>
+      <c r="S9" s="255"/>
+      <c r="T9" s="255"/>
+      <c r="U9" s="255"/>
+      <c r="V9" s="255"/>
+      <c r="W9" s="255"/>
+      <c r="X9" s="256"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
+        <v>379</v>
+      </c>
+      <c r="B10" s="250"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="133"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="133"/>
+      <c r="N10" s="133"/>
+      <c r="O10" s="266"/>
+      <c r="P10" s="257"/>
+      <c r="Q10" s="257"/>
+      <c r="R10" s="257"/>
+      <c r="S10" s="257"/>
+      <c r="T10" s="257"/>
+      <c r="U10" s="257"/>
+      <c r="V10" s="257"/>
+      <c r="W10" s="257"/>
+      <c r="X10" s="258"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="124"/>
+      <c r="K11" s="124"/>
+      <c r="L11" s="124"/>
+      <c r="M11" s="124"/>
+      <c r="N11" s="124"/>
+      <c r="O11" s="259"/>
+      <c r="P11" s="259"/>
+      <c r="Q11" s="259"/>
+      <c r="R11" s="259"/>
+      <c r="S11" s="259"/>
+      <c r="T11" s="259"/>
+      <c r="U11" s="259"/>
+      <c r="V11" s="259"/>
+      <c r="W11" s="259"/>
+      <c r="X11" s="259"/>
+    </row>
+    <row r="12" spans="1:24" s="120" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="125" t="s">
+        <v>357</v>
+      </c>
+      <c r="B12" s="125" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="125" t="s">
+        <v>380</v>
+      </c>
+      <c r="D12" s="125" t="s">
+        <v>386</v>
+      </c>
+      <c r="E12" s="125" t="s">
+        <v>381</v>
+      </c>
+      <c r="F12" s="125" t="s">
+        <v>387</v>
+      </c>
+      <c r="G12" s="125" t="s">
+        <v>382</v>
+      </c>
+      <c r="H12" s="125" t="s">
+        <v>388</v>
+      </c>
+      <c r="I12" s="125" t="s">
+        <v>383</v>
+      </c>
+      <c r="J12" s="125" t="s">
+        <v>389</v>
+      </c>
+      <c r="K12" s="125" t="s">
+        <v>384</v>
+      </c>
+      <c r="L12" s="125" t="s">
+        <v>390</v>
+      </c>
+      <c r="M12" s="125" t="s">
+        <v>385</v>
+      </c>
+      <c r="N12" s="125" t="s">
+        <v>391</v>
+      </c>
+      <c r="O12" s="260" t="s">
+        <v>405</v>
+      </c>
+      <c r="P12" s="260" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q12" s="260" t="s">
+        <v>368</v>
+      </c>
+      <c r="R12" s="260" t="s">
+        <v>369</v>
+      </c>
+      <c r="S12" s="260" t="s">
+        <v>370</v>
+      </c>
+      <c r="T12" s="260" t="s">
+        <v>371</v>
+      </c>
+      <c r="U12" s="260" t="s">
+        <v>372</v>
+      </c>
+      <c r="V12" s="260" t="s">
+        <v>417</v>
+      </c>
+      <c r="W12" s="260" t="s">
+        <v>418</v>
+      </c>
+      <c r="X12" s="260" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="251" t="s">
+        <v>364</v>
+      </c>
+      <c r="B13" s="135" t="s">
+        <v>358</v>
+      </c>
+      <c r="C13" s="135" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q13" s="261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="251" t="s">
+        <v>360</v>
+      </c>
+      <c r="B14" s="135" t="s">
+        <v>360</v>
+      </c>
+      <c r="C14" s="135" t="s">
+        <v>367</v>
+      </c>
+      <c r="Q14" s="261">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="251" t="s">
+        <v>304</v>
+      </c>
+      <c r="B15" s="135" t="s">
+        <v>358</v>
+      </c>
+      <c r="C15" s="135" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q15" s="261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" s="135" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="251" t="s">
+        <v>305</v>
+      </c>
+      <c r="B16" s="135" t="s">
+        <v>358</v>
+      </c>
+      <c r="C16" s="135" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q16" s="261">
+        <v>1</v>
+      </c>
+      <c r="R16" s="261"/>
+      <c r="S16" s="261"/>
+      <c r="T16" s="261"/>
+      <c r="U16" s="261"/>
+      <c r="V16" s="261"/>
+      <c r="W16" s="261"/>
+      <c r="X16" s="261"/>
+    </row>
+    <row r="17" spans="1:24" s="135" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="251" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="135" t="s">
+        <v>358</v>
+      </c>
+      <c r="C17" s="135" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="261">
+        <v>1</v>
+      </c>
+      <c r="R17" s="261"/>
+      <c r="S17" s="261"/>
+      <c r="T17" s="261"/>
+      <c r="U17" s="261"/>
+      <c r="V17" s="261"/>
+      <c r="W17" s="261"/>
+      <c r="X17" s="261"/>
+    </row>
+    <row r="18" spans="1:24" s="135" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="251" t="s">
+        <v>375</v>
+      </c>
+      <c r="B18" s="135" t="s">
+        <v>361</v>
+      </c>
+      <c r="C18" s="135" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q18" s="261">
+        <v>9.8066499999999994</v>
+      </c>
+      <c r="R18" s="261"/>
+      <c r="S18" s="261"/>
+      <c r="T18" s="261"/>
+      <c r="U18" s="261"/>
+      <c r="V18" s="261"/>
+      <c r="W18" s="261"/>
+      <c r="X18" s="261"/>
+    </row>
+    <row r="19" spans="1:24" s="135" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="251"/>
+      <c r="Q19" s="261"/>
+      <c r="R19" s="261"/>
+      <c r="S19" s="261"/>
+      <c r="T19" s="261"/>
+      <c r="U19" s="261"/>
+      <c r="V19" s="261"/>
+      <c r="X19" s="261"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D13:D1048576 F13:F1048576 H13:H1048576 J13:J1048576 N13:N1048576 L13:L1048576">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>OR($B13="Linear Static",$B13="Modal",$B13="Nonlinear Static")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O13:P1048576">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>OR($B13="Linear Static",$B13="Nonlinear Static", $B13="Modal",$B13="Linear Time History",$B13="Nonlinear Time History")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="9">
+    <dataValidation type="decimal" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="S13:T1048576 Q13 Q15:Q1048576" xr:uid="{E83FA1B3-9A14-4A46-BCD5-687BB132C6B0}">
+      <formula1>1</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="T13:T1048576" xr:uid="{AC94006E-E29A-4D66-ABA1-0EF21C06EE2A}">
+      <formula1>1</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="R13:V1048576 Q13 Q15:Q1048576" xr:uid="{3D3CCD84-10F7-4B18-BDA5-7F9D2CF2333C}">
+      <formula1>1</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter maximum 64 characters only." sqref="F13:F1048576 J13:J1048576 N13:N1048576 L13:L1048576 H13:H1048576 D13:D1048576" xr:uid="{7053D0B9-6996-4308-BD51-E55EE550AFCB}">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B13:B1048576" xr:uid="{4D2426DE-BDB5-4F0B-9999-8C7F914333DF}">
+      <formula1>Load_Case_Type</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter maximum 32 characters only." sqref="A13:A1048576" xr:uid="{4C2A4FC0-267E-41F0-A5B9-DB15A26C8D58}">
+      <formula1>1</formula1>
+      <formula2>32</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="W20:X1048576 X19 W13:X18 Q14" xr:uid="{F9039510-7A46-48BE-BA7A-78130746BBED}">
+      <formula1>-1000000000000</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="O13:P1048576 Q13 Q15:Q1048576" xr:uid="{417BFD0A-8E0C-4B35-86FD-B34943A6BAF8}">
+      <formula1>IF($B13="Response Spectrum",Modal_Comb,Blank)</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="E13:E1048576 C13:C1048576 K13:K1048576 I13:I1048576 M13:M1048576 G13:G1048576" xr:uid="{77E89617-D8C6-4EA4-8EFF-70194D12216B}">
+      <formula1>IF($B13="Linear Static",Normal_Load_Type,IF($B13="Modal",Modal_Load_Type,IF($B13="Response Spectrum",RS_Load_Type,Blank)))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B66DDE-F08F-4329-A2F8-5CA655E88314}">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:U13"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" style="135" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="135" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="261" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="135" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" style="261" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="135" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="261" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="135" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" style="261" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="135" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="261" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" style="135" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" style="261" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" style="135" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" style="261" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" style="135" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" style="261" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" style="135" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" style="261" customWidth="1"/>
+    <col min="20" max="20" width="15.7109375" style="135" customWidth="1"/>
+    <col min="21" max="21" width="15.7109375" style="261" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="124"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="126" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="247"/>
+      <c r="C1" s="253"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="253"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="253"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="253"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="253"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="253"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="253"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="254"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="252" t="s">
+        <v>434</v>
+      </c>
+      <c r="B2" s="248"/>
+      <c r="C2" s="270"/>
+      <c r="D2" s="271"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="271"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="271"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="270"/>
+      <c r="L2" s="271"/>
+      <c r="M2" s="270"/>
+      <c r="N2" s="271"/>
+      <c r="O2" s="270"/>
+      <c r="P2" s="271"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="271"/>
+      <c r="S2" s="270"/>
+      <c r="T2" s="271"/>
+      <c r="U2" s="256"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="252" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" s="249"/>
+      <c r="C3" s="270"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="271"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="271"/>
+      <c r="I3" s="270"/>
+      <c r="J3" s="271"/>
+      <c r="K3" s="270"/>
+      <c r="L3" s="271"/>
+      <c r="M3" s="270"/>
+      <c r="N3" s="271"/>
+      <c r="O3" s="270"/>
+      <c r="P3" s="271"/>
+      <c r="Q3" s="270"/>
+      <c r="R3" s="271"/>
+      <c r="S3" s="270"/>
+      <c r="T3" s="271"/>
+      <c r="U3" s="256"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="279" t="s">
+        <v>444</v>
+      </c>
+      <c r="B4" s="250"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="257"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="257"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="257"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="257"/>
+      <c r="N4" s="133"/>
+      <c r="O4" s="257"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="257"/>
+      <c r="R4" s="133"/>
+      <c r="S4" s="257"/>
+      <c r="T4" s="133"/>
+      <c r="U4" s="258"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="124"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="259"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="259"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="259"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="259"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="259"/>
+      <c r="L5" s="124"/>
+      <c r="M5" s="259"/>
+      <c r="N5" s="124"/>
+      <c r="O5" s="259"/>
+      <c r="P5" s="124"/>
+      <c r="Q5" s="259"/>
+      <c r="R5" s="124"/>
+      <c r="S5" s="259"/>
+      <c r="T5" s="124"/>
+      <c r="U5" s="259"/>
+    </row>
+    <row r="6" spans="1:21" s="120" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="125" t="s">
+        <v>423</v>
+      </c>
+      <c r="B6" s="125" t="s">
+        <v>424</v>
+      </c>
+      <c r="C6" s="260" t="s">
+        <v>392</v>
+      </c>
+      <c r="D6" s="125" t="s">
+        <v>429</v>
+      </c>
+      <c r="E6" s="260" t="s">
+        <v>393</v>
+      </c>
+      <c r="F6" s="125" t="s">
+        <v>430</v>
+      </c>
+      <c r="G6" s="260" t="s">
+        <v>394</v>
+      </c>
+      <c r="H6" s="125" t="s">
+        <v>431</v>
+      </c>
+      <c r="I6" s="260" t="s">
+        <v>395</v>
+      </c>
+      <c r="J6" s="125" t="s">
+        <v>432</v>
+      </c>
+      <c r="K6" s="260" t="s">
+        <v>396</v>
+      </c>
+      <c r="L6" s="125" t="s">
+        <v>433</v>
+      </c>
+      <c r="M6" s="260" t="s">
+        <v>397</v>
+      </c>
+      <c r="N6" s="125" t="s">
+        <v>435</v>
+      </c>
+      <c r="O6" s="260" t="s">
+        <v>436</v>
+      </c>
+      <c r="P6" s="125" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q6" s="260" t="s">
+        <v>438</v>
+      </c>
+      <c r="R6" s="125" t="s">
+        <v>439</v>
+      </c>
+      <c r="S6" s="260" t="s">
+        <v>440</v>
+      </c>
+      <c r="T6" s="125" t="s">
+        <v>441</v>
+      </c>
+      <c r="U6" s="260" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="251" t="s">
+        <v>426</v>
+      </c>
+      <c r="B7" s="135" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="261">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="251" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="251" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="251"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="251"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="251"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="251"/>
+    </row>
+  </sheetData>
+  <dataValidations count="6">
+    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter maximum 32 characters only." sqref="A7:A1048576" xr:uid="{A1D704A2-8AA0-42C0-A16D-2041D9EDB529}">
+      <formula1>1</formula1>
+      <formula2>32</formula2>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B7:B1048576 F7:F1048576 H7:H1048576 J7:J1048576 D7:D1048576 L7:L1048576 N7:N1048576 P7:P1048576 R7:R1048576 T7:T1048576" xr:uid="{9524B9FE-2F72-4051-9C68-E1368E298B47}">
+      <formula1>Load_Case_Name</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="C7:C1048576 E7:E1048576 G7:G1048576 I7:I1048576 K7:K1048576 M7:M1048576 O7:O1048576 Q7:Q1048576 S7:S1048576 U7:U1048576" xr:uid="{2CC3C382-0BEC-4663-A7A8-9870A3FDA6E8}">
+      <formula1>1</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="K7:K1048576 G7:G1048576 E7:E1048576 C7:C1048576" xr:uid="{3D34147E-5F46-4A36-814A-FEF9108F901D}">
+      <formula1>1</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="I7:I1048576" xr:uid="{F2976A9B-31C1-4BA3-95DC-A97510B606F6}">
+      <formula1>1</formula1>
+      <formula2>1000000000000</formula2>
+    </dataValidation>
+    <dataValidation type="textLength" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Please enter a float value only." sqref="I7:I1048576" xr:uid="{DAA2ADCA-00AE-48CD-876A-E47940738408}">
+      <formula1>1</formula1>
+      <formula2>64</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8BF8F5-8B72-4F82-8AD5-2105268CD711}">
+  <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15757,8 +17046,8 @@
       <c r="H1" s="128"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="203" t="s">
-        <v>320</v>
+      <c r="A2" s="202" t="s">
+        <v>315</v>
       </c>
       <c r="B2" s="130"/>
       <c r="C2" s="130"/>
@@ -15769,8 +17058,8 @@
       <c r="H2" s="131"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="203" t="s">
-        <v>321</v>
+      <c r="A3" s="202" t="s">
+        <v>316</v>
       </c>
       <c r="B3" s="130"/>
       <c r="C3" s="130"/>
@@ -15870,7 +17159,7 @@
     </row>
     <row r="11" spans="1:8" s="120" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="125" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B11" s="125" t="s">
         <v>215</v>
@@ -15904,15 +17193,16 @@
       <formula2>1000000000000</formula2>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B12:B1048576" xr:uid="{E93D2070-1536-4868-9F08-ED7C2E7CB253}">
-      <formula1>LC_Type</formula1>
+      <formula1>Basic_Load_Case_Name</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{105CF277-1F6A-492D-8E1A-EC3101EF3425}">
+  <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15937,8 +17227,8 @@
       <c r="K1" s="128"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="203" t="s">
-        <v>323</v>
+      <c r="A2" s="202" t="s">
+        <v>318</v>
       </c>
       <c r="B2" s="130"/>
       <c r="C2" s="130"/>
@@ -15952,8 +17242,8 @@
       <c r="K2" s="131"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="203" t="s">
-        <v>324</v>
+      <c r="A3" s="202" t="s">
+        <v>319</v>
       </c>
       <c r="B3" s="130"/>
       <c r="C3" s="130"/>
@@ -15967,8 +17257,8 @@
       <c r="K3" s="131"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="203" t="s">
-        <v>325</v>
+      <c r="A4" s="202" t="s">
+        <v>320</v>
       </c>
       <c r="B4" s="130"/>
       <c r="C4" s="130"/>
@@ -16124,7 +17414,7 @@
     </row>
     <row r="14" spans="1:11" s="120" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="125" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B14" s="125" t="s">
         <v>215</v>
@@ -16160,7 +17450,7 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B15:B1048576" xr:uid="{8399D4E5-15D3-44EB-BAF5-D4D9376E21A9}">
-      <formula1>LC_Type</formula1>
+      <formula1>Basic_Load_Case_Name</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A15:A1048576" xr:uid="{E806BA54-F03E-4170-B409-665005B7362E}">
       <formula1>Element_ID</formula1>
@@ -16177,8 +17467,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AAB727D-5FF3-4C5E-99AD-1C31CEAF2053}">
+  <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16205,8 +17496,8 @@
       <c r="L1" s="128"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="203" t="s">
-        <v>326</v>
+      <c r="A2" s="202" t="s">
+        <v>321</v>
       </c>
       <c r="B2" s="130"/>
       <c r="C2" s="130"/>
@@ -16221,8 +17512,8 @@
       <c r="L2" s="131"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="203" t="s">
-        <v>327</v>
+      <c r="A3" s="202" t="s">
+        <v>322</v>
       </c>
       <c r="B3" s="130"/>
       <c r="C3" s="130"/>
@@ -16237,8 +17528,8 @@
       <c r="L3" s="131"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="203" t="s">
-        <v>328</v>
+      <c r="A4" s="202" t="s">
+        <v>323</v>
       </c>
       <c r="B4" s="130"/>
       <c r="C4" s="130"/>
@@ -16421,7 +17712,7 @@
     </row>
     <row r="15" spans="1:12" s="120" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="125" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B15" s="125" t="s">
         <v>215</v>
@@ -16462,7 +17753,7 @@
         <v>101</v>
       </c>
       <c r="B16" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C16" s="135" t="s">
         <v>216</v>
@@ -16476,7 +17767,7 @@
         <v>102</v>
       </c>
       <c r="B17" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C17" s="135" t="s">
         <v>216</v>
@@ -16490,7 +17781,7 @@
         <v>103</v>
       </c>
       <c r="B18" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C18" s="135" t="s">
         <v>216</v>
@@ -16504,7 +17795,7 @@
         <v>104</v>
       </c>
       <c r="B19" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C19" s="135" t="s">
         <v>216</v>
@@ -16518,7 +17809,7 @@
         <v>117</v>
       </c>
       <c r="B20" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C20" s="135" t="s">
         <v>216</v>
@@ -16532,7 +17823,7 @@
         <v>118</v>
       </c>
       <c r="B21" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C21" s="135" t="s">
         <v>216</v>
@@ -16546,7 +17837,7 @@
         <v>119</v>
       </c>
       <c r="B22" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C22" s="135" t="s">
         <v>216</v>
@@ -16560,7 +17851,7 @@
         <v>120</v>
       </c>
       <c r="B23" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C23" s="135" t="s">
         <v>216</v>
@@ -16574,7 +17865,7 @@
         <v>181</v>
       </c>
       <c r="B24" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C24" s="135" t="s">
         <v>216</v>
@@ -16588,7 +17879,7 @@
         <v>185</v>
       </c>
       <c r="B25" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C25" s="135" t="s">
         <v>216</v>
@@ -16602,7 +17893,7 @@
         <v>186</v>
       </c>
       <c r="B26" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C26" s="135" t="s">
         <v>216</v>
@@ -16616,7 +17907,7 @@
         <v>190</v>
       </c>
       <c r="B27" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C27" s="135" t="s">
         <v>216</v>
@@ -16630,7 +17921,7 @@
         <v>191</v>
       </c>
       <c r="B28" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C28" s="135" t="s">
         <v>216</v>
@@ -16644,7 +17935,7 @@
         <v>195</v>
       </c>
       <c r="B29" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C29" s="135" t="s">
         <v>216</v>
@@ -16658,7 +17949,7 @@
         <v>196</v>
       </c>
       <c r="B30" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C30" s="135" t="s">
         <v>216</v>
@@ -16672,7 +17963,7 @@
         <v>200</v>
       </c>
       <c r="B31" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C31" s="135" t="s">
         <v>216</v>
@@ -16686,7 +17977,7 @@
         <v>121</v>
       </c>
       <c r="B32" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C32" s="135" t="s">
         <v>216</v>
@@ -16700,7 +17991,7 @@
         <v>122</v>
       </c>
       <c r="B33" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C33" s="135" t="s">
         <v>216</v>
@@ -16714,7 +18005,7 @@
         <v>123</v>
       </c>
       <c r="B34" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C34" s="135" t="s">
         <v>216</v>
@@ -16728,7 +18019,7 @@
         <v>124</v>
       </c>
       <c r="B35" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C35" s="135" t="s">
         <v>216</v>
@@ -16742,7 +18033,7 @@
         <v>137</v>
       </c>
       <c r="B36" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C36" s="135" t="s">
         <v>216</v>
@@ -16756,7 +18047,7 @@
         <v>138</v>
       </c>
       <c r="B37" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C37" s="135" t="s">
         <v>216</v>
@@ -16770,7 +18061,7 @@
         <v>139</v>
       </c>
       <c r="B38" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C38" s="135" t="s">
         <v>216</v>
@@ -16784,7 +18075,7 @@
         <v>140</v>
       </c>
       <c r="B39" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C39" s="135" t="s">
         <v>216</v>
@@ -16798,7 +18089,7 @@
         <v>201</v>
       </c>
       <c r="B40" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C40" s="135" t="s">
         <v>216</v>
@@ -16812,7 +18103,7 @@
         <v>205</v>
       </c>
       <c r="B41" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C41" s="135" t="s">
         <v>216</v>
@@ -16826,7 +18117,7 @@
         <v>206</v>
       </c>
       <c r="B42" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C42" s="135" t="s">
         <v>216</v>
@@ -16840,7 +18131,7 @@
         <v>210</v>
       </c>
       <c r="B43" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C43" s="135" t="s">
         <v>216</v>
@@ -16854,7 +18145,7 @@
         <v>211</v>
       </c>
       <c r="B44" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C44" s="135" t="s">
         <v>216</v>
@@ -16868,7 +18159,7 @@
         <v>215</v>
       </c>
       <c r="B45" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C45" s="135" t="s">
         <v>216</v>
@@ -16882,7 +18173,7 @@
         <v>216</v>
       </c>
       <c r="B46" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C46" s="135" t="s">
         <v>216</v>
@@ -16896,7 +18187,7 @@
         <v>220</v>
       </c>
       <c r="B47" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C47" s="135" t="s">
         <v>216</v>
@@ -16910,7 +18201,7 @@
         <v>141</v>
       </c>
       <c r="B48" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C48" s="135" t="s">
         <v>216</v>
@@ -16924,7 +18215,7 @@
         <v>142</v>
       </c>
       <c r="B49" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C49" s="135" t="s">
         <v>216</v>
@@ -16938,7 +18229,7 @@
         <v>143</v>
       </c>
       <c r="B50" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C50" s="135" t="s">
         <v>216</v>
@@ -16952,7 +18243,7 @@
         <v>144</v>
       </c>
       <c r="B51" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C51" s="135" t="s">
         <v>216</v>
@@ -16966,7 +18257,7 @@
         <v>157</v>
       </c>
       <c r="B52" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C52" s="135" t="s">
         <v>216</v>
@@ -16980,7 +18271,7 @@
         <v>158</v>
       </c>
       <c r="B53" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C53" s="135" t="s">
         <v>216</v>
@@ -16994,7 +18285,7 @@
         <v>159</v>
       </c>
       <c r="B54" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C54" s="135" t="s">
         <v>216</v>
@@ -17008,7 +18299,7 @@
         <v>160</v>
       </c>
       <c r="B55" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C55" s="135" t="s">
         <v>216</v>
@@ -17022,7 +18313,7 @@
         <v>221</v>
       </c>
       <c r="B56" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C56" s="135" t="s">
         <v>216</v>
@@ -17036,7 +18327,7 @@
         <v>225</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C57" s="135" t="s">
         <v>216</v>
@@ -17050,7 +18341,7 @@
         <v>226</v>
       </c>
       <c r="B58" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C58" s="135" t="s">
         <v>216</v>
@@ -17064,7 +18355,7 @@
         <v>230</v>
       </c>
       <c r="B59" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C59" s="135" t="s">
         <v>216</v>
@@ -17078,7 +18369,7 @@
         <v>231</v>
       </c>
       <c r="B60" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C60" s="135" t="s">
         <v>216</v>
@@ -17092,7 +18383,7 @@
         <v>235</v>
       </c>
       <c r="B61" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C61" s="135" t="s">
         <v>216</v>
@@ -17106,7 +18397,7 @@
         <v>236</v>
       </c>
       <c r="B62" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C62" s="135" t="s">
         <v>216</v>
@@ -17120,7 +18411,7 @@
         <v>240</v>
       </c>
       <c r="B63" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C63" s="135" t="s">
         <v>216</v>
@@ -17134,7 +18425,7 @@
         <v>161</v>
       </c>
       <c r="B64" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C64" s="135" t="s">
         <v>216</v>
@@ -17148,7 +18439,7 @@
         <v>162</v>
       </c>
       <c r="B65" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C65" s="135" t="s">
         <v>216</v>
@@ -17162,7 +18453,7 @@
         <v>163</v>
       </c>
       <c r="B66" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C66" s="135" t="s">
         <v>216</v>
@@ -17176,7 +18467,7 @@
         <v>164</v>
       </c>
       <c r="B67" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C67" s="135" t="s">
         <v>216</v>
@@ -17190,7 +18481,7 @@
         <v>177</v>
       </c>
       <c r="B68" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C68" s="135" t="s">
         <v>216</v>
@@ -17204,7 +18495,7 @@
         <v>178</v>
       </c>
       <c r="B69" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="135" t="s">
         <v>216</v>
@@ -17218,7 +18509,7 @@
         <v>179</v>
       </c>
       <c r="B70" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C70" s="135" t="s">
         <v>216</v>
@@ -17232,7 +18523,7 @@
         <v>180</v>
       </c>
       <c r="B71" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C71" s="135" t="s">
         <v>216</v>
@@ -17246,7 +18537,7 @@
         <v>241</v>
       </c>
       <c r="B72" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C72" s="135" t="s">
         <v>216</v>
@@ -17260,7 +18551,7 @@
         <v>245</v>
       </c>
       <c r="B73" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C73" s="135" t="s">
         <v>216</v>
@@ -17274,7 +18565,7 @@
         <v>246</v>
       </c>
       <c r="B74" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C74" s="135" t="s">
         <v>216</v>
@@ -17288,7 +18579,7 @@
         <v>250</v>
       </c>
       <c r="B75" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C75" s="135" t="s">
         <v>216</v>
@@ -17302,7 +18593,7 @@
         <v>251</v>
       </c>
       <c r="B76" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="135" t="s">
         <v>216</v>
@@ -17316,7 +18607,7 @@
         <v>255</v>
       </c>
       <c r="B77" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C77" s="135" t="s">
         <v>216</v>
@@ -17330,7 +18621,7 @@
         <v>256</v>
       </c>
       <c r="B78" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C78" s="135" t="s">
         <v>216</v>
@@ -17344,7 +18635,7 @@
         <v>260</v>
       </c>
       <c r="B79" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C79" s="135" t="s">
         <v>216</v>
@@ -17366,15 +18657,16 @@
       <formula1>Element_ID</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B16:B1048576" xr:uid="{E3D690A9-3459-485B-9D38-6E5066FAA865}">
-      <formula1>LC_Type</formula1>
+      <formula1>Basic_Load_Case_Name</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10204173-8D21-44EB-9119-A6BC046B304C}">
+  <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:F135"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17394,8 +18686,8 @@
       <c r="F1" s="128"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="203" t="s">
-        <v>330</v>
+      <c r="A2" s="202" t="s">
+        <v>325</v>
       </c>
       <c r="B2" s="130"/>
       <c r="C2" s="130"/>
@@ -17404,8 +18696,8 @@
       <c r="F2" s="131"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="203" t="s">
-        <v>331</v>
+      <c r="A3" s="202" t="s">
+        <v>326</v>
       </c>
       <c r="B3" s="130"/>
       <c r="C3" s="130"/>
@@ -17414,8 +18706,8 @@
       <c r="F3" s="131"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="203" t="s">
-        <v>332</v>
+      <c r="A4" s="202" t="s">
+        <v>327</v>
       </c>
       <c r="B4" s="130"/>
       <c r="C4" s="130"/>
@@ -17442,7 +18734,7 @@
     </row>
     <row r="7" spans="1:6" s="120" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="125" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B7" s="125" t="s">
         <v>215</v>
@@ -17459,7 +18751,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C8" s="135" t="s">
         <v>216</v>
@@ -17473,7 +18765,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C9" s="135" t="s">
         <v>216</v>
@@ -17487,7 +18779,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C10" s="135" t="s">
         <v>216</v>
@@ -17501,7 +18793,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C11" s="135" t="s">
         <v>216</v>
@@ -17515,7 +18807,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C12" s="135" t="s">
         <v>216</v>
@@ -17529,7 +18821,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C13" s="135" t="s">
         <v>216</v>
@@ -17543,7 +18835,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C14" s="135" t="s">
         <v>216</v>
@@ -17557,7 +18849,7 @@
         <v>8</v>
       </c>
       <c r="B15" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C15" s="135" t="s">
         <v>216</v>
@@ -17571,7 +18863,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C16" s="135" t="s">
         <v>216</v>
@@ -17585,7 +18877,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C17" s="135" t="s">
         <v>216</v>
@@ -17599,7 +18891,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C18" s="135" t="s">
         <v>216</v>
@@ -17613,7 +18905,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C19" s="135" t="s">
         <v>216</v>
@@ -17627,7 +18919,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C20" s="135" t="s">
         <v>216</v>
@@ -17641,7 +18933,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C21" s="135" t="s">
         <v>216</v>
@@ -17655,7 +18947,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C22" s="135" t="s">
         <v>216</v>
@@ -17669,7 +18961,7 @@
         <v>16</v>
       </c>
       <c r="B23" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C23" s="135" t="s">
         <v>216</v>
@@ -17683,7 +18975,7 @@
         <v>17</v>
       </c>
       <c r="B24" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C24" s="135" t="s">
         <v>216</v>
@@ -17697,7 +18989,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C25" s="135" t="s">
         <v>216</v>
@@ -17711,7 +19003,7 @@
         <v>19</v>
       </c>
       <c r="B26" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C26" s="135" t="s">
         <v>216</v>
@@ -17725,7 +19017,7 @@
         <v>20</v>
       </c>
       <c r="B27" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C27" s="135" t="s">
         <v>216</v>
@@ -17739,7 +19031,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C28" s="135" t="s">
         <v>216</v>
@@ -17753,7 +19045,7 @@
         <v>22</v>
       </c>
       <c r="B29" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C29" s="135" t="s">
         <v>216</v>
@@ -17767,7 +19059,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C30" s="135" t="s">
         <v>216</v>
@@ -17781,7 +19073,7 @@
         <v>24</v>
       </c>
       <c r="B31" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C31" s="135" t="s">
         <v>216</v>
@@ -17795,7 +19087,7 @@
         <v>25</v>
       </c>
       <c r="B32" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C32" s="135" t="s">
         <v>216</v>
@@ -17809,7 +19101,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C33" s="135" t="s">
         <v>216</v>
@@ -17823,7 +19115,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C34" s="135" t="s">
         <v>216</v>
@@ -17837,7 +19129,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C35" s="135" t="s">
         <v>216</v>
@@ -17851,7 +19143,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C36" s="135" t="s">
         <v>216</v>
@@ -17865,7 +19157,7 @@
         <v>30</v>
       </c>
       <c r="B37" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C37" s="135" t="s">
         <v>216</v>
@@ -17879,7 +19171,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C38" s="135" t="s">
         <v>216</v>
@@ -17893,7 +19185,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C39" s="135" t="s">
         <v>216</v>
@@ -17907,7 +19199,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C40" s="135" t="s">
         <v>216</v>
@@ -17921,7 +19213,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C41" s="135" t="s">
         <v>216</v>
@@ -17935,7 +19227,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C42" s="135" t="s">
         <v>216</v>
@@ -17949,7 +19241,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C43" s="135" t="s">
         <v>216</v>
@@ -17963,7 +19255,7 @@
         <v>37</v>
       </c>
       <c r="B44" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C44" s="135" t="s">
         <v>216</v>
@@ -17977,7 +19269,7 @@
         <v>38</v>
       </c>
       <c r="B45" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C45" s="135" t="s">
         <v>216</v>
@@ -17991,7 +19283,7 @@
         <v>39</v>
       </c>
       <c r="B46" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C46" s="135" t="s">
         <v>216</v>
@@ -18005,7 +19297,7 @@
         <v>40</v>
       </c>
       <c r="B47" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C47" s="135" t="s">
         <v>216</v>
@@ -18019,7 +19311,7 @@
         <v>41</v>
       </c>
       <c r="B48" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C48" s="135" t="s">
         <v>216</v>
@@ -18033,7 +19325,7 @@
         <v>42</v>
       </c>
       <c r="B49" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C49" s="135" t="s">
         <v>216</v>
@@ -18047,7 +19339,7 @@
         <v>43</v>
       </c>
       <c r="B50" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C50" s="135" t="s">
         <v>216</v>
@@ -18061,7 +19353,7 @@
         <v>44</v>
       </c>
       <c r="B51" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C51" s="135" t="s">
         <v>216</v>
@@ -18075,7 +19367,7 @@
         <v>45</v>
       </c>
       <c r="B52" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C52" s="135" t="s">
         <v>216</v>
@@ -18089,7 +19381,7 @@
         <v>46</v>
       </c>
       <c r="B53" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C53" s="135" t="s">
         <v>216</v>
@@ -18103,7 +19395,7 @@
         <v>47</v>
       </c>
       <c r="B54" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C54" s="135" t="s">
         <v>216</v>
@@ -18117,7 +19409,7 @@
         <v>48</v>
       </c>
       <c r="B55" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C55" s="135" t="s">
         <v>216</v>
@@ -18131,7 +19423,7 @@
         <v>49</v>
       </c>
       <c r="B56" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C56" s="135" t="s">
         <v>216</v>
@@ -18145,7 +19437,7 @@
         <v>50</v>
       </c>
       <c r="B57" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C57" s="135" t="s">
         <v>216</v>
@@ -18159,7 +19451,7 @@
         <v>51</v>
       </c>
       <c r="B58" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C58" s="135" t="s">
         <v>216</v>
@@ -18173,7 +19465,7 @@
         <v>52</v>
       </c>
       <c r="B59" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C59" s="135" t="s">
         <v>216</v>
@@ -18187,7 +19479,7 @@
         <v>53</v>
       </c>
       <c r="B60" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C60" s="135" t="s">
         <v>216</v>
@@ -18201,7 +19493,7 @@
         <v>54</v>
       </c>
       <c r="B61" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C61" s="135" t="s">
         <v>216</v>
@@ -18215,7 +19507,7 @@
         <v>55</v>
       </c>
       <c r="B62" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C62" s="135" t="s">
         <v>216</v>
@@ -18229,7 +19521,7 @@
         <v>56</v>
       </c>
       <c r="B63" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C63" s="135" t="s">
         <v>216</v>
@@ -18243,7 +19535,7 @@
         <v>57</v>
       </c>
       <c r="B64" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C64" s="135" t="s">
         <v>216</v>
@@ -18257,7 +19549,7 @@
         <v>58</v>
       </c>
       <c r="B65" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C65" s="135" t="s">
         <v>216</v>
@@ -18271,7 +19563,7 @@
         <v>59</v>
       </c>
       <c r="B66" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C66" s="135" t="s">
         <v>216</v>
@@ -18285,7 +19577,7 @@
         <v>60</v>
       </c>
       <c r="B67" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C67" s="135" t="s">
         <v>216</v>
@@ -18299,7 +19591,7 @@
         <v>61</v>
       </c>
       <c r="B68" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C68" s="135" t="s">
         <v>216</v>
@@ -18313,7 +19605,7 @@
         <v>62</v>
       </c>
       <c r="B69" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="135" t="s">
         <v>216</v>
@@ -18327,7 +19619,7 @@
         <v>63</v>
       </c>
       <c r="B70" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C70" s="135" t="s">
         <v>216</v>
@@ -18341,7 +19633,7 @@
         <v>64</v>
       </c>
       <c r="B71" s="135" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C71" s="135" t="s">
         <v>216</v>
@@ -18355,7 +19647,7 @@
         <v>1</v>
       </c>
       <c r="B72" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C72" s="135" t="s">
         <v>216</v>
@@ -18369,7 +19661,7 @@
         <v>2</v>
       </c>
       <c r="B73" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C73" s="135" t="s">
         <v>216</v>
@@ -18383,7 +19675,7 @@
         <v>3</v>
       </c>
       <c r="B74" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C74" s="135" t="s">
         <v>216</v>
@@ -18397,7 +19689,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C75" s="135" t="s">
         <v>216</v>
@@ -18411,7 +19703,7 @@
         <v>5</v>
       </c>
       <c r="B76" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C76" s="135" t="s">
         <v>216</v>
@@ -18425,7 +19717,7 @@
         <v>6</v>
       </c>
       <c r="B77" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C77" s="135" t="s">
         <v>216</v>
@@ -18439,7 +19731,7 @@
         <v>7</v>
       </c>
       <c r="B78" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C78" s="135" t="s">
         <v>216</v>
@@ -18453,7 +19745,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C79" s="135" t="s">
         <v>216</v>
@@ -18467,7 +19759,7 @@
         <v>9</v>
       </c>
       <c r="B80" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C80" s="135" t="s">
         <v>216</v>
@@ -18481,7 +19773,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C81" s="135" t="s">
         <v>216</v>
@@ -18495,7 +19787,7 @@
         <v>11</v>
       </c>
       <c r="B82" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C82" s="135" t="s">
         <v>216</v>
@@ -18509,7 +19801,7 @@
         <v>12</v>
       </c>
       <c r="B83" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C83" s="135" t="s">
         <v>216</v>
@@ -18523,7 +19815,7 @@
         <v>13</v>
       </c>
       <c r="B84" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C84" s="135" t="s">
         <v>216</v>
@@ -18537,7 +19829,7 @@
         <v>14</v>
       </c>
       <c r="B85" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C85" s="135" t="s">
         <v>216</v>
@@ -18551,7 +19843,7 @@
         <v>15</v>
       </c>
       <c r="B86" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C86" s="135" t="s">
         <v>216</v>
@@ -18565,7 +19857,7 @@
         <v>16</v>
       </c>
       <c r="B87" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="135" t="s">
         <v>216</v>
@@ -18579,7 +19871,7 @@
         <v>17</v>
       </c>
       <c r="B88" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C88" s="135" t="s">
         <v>216</v>
@@ -18593,7 +19885,7 @@
         <v>18</v>
       </c>
       <c r="B89" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C89" s="135" t="s">
         <v>216</v>
@@ -18607,7 +19899,7 @@
         <v>19</v>
       </c>
       <c r="B90" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C90" s="135" t="s">
         <v>216</v>
@@ -18621,7 +19913,7 @@
         <v>20</v>
       </c>
       <c r="B91" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C91" s="135" t="s">
         <v>216</v>
@@ -18635,7 +19927,7 @@
         <v>21</v>
       </c>
       <c r="B92" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C92" s="135" t="s">
         <v>216</v>
@@ -18649,7 +19941,7 @@
         <v>22</v>
       </c>
       <c r="B93" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C93" s="135" t="s">
         <v>216</v>
@@ -18663,7 +19955,7 @@
         <v>23</v>
       </c>
       <c r="B94" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C94" s="135" t="s">
         <v>216</v>
@@ -18677,7 +19969,7 @@
         <v>24</v>
       </c>
       <c r="B95" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C95" s="135" t="s">
         <v>216</v>
@@ -18691,7 +19983,7 @@
         <v>25</v>
       </c>
       <c r="B96" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C96" s="135" t="s">
         <v>216</v>
@@ -18705,7 +19997,7 @@
         <v>26</v>
       </c>
       <c r="B97" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C97" s="135" t="s">
         <v>216</v>
@@ -18719,7 +20011,7 @@
         <v>27</v>
       </c>
       <c r="B98" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C98" s="135" t="s">
         <v>216</v>
@@ -18733,7 +20025,7 @@
         <v>28</v>
       </c>
       <c r="B99" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C99" s="135" t="s">
         <v>216</v>
@@ -18747,7 +20039,7 @@
         <v>29</v>
       </c>
       <c r="B100" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C100" s="135" t="s">
         <v>216</v>
@@ -18761,7 +20053,7 @@
         <v>30</v>
       </c>
       <c r="B101" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C101" s="135" t="s">
         <v>216</v>
@@ -18775,7 +20067,7 @@
         <v>31</v>
       </c>
       <c r="B102" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C102" s="135" t="s">
         <v>216</v>
@@ -18789,7 +20081,7 @@
         <v>32</v>
       </c>
       <c r="B103" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C103" s="135" t="s">
         <v>216</v>
@@ -18803,7 +20095,7 @@
         <v>33</v>
       </c>
       <c r="B104" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C104" s="135" t="s">
         <v>216</v>
@@ -18817,7 +20109,7 @@
         <v>34</v>
       </c>
       <c r="B105" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C105" s="135" t="s">
         <v>216</v>
@@ -18831,7 +20123,7 @@
         <v>35</v>
       </c>
       <c r="B106" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C106" s="135" t="s">
         <v>216</v>
@@ -18845,7 +20137,7 @@
         <v>36</v>
       </c>
       <c r="B107" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C107" s="135" t="s">
         <v>216</v>
@@ -18859,7 +20151,7 @@
         <v>37</v>
       </c>
       <c r="B108" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C108" s="135" t="s">
         <v>216</v>
@@ -18873,7 +20165,7 @@
         <v>38</v>
       </c>
       <c r="B109" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C109" s="135" t="s">
         <v>216</v>
@@ -18887,7 +20179,7 @@
         <v>39</v>
       </c>
       <c r="B110" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C110" s="135" t="s">
         <v>216</v>
@@ -18901,7 +20193,7 @@
         <v>40</v>
       </c>
       <c r="B111" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C111" s="135" t="s">
         <v>216</v>
@@ -18915,7 +20207,7 @@
         <v>41</v>
       </c>
       <c r="B112" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C112" s="135" t="s">
         <v>216</v>
@@ -18929,7 +20221,7 @@
         <v>42</v>
       </c>
       <c r="B113" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C113" s="135" t="s">
         <v>216</v>
@@ -18943,7 +20235,7 @@
         <v>43</v>
       </c>
       <c r="B114" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C114" s="135" t="s">
         <v>216</v>
@@ -18957,7 +20249,7 @@
         <v>44</v>
       </c>
       <c r="B115" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C115" s="135" t="s">
         <v>216</v>
@@ -18971,7 +20263,7 @@
         <v>45</v>
       </c>
       <c r="B116" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C116" s="135" t="s">
         <v>216</v>
@@ -18985,7 +20277,7 @@
         <v>46</v>
       </c>
       <c r="B117" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C117" s="135" t="s">
         <v>216</v>
@@ -18999,7 +20291,7 @@
         <v>47</v>
       </c>
       <c r="B118" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C118" s="135" t="s">
         <v>216</v>
@@ -19013,7 +20305,7 @@
         <v>48</v>
       </c>
       <c r="B119" s="135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C119" s="135" t="s">
         <v>216</v>
@@ -19249,7 +20541,7 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="B8:B1048576" xr:uid="{1512AF2D-8ABF-408B-A5A3-341A7F908033}">
-      <formula1>LC_Type</formula1>
+      <formula1>Basic_Load_Case_Name</formula1>
     </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Input" error="Choose from the list" sqref="A8:A1048576" xr:uid="{0FB351FE-4722-4B30-B2C7-F77C6F4CB4C8}">
       <formula1>Shell_ID</formula1>
@@ -19269,7 +20561,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC83A73-50DB-4818-AD57-9D1D23C8BA8A}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="30.7109375" style="98" customWidth="1"/>
@@ -19277,17 +20569,19 @@
     <col min="8" max="13" width="20.7109375" style="78" customWidth="1"/>
     <col min="14" max="19" width="20.7109375" style="49" customWidth="1"/>
     <col min="20" max="21" width="20.7109375" style="78" customWidth="1"/>
-    <col min="22" max="22" width="15.7109375" style="49" customWidth="1"/>
-    <col min="23" max="28" width="10.7109375" style="49" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="49"/>
+    <col min="22" max="23" width="15.7109375" style="78" customWidth="1"/>
+    <col min="24" max="24" width="25.7109375" style="78" customWidth="1"/>
+    <col min="25" max="29" width="15.7109375" style="78" customWidth="1"/>
+    <col min="30" max="35" width="10.7109375" style="49" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="98" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" s="98" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="122" t="s">
         <v>171</v>
       </c>
       <c r="B1" s="122" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C1" s="122" t="s">
         <v>8</v>
@@ -19302,7 +20596,7 @@
         <v>234</v>
       </c>
       <c r="G1" s="122" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="H1" s="122" t="s">
         <v>280</v>
@@ -19347,48 +20641,69 @@
         <v>21</v>
       </c>
       <c r="V1" s="122" t="s">
+        <v>357</v>
+      </c>
+      <c r="W1" s="122" t="s">
+        <v>425</v>
+      </c>
+      <c r="X1" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="122" t="s">
+      <c r="Y1" s="122" t="s">
+        <v>378</v>
+      </c>
+      <c r="Z1" s="122" t="s">
+        <v>377</v>
+      </c>
+      <c r="AA1" s="122" t="s">
+        <v>376</v>
+      </c>
+      <c r="AB1" s="122" t="s">
+        <v>405</v>
+      </c>
+      <c r="AC1" s="122" t="s">
+        <v>408</v>
+      </c>
+      <c r="AD1" s="122" t="s">
         <v>58</v>
       </c>
-      <c r="X1" s="122" t="s">
+      <c r="AE1" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="Y1" s="122" t="s">
+      <c r="AF1" s="122" t="s">
         <v>60</v>
       </c>
-      <c r="Z1" s="122" t="s">
+      <c r="AG1" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="AA1" s="122" t="s">
+      <c r="AH1" s="122" t="s">
         <v>62</v>
       </c>
-      <c r="AB1" s="122" t="s">
+      <c r="AI1" s="122" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="99" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="245" t="s">
-        <v>358</v>
+      <c r="B2" s="232" t="s">
+        <v>353</v>
       </c>
       <c r="C2" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="139" t="s">
+      <c r="D2" s="229" t="s">
         <v>229</v>
       </c>
-      <c r="E2" s="139" t="s">
+      <c r="E2" s="229" t="s">
         <v>229</v>
       </c>
       <c r="F2" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="G2" s="222" t="s">
-        <v>340</v>
+      <c r="G2" s="221" t="s">
+        <v>335</v>
       </c>
       <c r="H2" s="121" t="e" cm="1" vm="1">
         <f t="array" ref="H2">_xlfn._xlws.FILTER(Materials!A33:A1032,(Materials!B33:B1032="Spring")*(Materials!A33:A1032&lt;&gt;""))</f>
@@ -19443,34 +20758,57 @@
         <f t="array" ref="U2:U3">_xlfn._xlws.FILTER('Frame Sections'!A20:A1019,(('Frame Sections'!C20:C1019="Elastic")+('Frame Sections'!C20:C1019="Fiber")+('Frame Sections'!C20:C1019="Aggregator"))*('Frame Sections'!A20:A1019&lt;&gt;""))</f>
         <v>C1</v>
       </c>
-      <c r="V2" s="212" t="s">
+      <c r="V2" s="263" t="str" cm="1">
+        <f t="array" ref="V2:V7">_xlfn.VSTACK(_xlfn._xlws.FILTER('Load Cases'!A13:A1012,(('Load Cases'!B13:B1012="Linear Static")+('Load Cases'!B13:B1012="Nonlinear Static")+('Load Cases'!B13:B1012="Modal")+('Load Cases'!B13:B1012="Response Spectrum")+('Load Cases'!B13:B1012="Linear Time History")+('Load Cases'!B13:B1012="Nonlinear Time History"))*('Load Cases'!A13:A1012&lt;&gt;"")))</f>
+        <v>Self Weight</v>
+      </c>
+      <c r="W2" s="263" t="str" cm="1">
+        <f t="array" ref="W2:W5">_xlfn._xlws.FILTER('Load Cases'!A13:A1012,(('Load Cases'!B13:B1012="Linear Static")+('Load Cases'!B13:B1012="Nonlinear Static"))*('Load Cases'!A13:A1012&lt;&gt;""))</f>
+        <v>Self Weight</v>
+      </c>
+      <c r="X2" s="262" t="s">
+        <v>358</v>
+      </c>
+      <c r="Y2" s="262" t="s">
+        <v>398</v>
+      </c>
+      <c r="Z2" s="262" t="s">
+        <v>367</v>
+      </c>
+      <c r="AA2" s="263" t="s">
         <v>304</v>
       </c>
-      <c r="W2" s="101" t="s">
+      <c r="AB2" s="262" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC2" s="262" t="s">
+        <v>407</v>
+      </c>
+      <c r="AD2" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="X2" s="101" t="s">
+      <c r="AE2" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="Y2" s="101" t="s">
+      <c r="AF2" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="Z2" s="101" t="s">
+      <c r="AG2" s="101" t="s">
         <v>81</v>
       </c>
-      <c r="AA2" s="101" t="s">
+      <c r="AH2" s="101" t="s">
         <v>89</v>
       </c>
-      <c r="AB2" s="101" t="s">
+      <c r="AI2" s="101" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="B3" s="245" t="s">
-        <v>359</v>
+      <c r="B3" s="232" t="s">
+        <v>354</v>
       </c>
       <c r="C3" s="100" t="s">
         <v>3</v>
@@ -19484,8 +20822,8 @@
       <c r="F3" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="G3" s="222" t="s">
-        <v>341</v>
+      <c r="G3" s="221" t="s">
+        <v>336</v>
       </c>
       <c r="H3" s="121"/>
       <c r="I3" s="121" t="str">
@@ -19515,29 +20853,46 @@
       <c r="U3" s="121" t="str">
         <v>B1</v>
       </c>
-      <c r="V3" s="212" t="s">
+      <c r="V3" s="263" t="str">
+        <v>Modal</v>
+      </c>
+      <c r="W3" s="263" t="str">
+        <v>Dead</v>
+      </c>
+      <c r="X3" s="262" t="s">
+        <v>359</v>
+      </c>
+      <c r="Y3" s="262" t="s">
+        <v>399</v>
+      </c>
+      <c r="Z3" s="263"/>
+      <c r="AA3" s="263" t="s">
         <v>305</v>
       </c>
-      <c r="W3" s="101" t="s">
+      <c r="AB3" s="262" t="s">
+        <v>407</v>
+      </c>
+      <c r="AC3" s="262"/>
+      <c r="AD3" s="101" t="s">
         <v>65</v>
       </c>
-      <c r="X3" s="101" t="s">
+      <c r="AE3" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="Y3" s="101" t="s">
+      <c r="AF3" s="101" t="s">
         <v>77</v>
       </c>
-      <c r="Z3" s="101" t="s">
+      <c r="AG3" s="101" t="s">
         <v>82</v>
       </c>
-      <c r="AA3" s="101" t="s">
+      <c r="AH3" s="101" t="s">
         <v>101</v>
       </c>
-      <c r="AB3" s="101" t="s">
+      <c r="AI3" s="101" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="99" t="s">
         <v>175</v>
       </c>
@@ -19545,17 +20900,17 @@
       <c r="C4" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="139" t="s">
+      <c r="D4" s="229" t="s">
         <v>266</v>
       </c>
-      <c r="E4" s="139" t="s">
+      <c r="E4" s="229" t="s">
         <v>267</v>
       </c>
       <c r="F4" s="139" t="s">
         <v>236</v>
       </c>
-      <c r="G4" s="222" t="s">
-        <v>338</v>
+      <c r="G4" s="221" t="s">
+        <v>333</v>
       </c>
       <c r="H4" s="121"/>
       <c r="I4" s="121"/>
@@ -19570,30 +20925,45 @@
         <v>204</v>
       </c>
       <c r="R4" s="100"/>
-      <c r="S4" s="212" t="s">
+      <c r="S4" s="211" t="s">
         <v>300</v>
       </c>
       <c r="T4" s="121"/>
       <c r="U4" s="121"/>
-      <c r="V4" s="212" t="s">
-        <v>306</v>
-      </c>
-      <c r="W4" s="101" t="s">
+      <c r="V4" s="263" t="str">
+        <v>Dead</v>
+      </c>
+      <c r="W4" s="263" t="str">
+        <v>Live</v>
+      </c>
+      <c r="X4" s="262" t="s">
+        <v>360</v>
+      </c>
+      <c r="Y4" s="262" t="s">
+        <v>400</v>
+      </c>
+      <c r="Z4" s="263"/>
+      <c r="AA4" s="263" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB4" s="263"/>
+      <c r="AC4" s="263"/>
+      <c r="AD4" s="101" t="s">
         <v>66</v>
       </c>
-      <c r="X4" s="101" t="s">
+      <c r="AE4" s="101" t="s">
         <v>73</v>
       </c>
-      <c r="Y4" s="101" t="s">
+      <c r="AF4" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="Z4" s="101" t="s">
+      <c r="AG4" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="102"/>
       <c r="B5" s="102"/>
       <c r="C5" s="139" t="s">
@@ -19602,8 +20972,8 @@
       <c r="D5" s="139"/>
       <c r="E5" s="139"/>
       <c r="F5" s="139"/>
-      <c r="G5" s="222" t="s">
-        <v>342</v>
+      <c r="G5" s="221" t="s">
+        <v>337</v>
       </c>
       <c r="H5" s="121"/>
       <c r="I5" s="121"/>
@@ -19614,44 +20984,59 @@
       <c r="N5" s="100"/>
       <c r="O5" s="100"/>
       <c r="P5" s="100"/>
-      <c r="Q5" s="212" t="s">
+      <c r="Q5" s="211" t="s">
         <v>302</v>
       </c>
       <c r="R5" s="100"/>
-      <c r="S5" s="230" t="s">
-        <v>347</v>
+      <c r="S5" s="229" t="s">
+        <v>342</v>
       </c>
       <c r="T5" s="121"/>
       <c r="U5" s="121"/>
-      <c r="V5" s="212" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" s="101" t="s">
+      <c r="V5" s="262" t="str">
+        <v>Live</v>
+      </c>
+      <c r="W5" s="262" t="str">
+        <v>Live Roof</v>
+      </c>
+      <c r="X5" s="262" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y5" s="262" t="s">
+        <v>401</v>
+      </c>
+      <c r="Z5" s="262"/>
+      <c r="AA5" s="262" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB5" s="262"/>
+      <c r="AC5" s="262"/>
+      <c r="AD5" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="X5" s="101" t="s">
+      <c r="AE5" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="Y5" s="101" t="s">
+      <c r="AF5" s="101" t="s">
         <v>79</v>
       </c>
-      <c r="Z5" s="101" t="s">
+      <c r="AG5" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="AA5" s="100"/>
-      <c r="AB5" s="100"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AH5" s="100"/>
+      <c r="AI5" s="100"/>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="102"/>
       <c r="B6" s="102"/>
-      <c r="C6" s="222" t="s">
+      <c r="C6" s="221" t="s">
         <v>300</v>
       </c>
       <c r="D6" s="100"/>
       <c r="E6" s="100"/>
       <c r="F6" s="100"/>
-      <c r="G6" s="222" t="s">
-        <v>343</v>
+      <c r="G6" s="221" t="s">
+        <v>338</v>
       </c>
       <c r="H6" s="121"/>
       <c r="I6" s="121"/>
@@ -19662,40 +21047,53 @@
       <c r="N6" s="100"/>
       <c r="O6" s="100"/>
       <c r="P6" s="100"/>
-      <c r="Q6" s="212" t="s">
+      <c r="Q6" s="211" t="s">
         <v>303</v>
       </c>
       <c r="R6" s="100"/>
       <c r="S6" s="100"/>
       <c r="T6" s="121"/>
       <c r="U6" s="121"/>
-      <c r="V6" s="212" t="s">
-        <v>307</v>
-      </c>
-      <c r="W6" s="101" t="s">
+      <c r="V6" s="262" t="str">
+        <v>Live Roof</v>
+      </c>
+      <c r="W6" s="262"/>
+      <c r="X6" s="262" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y6" s="262" t="s">
+        <v>402</v>
+      </c>
+      <c r="Z6" s="262"/>
+      <c r="AA6" s="262" t="s">
+        <v>374</v>
+      </c>
+      <c r="AB6" s="262"/>
+      <c r="AC6" s="262"/>
+      <c r="AD6" s="101" t="s">
         <v>68</v>
       </c>
-      <c r="X6" s="101" t="s">
+      <c r="AE6" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="Y6" s="101" t="s">
+      <c r="AF6" s="101" t="s">
         <v>80</v>
       </c>
-      <c r="Z6" s="101" t="s">
+      <c r="AG6" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="AA6" s="100"/>
-      <c r="AB6" s="100"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AH6" s="100"/>
+      <c r="AI6" s="100"/>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="102"/>
       <c r="B7" s="102"/>
       <c r="C7" s="100"/>
       <c r="D7" s="100"/>
       <c r="E7" s="100"/>
       <c r="F7" s="100"/>
-      <c r="G7" s="222" t="s">
-        <v>344</v>
+      <c r="G7" s="221" t="s">
+        <v>339</v>
       </c>
       <c r="H7" s="121"/>
       <c r="I7" s="121"/>
@@ -19711,21 +21109,32 @@
       <c r="S7" s="100"/>
       <c r="T7" s="121"/>
       <c r="U7" s="121"/>
-      <c r="V7" s="212" t="s">
-        <v>308</v>
-      </c>
-      <c r="W7" s="101" t="s">
+      <c r="V7" s="262" t="str">
+        <v>RespX</v>
+      </c>
+      <c r="W7" s="262"/>
+      <c r="X7" s="262" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y7" s="262" t="s">
+        <v>403</v>
+      </c>
+      <c r="Z7" s="262"/>
+      <c r="AA7" s="262"/>
+      <c r="AB7" s="262"/>
+      <c r="AC7" s="262"/>
+      <c r="AD7" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="X7" s="100"/>
-      <c r="Y7" s="100"/>
-      <c r="Z7" s="101" t="s">
+      <c r="AE7" s="100"/>
+      <c r="AF7" s="100"/>
+      <c r="AG7" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="AA7" s="100"/>
-      <c r="AB7" s="100"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AH7" s="100"/>
+      <c r="AI7" s="100"/>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="102"/>
       <c r="B8" s="102"/>
       <c r="C8" s="100"/>
@@ -19747,21 +21156,26 @@
       <c r="S8" s="100"/>
       <c r="T8" s="121"/>
       <c r="U8" s="121"/>
-      <c r="V8" s="212" t="s">
-        <v>309</v>
-      </c>
-      <c r="W8" s="101" t="s">
+      <c r="V8" s="262"/>
+      <c r="W8" s="262"/>
+      <c r="X8" s="263"/>
+      <c r="Y8" s="262"/>
+      <c r="Z8" s="262"/>
+      <c r="AA8" s="262"/>
+      <c r="AB8" s="262"/>
+      <c r="AC8" s="262"/>
+      <c r="AD8" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="X8" s="100"/>
-      <c r="Y8" s="100"/>
-      <c r="Z8" s="101" t="s">
+      <c r="AE8" s="100"/>
+      <c r="AF8" s="100"/>
+      <c r="AG8" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="AA8" s="100"/>
-      <c r="AB8" s="100"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AH8" s="100"/>
+      <c r="AI8" s="100"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A9" s="102"/>
       <c r="B9" s="102"/>
       <c r="C9" s="100"/>
@@ -19783,17 +21197,25 @@
       <c r="S9" s="100"/>
       <c r="T9" s="121"/>
       <c r="U9" s="121"/>
-      <c r="V9" s="212" t="s">
-        <v>310</v>
-      </c>
-      <c r="W9" s="100"/>
-      <c r="X9" s="100"/>
-      <c r="Y9" s="100"/>
-      <c r="Z9" s="101" t="s">
+      <c r="V9" s="262"/>
+      <c r="W9" s="262"/>
+      <c r="X9" s="263"/>
+      <c r="Y9" s="262"/>
+      <c r="Z9" s="262"/>
+      <c r="AA9" s="262"/>
+      <c r="AB9" s="262"/>
+      <c r="AC9" s="262"/>
+      <c r="AD9" s="100"/>
+      <c r="AE9" s="100"/>
+      <c r="AF9" s="100"/>
+      <c r="AG9" s="101" t="s">
         <v>88</v>
       </c>
-      <c r="AA9" s="100"/>
-      <c r="AB9" s="100"/>
+      <c r="AH9" s="100"/>
+      <c r="AI9" s="100"/>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="Y10" s="262"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19803,6 +21225,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB248C0-32DF-4CB7-98B5-97665BDFC2C3}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20140,8 +21563,8 @@
       <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="247" t="s">
-        <v>361</v>
+      <c r="A4" s="234" t="s">
+        <v>356</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
@@ -20173,11 +21596,11 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="244" t="s">
-        <v>360</v>
-      </c>
-      <c r="B9" s="246" t="s">
-        <v>358</v>
+      <c r="A9" s="231" t="s">
+        <v>355</v>
+      </c>
+      <c r="B9" s="233" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -20276,17 +21699,17 @@
       <c r="X2" s="142"/>
       <c r="Y2" s="142"/>
       <c r="Z2" s="142"/>
-      <c r="AA2" s="226" t="str">
+      <c r="AA2" s="225" t="str">
         <f>"- EA: Axial rigidity of material aggregator (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
         <v>- EA: Axial rigidity of material aggregator (Input as Float) (kN)</v>
       </c>
-      <c r="AB2" s="224"/>
-      <c r="AC2" s="224"/>
-      <c r="AD2" s="224"/>
-      <c r="AE2" s="224"/>
-      <c r="AF2" s="224"/>
-      <c r="AG2" s="224"/>
-      <c r="AH2" s="225"/>
+      <c r="AB2" s="223"/>
+      <c r="AC2" s="223"/>
+      <c r="AD2" s="223"/>
+      <c r="AE2" s="223"/>
+      <c r="AF2" s="223"/>
+      <c r="AG2" s="223"/>
+      <c r="AH2" s="224"/>
       <c r="AI2" s="169"/>
       <c r="AJ2" s="169"/>
       <c r="AK2" s="169"/>
@@ -20326,17 +21749,17 @@
       <c r="X3" s="161"/>
       <c r="Y3" s="161"/>
       <c r="Z3" s="161"/>
-      <c r="AA3" s="226" t="str">
+      <c r="AA3" s="225" t="str">
         <f>"- EIz: Flexural rigidity of material aggregator about local z-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"-"&amp;'User Defined Units'!$B$11&amp;"2)"</f>
         <v>- EIz: Flexural rigidity of material aggregator about local z-axis (Input as Float) (kN-m2)</v>
       </c>
-      <c r="AB3" s="224"/>
-      <c r="AC3" s="224"/>
-      <c r="AD3" s="224"/>
-      <c r="AE3" s="224"/>
-      <c r="AF3" s="224"/>
-      <c r="AG3" s="224"/>
-      <c r="AH3" s="225"/>
+      <c r="AB3" s="223"/>
+      <c r="AC3" s="223"/>
+      <c r="AD3" s="223"/>
+      <c r="AE3" s="223"/>
+      <c r="AF3" s="223"/>
+      <c r="AG3" s="223"/>
+      <c r="AH3" s="224"/>
       <c r="AI3" s="169"/>
       <c r="AJ3" s="169"/>
       <c r="AK3" s="169"/>
@@ -20376,17 +21799,17 @@
       <c r="X4" s="161"/>
       <c r="Y4" s="161"/>
       <c r="Z4" s="161"/>
-      <c r="AA4" s="226" t="str">
+      <c r="AA4" s="225" t="str">
         <f>"- GAvy: Shear rigidity of material aggregator along local y-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
         <v>- GAvy: Shear rigidity of material aggregator along local y-axis (Input as Float) (kN)</v>
       </c>
-      <c r="AB4" s="224"/>
-      <c r="AC4" s="224"/>
-      <c r="AD4" s="224"/>
-      <c r="AE4" s="224"/>
-      <c r="AF4" s="224"/>
-      <c r="AG4" s="224"/>
-      <c r="AH4" s="225"/>
+      <c r="AB4" s="223"/>
+      <c r="AC4" s="223"/>
+      <c r="AD4" s="223"/>
+      <c r="AE4" s="223"/>
+      <c r="AF4" s="223"/>
+      <c r="AG4" s="223"/>
+      <c r="AH4" s="224"/>
       <c r="AI4" s="169"/>
       <c r="AJ4" s="169"/>
       <c r="AK4" s="169"/>
@@ -20428,17 +21851,17 @@
       <c r="X5" s="142"/>
       <c r="Y5" s="142"/>
       <c r="Z5" s="142"/>
-      <c r="AA5" s="226" t="str">
+      <c r="AA5" s="225" t="str">
         <f>"- EIy: Flexural rigidity of material aggregator about local y-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"-"&amp;'User Defined Units'!$B$11&amp;"2)"</f>
         <v>- EIy: Flexural rigidity of material aggregator about local y-axis (Input as Float) (kN-m2)</v>
       </c>
-      <c r="AB5" s="224"/>
-      <c r="AC5" s="224"/>
-      <c r="AD5" s="224"/>
-      <c r="AE5" s="224"/>
-      <c r="AF5" s="224"/>
-      <c r="AG5" s="224"/>
-      <c r="AH5" s="225"/>
+      <c r="AB5" s="223"/>
+      <c r="AC5" s="223"/>
+      <c r="AD5" s="223"/>
+      <c r="AE5" s="223"/>
+      <c r="AF5" s="223"/>
+      <c r="AG5" s="223"/>
+      <c r="AH5" s="224"/>
       <c r="AI5" s="170"/>
       <c r="AJ5" s="170"/>
       <c r="AK5" s="170"/>
@@ -20480,17 +21903,17 @@
       <c r="X6" s="142"/>
       <c r="Y6" s="142"/>
       <c r="Z6" s="142"/>
-      <c r="AA6" s="226" t="str">
+      <c r="AA6" s="225" t="str">
         <f>"- GAvz: Shear rigidity of material aggregator along local z-axis (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;")"</f>
         <v>- GAvz: Shear rigidity of material aggregator along local z-axis (Input as Float) (kN)</v>
       </c>
-      <c r="AB6" s="224"/>
-      <c r="AC6" s="224"/>
-      <c r="AD6" s="224"/>
-      <c r="AE6" s="224"/>
-      <c r="AF6" s="224"/>
-      <c r="AG6" s="224"/>
-      <c r="AH6" s="225"/>
+      <c r="AB6" s="223"/>
+      <c r="AC6" s="223"/>
+      <c r="AD6" s="223"/>
+      <c r="AE6" s="223"/>
+      <c r="AF6" s="223"/>
+      <c r="AG6" s="223"/>
+      <c r="AH6" s="224"/>
       <c r="AI6" s="170"/>
       <c r="AJ6" s="170"/>
       <c r="AK6" s="170"/>
@@ -20531,17 +21954,17 @@
       <c r="X7" s="142"/>
       <c r="Y7" s="142"/>
       <c r="Z7" s="142"/>
-      <c r="AA7" s="226" t="str">
+      <c r="AA7" s="225" t="str">
         <f>"- GJxx: Torsional rigidity of material aggregator (Input as Float) ("&amp;'User Defined Units'!$B$10&amp;"-"&amp;'User Defined Units'!$B$11&amp;"2)"</f>
         <v>- GJxx: Torsional rigidity of material aggregator (Input as Float) (kN-m2)</v>
       </c>
-      <c r="AB7" s="227"/>
-      <c r="AC7" s="227"/>
-      <c r="AD7" s="227"/>
-      <c r="AE7" s="227"/>
-      <c r="AF7" s="227"/>
-      <c r="AG7" s="227"/>
-      <c r="AH7" s="228"/>
+      <c r="AB7" s="226"/>
+      <c r="AC7" s="226"/>
+      <c r="AD7" s="226"/>
+      <c r="AE7" s="226"/>
+      <c r="AF7" s="226"/>
+      <c r="AG7" s="226"/>
+      <c r="AH7" s="227"/>
       <c r="AI7" s="170"/>
       <c r="AJ7" s="170"/>
       <c r="AK7" s="170"/>
@@ -20583,14 +22006,16 @@
       <c r="X8" s="142"/>
       <c r="Y8" s="142"/>
       <c r="Z8" s="142"/>
-      <c r="AA8" s="226"/>
-      <c r="AB8" s="224"/>
-      <c r="AC8" s="224"/>
-      <c r="AD8" s="224"/>
-      <c r="AE8" s="224"/>
-      <c r="AF8" s="224"/>
-      <c r="AG8" s="224"/>
-      <c r="AH8" s="225"/>
+      <c r="AA8" s="275" t="s">
+        <v>422</v>
+      </c>
+      <c r="AB8" s="223"/>
+      <c r="AC8" s="223"/>
+      <c r="AD8" s="223"/>
+      <c r="AE8" s="223"/>
+      <c r="AF8" s="223"/>
+      <c r="AG8" s="223"/>
+      <c r="AH8" s="224"/>
       <c r="AI8" s="170"/>
       <c r="AJ8" s="170"/>
       <c r="AK8" s="170"/>
@@ -20630,16 +22055,16 @@
       <c r="X9" s="142"/>
       <c r="Y9" s="142"/>
       <c r="Z9" s="142"/>
-      <c r="AA9" s="231" t="s">
+      <c r="AA9" s="235" t="s">
         <v>273</v>
       </c>
-      <c r="AB9" s="232"/>
-      <c r="AC9" s="232"/>
-      <c r="AD9" s="232"/>
-      <c r="AE9" s="232"/>
-      <c r="AF9" s="232"/>
-      <c r="AG9" s="232"/>
-      <c r="AH9" s="233"/>
+      <c r="AB9" s="236"/>
+      <c r="AC9" s="236"/>
+      <c r="AD9" s="236"/>
+      <c r="AE9" s="236"/>
+      <c r="AF9" s="236"/>
+      <c r="AG9" s="236"/>
+      <c r="AH9" s="237"/>
       <c r="AI9" s="171"/>
       <c r="AJ9" s="171"/>
       <c r="AK9" s="171"/>
@@ -20679,16 +22104,16 @@
       <c r="X10" s="142"/>
       <c r="Y10" s="142"/>
       <c r="Z10" s="142"/>
-      <c r="AA10" s="234" t="s">
+      <c r="AA10" s="238" t="s">
         <v>272</v>
       </c>
-      <c r="AB10" s="235"/>
-      <c r="AC10" s="235"/>
-      <c r="AD10" s="235"/>
-      <c r="AE10" s="235"/>
-      <c r="AF10" s="235"/>
-      <c r="AG10" s="235"/>
-      <c r="AH10" s="236"/>
+      <c r="AB10" s="239"/>
+      <c r="AC10" s="239"/>
+      <c r="AD10" s="239"/>
+      <c r="AE10" s="239"/>
+      <c r="AF10" s="239"/>
+      <c r="AG10" s="239"/>
+      <c r="AH10" s="240"/>
       <c r="AI10" s="171"/>
       <c r="AJ10" s="171"/>
       <c r="AK10" s="171"/>
@@ -20729,16 +22154,16 @@
       <c r="X11" s="142"/>
       <c r="Y11" s="142"/>
       <c r="Z11" s="142"/>
-      <c r="AA11" s="234" t="s">
+      <c r="AA11" s="238" t="s">
         <v>271</v>
       </c>
-      <c r="AB11" s="235"/>
-      <c r="AC11" s="235"/>
-      <c r="AD11" s="235"/>
-      <c r="AE11" s="235"/>
-      <c r="AF11" s="235"/>
-      <c r="AG11" s="235"/>
-      <c r="AH11" s="236"/>
+      <c r="AB11" s="239"/>
+      <c r="AC11" s="239"/>
+      <c r="AD11" s="239"/>
+      <c r="AE11" s="239"/>
+      <c r="AF11" s="239"/>
+      <c r="AG11" s="239"/>
+      <c r="AH11" s="240"/>
       <c r="AI11" s="171"/>
       <c r="AJ11" s="171"/>
       <c r="AK11" s="171"/>
@@ -20778,16 +22203,16 @@
       <c r="X12" s="142"/>
       <c r="Y12" s="142"/>
       <c r="Z12" s="142"/>
-      <c r="AA12" s="234" t="s">
+      <c r="AA12" s="238" t="s">
         <v>270</v>
       </c>
-      <c r="AB12" s="235"/>
-      <c r="AC12" s="235"/>
-      <c r="AD12" s="235"/>
-      <c r="AE12" s="235"/>
-      <c r="AF12" s="235"/>
-      <c r="AG12" s="235"/>
-      <c r="AH12" s="236"/>
+      <c r="AB12" s="239"/>
+      <c r="AC12" s="239"/>
+      <c r="AD12" s="239"/>
+      <c r="AE12" s="239"/>
+      <c r="AF12" s="239"/>
+      <c r="AG12" s="239"/>
+      <c r="AH12" s="240"/>
       <c r="AI12" s="171"/>
       <c r="AJ12" s="171"/>
       <c r="AK12" s="171"/>
@@ -20827,16 +22252,16 @@
       <c r="X13" s="142"/>
       <c r="Y13" s="142"/>
       <c r="Z13" s="142"/>
-      <c r="AA13" s="234" t="s">
+      <c r="AA13" s="238" t="s">
         <v>269</v>
       </c>
-      <c r="AB13" s="235"/>
-      <c r="AC13" s="235"/>
-      <c r="AD13" s="235"/>
-      <c r="AE13" s="235"/>
-      <c r="AF13" s="235"/>
-      <c r="AG13" s="235"/>
-      <c r="AH13" s="236"/>
+      <c r="AB13" s="239"/>
+      <c r="AC13" s="239"/>
+      <c r="AD13" s="239"/>
+      <c r="AE13" s="239"/>
+      <c r="AF13" s="239"/>
+      <c r="AG13" s="239"/>
+      <c r="AH13" s="240"/>
       <c r="AI13" s="170"/>
       <c r="AJ13" s="170"/>
       <c r="AK13" s="170"/>
@@ -20877,16 +22302,16 @@
       <c r="X14" s="142"/>
       <c r="Y14" s="142"/>
       <c r="Z14" s="142"/>
-      <c r="AA14" s="234" t="s">
+      <c r="AA14" s="238" t="s">
         <v>268</v>
       </c>
-      <c r="AB14" s="235"/>
-      <c r="AC14" s="235"/>
-      <c r="AD14" s="235"/>
-      <c r="AE14" s="235"/>
-      <c r="AF14" s="235"/>
-      <c r="AG14" s="235"/>
-      <c r="AH14" s="236"/>
+      <c r="AB14" s="239"/>
+      <c r="AC14" s="239"/>
+      <c r="AD14" s="239"/>
+      <c r="AE14" s="239"/>
+      <c r="AF14" s="239"/>
+      <c r="AG14" s="239"/>
+      <c r="AH14" s="240"/>
       <c r="AI14" s="170"/>
       <c r="AJ14" s="170"/>
       <c r="AK14" s="170"/>
@@ -20927,14 +22352,14 @@
       <c r="X15" s="142"/>
       <c r="Y15" s="142"/>
       <c r="Z15" s="142"/>
-      <c r="AA15" s="234"/>
-      <c r="AB15" s="235"/>
-      <c r="AC15" s="235"/>
-      <c r="AD15" s="235"/>
-      <c r="AE15" s="235"/>
-      <c r="AF15" s="235"/>
-      <c r="AG15" s="235"/>
-      <c r="AH15" s="236"/>
+      <c r="AA15" s="238"/>
+      <c r="AB15" s="239"/>
+      <c r="AC15" s="239"/>
+      <c r="AD15" s="239"/>
+      <c r="AE15" s="239"/>
+      <c r="AF15" s="239"/>
+      <c r="AG15" s="239"/>
+      <c r="AH15" s="240"/>
       <c r="AI15" s="170"/>
       <c r="AJ15" s="170"/>
       <c r="AK15" s="170"/>
@@ -20974,16 +22399,16 @@
       <c r="X16" s="142"/>
       <c r="Y16" s="142"/>
       <c r="Z16" s="142"/>
-      <c r="AA16" s="234" t="s">
+      <c r="AA16" s="238" t="s">
         <v>274</v>
       </c>
-      <c r="AB16" s="235"/>
-      <c r="AC16" s="235"/>
-      <c r="AD16" s="235"/>
-      <c r="AE16" s="235"/>
-      <c r="AF16" s="235"/>
-      <c r="AG16" s="235"/>
-      <c r="AH16" s="236"/>
+      <c r="AB16" s="239"/>
+      <c r="AC16" s="239"/>
+      <c r="AD16" s="239"/>
+      <c r="AE16" s="239"/>
+      <c r="AF16" s="239"/>
+      <c r="AG16" s="239"/>
+      <c r="AH16" s="240"/>
       <c r="AI16" s="170"/>
       <c r="AJ16" s="170"/>
       <c r="AK16" s="170"/>
@@ -21023,14 +22448,14 @@
       <c r="X17" s="142"/>
       <c r="Y17" s="142"/>
       <c r="Z17" s="142"/>
-      <c r="AA17" s="234"/>
-      <c r="AB17" s="235"/>
-      <c r="AC17" s="235"/>
-      <c r="AD17" s="235"/>
-      <c r="AE17" s="235"/>
-      <c r="AF17" s="235"/>
-      <c r="AG17" s="235"/>
-      <c r="AH17" s="236"/>
+      <c r="AA17" s="238"/>
+      <c r="AB17" s="239"/>
+      <c r="AC17" s="239"/>
+      <c r="AD17" s="239"/>
+      <c r="AE17" s="239"/>
+      <c r="AF17" s="239"/>
+      <c r="AG17" s="239"/>
+      <c r="AH17" s="240"/>
       <c r="AI17" s="171"/>
       <c r="AJ17" s="171"/>
       <c r="AK17" s="171"/>
@@ -21070,14 +22495,14 @@
       <c r="X18" s="142"/>
       <c r="Y18" s="142"/>
       <c r="Z18" s="142"/>
-      <c r="AA18" s="234"/>
-      <c r="AB18" s="235"/>
-      <c r="AC18" s="235"/>
-      <c r="AD18" s="235"/>
-      <c r="AE18" s="235"/>
-      <c r="AF18" s="235"/>
-      <c r="AG18" s="235"/>
-      <c r="AH18" s="236"/>
+      <c r="AA18" s="238"/>
+      <c r="AB18" s="239"/>
+      <c r="AC18" s="239"/>
+      <c r="AD18" s="239"/>
+      <c r="AE18" s="239"/>
+      <c r="AF18" s="239"/>
+      <c r="AG18" s="239"/>
+      <c r="AH18" s="240"/>
       <c r="AI18" s="171"/>
       <c r="AJ18" s="171"/>
       <c r="AK18" s="171"/>
@@ -21117,16 +22542,16 @@
       <c r="X19" s="142"/>
       <c r="Y19" s="142"/>
       <c r="Z19" s="142"/>
-      <c r="AA19" s="231" t="s">
+      <c r="AA19" s="235" t="s">
         <v>275</v>
       </c>
-      <c r="AB19" s="232"/>
-      <c r="AC19" s="232"/>
-      <c r="AD19" s="232"/>
-      <c r="AE19" s="232"/>
-      <c r="AF19" s="232"/>
-      <c r="AG19" s="232"/>
-      <c r="AH19" s="233"/>
+      <c r="AB19" s="236"/>
+      <c r="AC19" s="236"/>
+      <c r="AD19" s="236"/>
+      <c r="AE19" s="236"/>
+      <c r="AF19" s="236"/>
+      <c r="AG19" s="236"/>
+      <c r="AH19" s="237"/>
       <c r="AI19" s="171"/>
       <c r="AJ19" s="171"/>
       <c r="AK19" s="171"/>
@@ -21166,14 +22591,14 @@
       <c r="X20" s="142"/>
       <c r="Y20" s="142"/>
       <c r="Z20" s="142"/>
-      <c r="AA20" s="231"/>
-      <c r="AB20" s="232"/>
-      <c r="AC20" s="232"/>
-      <c r="AD20" s="232"/>
-      <c r="AE20" s="232"/>
-      <c r="AF20" s="232"/>
-      <c r="AG20" s="232"/>
-      <c r="AH20" s="233"/>
+      <c r="AA20" s="235"/>
+      <c r="AB20" s="236"/>
+      <c r="AC20" s="236"/>
+      <c r="AD20" s="236"/>
+      <c r="AE20" s="236"/>
+      <c r="AF20" s="236"/>
+      <c r="AG20" s="236"/>
+      <c r="AH20" s="237"/>
       <c r="AI20" s="171"/>
       <c r="AJ20" s="171"/>
       <c r="AK20" s="171"/>
@@ -21213,14 +22638,14 @@
       <c r="X21" s="142"/>
       <c r="Y21" s="142"/>
       <c r="Z21" s="142"/>
-      <c r="AA21" s="231"/>
-      <c r="AB21" s="232"/>
-      <c r="AC21" s="232"/>
-      <c r="AD21" s="232"/>
-      <c r="AE21" s="232"/>
-      <c r="AF21" s="232"/>
-      <c r="AG21" s="232"/>
-      <c r="AH21" s="233"/>
+      <c r="AA21" s="235"/>
+      <c r="AB21" s="236"/>
+      <c r="AC21" s="236"/>
+      <c r="AD21" s="236"/>
+      <c r="AE21" s="236"/>
+      <c r="AF21" s="236"/>
+      <c r="AG21" s="236"/>
+      <c r="AH21" s="237"/>
       <c r="AI21" s="172"/>
       <c r="AJ21" s="172"/>
       <c r="AK21" s="172"/>
@@ -21260,16 +22685,16 @@
       <c r="X22" s="142"/>
       <c r="Y22" s="142"/>
       <c r="Z22" s="142"/>
-      <c r="AA22" s="234" t="s">
+      <c r="AA22" s="238" t="s">
         <v>276</v>
       </c>
-      <c r="AB22" s="235"/>
-      <c r="AC22" s="235"/>
-      <c r="AD22" s="235"/>
-      <c r="AE22" s="235"/>
-      <c r="AF22" s="235"/>
-      <c r="AG22" s="235"/>
-      <c r="AH22" s="236"/>
+      <c r="AB22" s="239"/>
+      <c r="AC22" s="239"/>
+      <c r="AD22" s="239"/>
+      <c r="AE22" s="239"/>
+      <c r="AF22" s="239"/>
+      <c r="AG22" s="239"/>
+      <c r="AH22" s="240"/>
       <c r="AI22" s="146"/>
     </row>
     <row r="23" spans="1:41" x14ac:dyDescent="0.25">
@@ -21303,14 +22728,14 @@
       <c r="X23" s="142"/>
       <c r="Y23" s="142"/>
       <c r="Z23" s="142"/>
-      <c r="AA23" s="234"/>
-      <c r="AB23" s="235"/>
-      <c r="AC23" s="235"/>
-      <c r="AD23" s="235"/>
-      <c r="AE23" s="235"/>
-      <c r="AF23" s="235"/>
-      <c r="AG23" s="235"/>
-      <c r="AH23" s="236"/>
+      <c r="AA23" s="238"/>
+      <c r="AB23" s="239"/>
+      <c r="AC23" s="239"/>
+      <c r="AD23" s="239"/>
+      <c r="AE23" s="239"/>
+      <c r="AF23" s="239"/>
+      <c r="AG23" s="239"/>
+      <c r="AH23" s="240"/>
       <c r="AI23" s="146"/>
     </row>
     <row r="24" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21344,14 +22769,14 @@
       <c r="X24" s="142"/>
       <c r="Y24" s="142"/>
       <c r="Z24" s="142"/>
-      <c r="AA24" s="234"/>
-      <c r="AB24" s="235"/>
-      <c r="AC24" s="235"/>
-      <c r="AD24" s="235"/>
-      <c r="AE24" s="235"/>
-      <c r="AF24" s="235"/>
-      <c r="AG24" s="235"/>
-      <c r="AH24" s="236"/>
+      <c r="AA24" s="238"/>
+      <c r="AB24" s="239"/>
+      <c r="AC24" s="239"/>
+      <c r="AD24" s="239"/>
+      <c r="AE24" s="239"/>
+      <c r="AF24" s="239"/>
+      <c r="AG24" s="239"/>
+      <c r="AH24" s="240"/>
       <c r="AI24" s="146"/>
     </row>
     <row r="25" spans="1:41" x14ac:dyDescent="0.25">
@@ -21386,14 +22811,14 @@
       <c r="X25" s="142"/>
       <c r="Y25" s="142"/>
       <c r="Z25" s="142"/>
-      <c r="AA25" s="234"/>
-      <c r="AB25" s="235"/>
-      <c r="AC25" s="235"/>
-      <c r="AD25" s="235"/>
-      <c r="AE25" s="235"/>
-      <c r="AF25" s="235"/>
-      <c r="AG25" s="235"/>
-      <c r="AH25" s="236"/>
+      <c r="AA25" s="238"/>
+      <c r="AB25" s="239"/>
+      <c r="AC25" s="239"/>
+      <c r="AD25" s="239"/>
+      <c r="AE25" s="239"/>
+      <c r="AF25" s="239"/>
+      <c r="AG25" s="239"/>
+      <c r="AH25" s="240"/>
       <c r="AI25" s="146"/>
     </row>
     <row r="26" spans="1:41" x14ac:dyDescent="0.25">
@@ -21427,16 +22852,16 @@
       <c r="X26" s="142"/>
       <c r="Y26" s="142"/>
       <c r="Z26" s="142"/>
-      <c r="AA26" s="237" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB26" s="238"/>
-      <c r="AC26" s="238"/>
-      <c r="AD26" s="238"/>
-      <c r="AE26" s="238"/>
-      <c r="AF26" s="238"/>
-      <c r="AG26" s="238"/>
-      <c r="AH26" s="239"/>
+      <c r="AA26" s="241" t="s">
+        <v>334</v>
+      </c>
+      <c r="AB26" s="242"/>
+      <c r="AC26" s="242"/>
+      <c r="AD26" s="242"/>
+      <c r="AE26" s="242"/>
+      <c r="AF26" s="242"/>
+      <c r="AG26" s="242"/>
+      <c r="AH26" s="243"/>
       <c r="AI26" s="146"/>
     </row>
     <row r="27" spans="1:41" x14ac:dyDescent="0.25">
@@ -21959,10 +23384,10 @@
       <c r="A38" s="158"/>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A39" s="219"/>
+      <c r="A39" s="218"/>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A40" s="219"/>
+      <c r="A40" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -21978,53 +23403,53 @@
     <mergeCell ref="AA22:AH25"/>
   </mergeCells>
   <conditionalFormatting sqref="D33:F1048576">
-    <cfRule type="expression" dxfId="18" priority="2">
+    <cfRule type="expression" dxfId="20" priority="2">
       <formula>OR($B33="Aggregator")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="6">
+    <cfRule type="expression" dxfId="19" priority="6">
       <formula>OR($B33="Spring")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H33:AH1048576">
-    <cfRule type="expression" dxfId="16" priority="9">
+    <cfRule type="expression" dxfId="18" priority="9">
       <formula>AND($B33="Concrete",$C33="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33:AH1048576">
-    <cfRule type="expression" dxfId="15" priority="8">
+    <cfRule type="expression" dxfId="17" priority="8">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M33:AH1048576">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>AND($B33="Aggregator",$C33="ElasticAggregator")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="20">
+    <cfRule type="expression" dxfId="15" priority="20">
       <formula>AND($B33="Concrete",$C33="Concrete04")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O33:AH1048576">
-    <cfRule type="expression" dxfId="12" priority="11">
+    <cfRule type="expression" dxfId="14" priority="11">
       <formula>AND($B33="Concrete",$C33="Concrete04+MinMax")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S33:AH1048576">
-    <cfRule type="expression" dxfId="11" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Steel02")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U33:AH1048576">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="12" priority="10">
       <formula>AND(OR($B33="Rebar",$B33="Steel"),$C33="Steel02+MinMax")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF33:AH1048576">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="11" priority="4">
       <formula>AND($B33="Spring",$C33="IMKPeakOriented")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG33:AH1048576">
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>AND($B33="Spring",$C33="IMKBilinear")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22085,16 +23510,18 @@
       <c r="R1" s="177"/>
       <c r="S1" s="177"/>
       <c r="T1" s="178"/>
-      <c r="U1" s="177"/>
+      <c r="U1" s="274" t="s">
+        <v>422</v>
+      </c>
       <c r="V1" s="177"/>
-      <c r="W1" s="196"/>
-      <c r="X1" s="196"/>
-      <c r="Y1" s="196"/>
-      <c r="Z1" s="196"/>
-      <c r="AA1" s="196"/>
-      <c r="AB1" s="196"/>
-      <c r="AC1" s="196"/>
-      <c r="AD1" s="197"/>
+      <c r="W1" s="195"/>
+      <c r="X1" s="195"/>
+      <c r="Y1" s="195"/>
+      <c r="Z1" s="195"/>
+      <c r="AA1" s="195"/>
+      <c r="AB1" s="195"/>
+      <c r="AC1" s="195"/>
+      <c r="AD1" s="196"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="180" t="s">
@@ -22108,31 +23535,31 @@
       <c r="G2" s="121"/>
       <c r="H2" s="121"/>
       <c r="I2" s="121"/>
-      <c r="J2" s="205"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="205"/>
-      <c r="M2" s="205"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="204"/>
       <c r="N2" s="182" t="s">
         <v>197</v>
       </c>
-      <c r="O2" s="208"/>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="209"/>
-      <c r="S2" s="208"/>
-      <c r="T2" s="214"/>
-      <c r="U2" s="209" t="s">
+      <c r="O2" s="207"/>
+      <c r="P2" s="207"/>
+      <c r="Q2" s="207"/>
+      <c r="R2" s="208"/>
+      <c r="S2" s="207"/>
+      <c r="T2" s="213"/>
+      <c r="U2" s="208" t="s">
         <v>296</v>
       </c>
-      <c r="V2" s="209"/>
-      <c r="W2" s="210"/>
-      <c r="X2" s="210"/>
-      <c r="Y2" s="210"/>
-      <c r="Z2" s="210"/>
-      <c r="AA2" s="210"/>
-      <c r="AB2" s="210"/>
-      <c r="AC2" s="210"/>
-      <c r="AD2" s="198"/>
+      <c r="V2" s="208"/>
+      <c r="W2" s="209"/>
+      <c r="X2" s="209"/>
+      <c r="Y2" s="209"/>
+      <c r="Z2" s="209"/>
+      <c r="AA2" s="209"/>
+      <c r="AB2" s="209"/>
+      <c r="AC2" s="209"/>
+      <c r="AD2" s="197"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="180" t="s">
@@ -22146,31 +23573,31 @@
       <c r="G3" s="121"/>
       <c r="H3" s="121"/>
       <c r="I3" s="121"/>
-      <c r="J3" s="205"/>
-      <c r="K3" s="205"/>
-      <c r="L3" s="205"/>
-      <c r="M3" s="205"/>
+      <c r="J3" s="204"/>
+      <c r="K3" s="204"/>
+      <c r="L3" s="204"/>
+      <c r="M3" s="204"/>
       <c r="N3" s="182" t="s">
         <v>198</v>
       </c>
-      <c r="O3" s="208"/>
-      <c r="P3" s="208"/>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="209"/>
-      <c r="S3" s="208"/>
-      <c r="T3" s="214"/>
-      <c r="U3" s="209" t="s">
+      <c r="O3" s="207"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="208"/>
+      <c r="S3" s="207"/>
+      <c r="T3" s="213"/>
+      <c r="U3" s="208" t="s">
         <v>295</v>
       </c>
-      <c r="V3" s="209"/>
-      <c r="W3" s="210"/>
-      <c r="X3" s="210"/>
-      <c r="Y3" s="210"/>
-      <c r="Z3" s="210"/>
-      <c r="AA3" s="210"/>
-      <c r="AB3" s="210"/>
-      <c r="AC3" s="210"/>
-      <c r="AD3" s="198"/>
+      <c r="V3" s="208"/>
+      <c r="W3" s="209"/>
+      <c r="X3" s="209"/>
+      <c r="Y3" s="209"/>
+      <c r="Z3" s="209"/>
+      <c r="AA3" s="209"/>
+      <c r="AB3" s="209"/>
+      <c r="AC3" s="209"/>
+      <c r="AD3" s="197"/>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="173" t="s">
@@ -22184,464 +23611,464 @@
       <c r="G4" s="121"/>
       <c r="H4" s="121"/>
       <c r="I4" s="121"/>
-      <c r="J4" s="205"/>
-      <c r="K4" s="205"/>
-      <c r="L4" s="205"/>
-      <c r="M4" s="205"/>
+      <c r="J4" s="204"/>
+      <c r="K4" s="204"/>
+      <c r="L4" s="204"/>
+      <c r="M4" s="204"/>
       <c r="N4" s="182" t="s">
         <v>199</v>
       </c>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="205"/>
-      <c r="S4" s="208"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="204"/>
+      <c r="S4" s="207"/>
       <c r="T4" s="181"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="208"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="210"/>
-      <c r="Y4" s="210"/>
-      <c r="Z4" s="210"/>
-      <c r="AA4" s="210"/>
-      <c r="AB4" s="210"/>
-      <c r="AC4" s="210"/>
-      <c r="AD4" s="198"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="207"/>
+      <c r="W4" s="209"/>
+      <c r="X4" s="209"/>
+      <c r="Y4" s="209"/>
+      <c r="Z4" s="209"/>
+      <c r="AA4" s="209"/>
+      <c r="AB4" s="209"/>
+      <c r="AC4" s="209"/>
+      <c r="AD4" s="197"/>
     </row>
     <row r="5" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="240" t="s">
-        <v>348</v>
-      </c>
-      <c r="B5" s="241"/>
-      <c r="C5" s="241"/>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="218"/>
-      <c r="L5" s="218"/>
-      <c r="M5" s="218"/>
+      <c r="A5" s="244" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="217"/>
+      <c r="M5" s="217"/>
       <c r="N5" s="182" t="s">
         <v>200</v>
       </c>
-      <c r="O5" s="202"/>
-      <c r="P5" s="202"/>
-      <c r="Q5" s="202"/>
-      <c r="R5" s="205"/>
-      <c r="S5" s="208"/>
+      <c r="O5" s="201"/>
+      <c r="P5" s="201"/>
+      <c r="Q5" s="201"/>
+      <c r="R5" s="204"/>
+      <c r="S5" s="207"/>
       <c r="T5" s="181"/>
-      <c r="U5" s="208"/>
-      <c r="V5" s="208"/>
-      <c r="W5" s="210"/>
-      <c r="X5" s="210"/>
-      <c r="Y5" s="210"/>
-      <c r="Z5" s="210"/>
-      <c r="AA5" s="210"/>
-      <c r="AB5" s="210"/>
-      <c r="AC5" s="210"/>
-      <c r="AD5" s="198"/>
+      <c r="U5" s="207"/>
+      <c r="V5" s="207"/>
+      <c r="W5" s="209"/>
+      <c r="X5" s="209"/>
+      <c r="Y5" s="209"/>
+      <c r="Z5" s="209"/>
+      <c r="AA5" s="209"/>
+      <c r="AB5" s="209"/>
+      <c r="AC5" s="209"/>
+      <c r="AD5" s="197"/>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="242"/>
-      <c r="B6" s="241"/>
-      <c r="C6" s="241"/>
-      <c r="D6" s="241"/>
-      <c r="E6" s="241"/>
-      <c r="F6" s="241"/>
-      <c r="G6" s="241"/>
-      <c r="H6" s="241"/>
-      <c r="I6" s="241"/>
-      <c r="J6" s="241"/>
-      <c r="K6" s="218"/>
-      <c r="L6" s="218"/>
-      <c r="M6" s="218"/>
+      <c r="A6" s="246"/>
+      <c r="B6" s="245"/>
+      <c r="C6" s="245"/>
+      <c r="D6" s="245"/>
+      <c r="E6" s="245"/>
+      <c r="F6" s="245"/>
+      <c r="G6" s="245"/>
+      <c r="H6" s="245"/>
+      <c r="I6" s="245"/>
+      <c r="J6" s="245"/>
+      <c r="K6" s="217"/>
+      <c r="L6" s="217"/>
+      <c r="M6" s="217"/>
       <c r="N6" s="182" t="s">
         <v>201</v>
       </c>
-      <c r="O6" s="202"/>
-      <c r="P6" s="202"/>
-      <c r="Q6" s="202"/>
-      <c r="R6" s="205"/>
-      <c r="S6" s="208"/>
+      <c r="O6" s="201"/>
+      <c r="P6" s="201"/>
+      <c r="Q6" s="201"/>
+      <c r="R6" s="204"/>
+      <c r="S6" s="207"/>
       <c r="T6" s="181"/>
-      <c r="U6" s="208"/>
-      <c r="V6" s="208"/>
-      <c r="W6" s="210"/>
-      <c r="X6" s="210"/>
-      <c r="Y6" s="210"/>
-      <c r="Z6" s="210"/>
-      <c r="AA6" s="210"/>
-      <c r="AB6" s="210"/>
-      <c r="AC6" s="210"/>
-      <c r="AD6" s="198"/>
+      <c r="U6" s="207"/>
+      <c r="V6" s="207"/>
+      <c r="W6" s="209"/>
+      <c r="X6" s="209"/>
+      <c r="Y6" s="209"/>
+      <c r="Z6" s="209"/>
+      <c r="AA6" s="209"/>
+      <c r="AB6" s="209"/>
+      <c r="AC6" s="209"/>
+      <c r="AD6" s="197"/>
     </row>
     <row r="7" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="240" t="s">
-        <v>349</v>
-      </c>
-      <c r="B7" s="241"/>
-      <c r="C7" s="241"/>
-      <c r="D7" s="241"/>
-      <c r="E7" s="241"/>
-      <c r="F7" s="241"/>
-      <c r="G7" s="241"/>
-      <c r="H7" s="241"/>
-      <c r="I7" s="241"/>
-      <c r="J7" s="241"/>
-      <c r="K7" s="218"/>
-      <c r="L7" s="218"/>
-      <c r="M7" s="218"/>
+      <c r="A7" s="244" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" s="245"/>
+      <c r="C7" s="245"/>
+      <c r="D7" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
+      <c r="I7" s="245"/>
+      <c r="J7" s="245"/>
+      <c r="K7" s="217"/>
+      <c r="L7" s="217"/>
+      <c r="M7" s="217"/>
       <c r="N7" s="182" t="s">
         <v>202</v>
       </c>
-      <c r="O7" s="202"/>
-      <c r="P7" s="202"/>
-      <c r="Q7" s="202"/>
-      <c r="R7" s="205"/>
-      <c r="S7" s="208"/>
+      <c r="O7" s="201"/>
+      <c r="P7" s="201"/>
+      <c r="Q7" s="201"/>
+      <c r="R7" s="204"/>
+      <c r="S7" s="207"/>
       <c r="T7" s="181"/>
-      <c r="U7" s="208"/>
-      <c r="V7" s="208"/>
-      <c r="W7" s="210"/>
-      <c r="X7" s="210"/>
-      <c r="Y7" s="210"/>
-      <c r="Z7" s="210"/>
-      <c r="AA7" s="210"/>
-      <c r="AB7" s="210"/>
-      <c r="AC7" s="210"/>
-      <c r="AD7" s="198"/>
+      <c r="U7" s="207"/>
+      <c r="V7" s="207"/>
+      <c r="W7" s="209"/>
+      <c r="X7" s="209"/>
+      <c r="Y7" s="209"/>
+      <c r="Z7" s="209"/>
+      <c r="AA7" s="209"/>
+      <c r="AB7" s="209"/>
+      <c r="AC7" s="209"/>
+      <c r="AD7" s="197"/>
     </row>
     <row r="8" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="240" t="s">
-        <v>350</v>
-      </c>
-      <c r="B8" s="241"/>
-      <c r="C8" s="241"/>
-      <c r="D8" s="241"/>
-      <c r="E8" s="241"/>
-      <c r="F8" s="241"/>
-      <c r="G8" s="241"/>
-      <c r="H8" s="241"/>
-      <c r="I8" s="241"/>
-      <c r="J8" s="241"/>
-      <c r="K8" s="218"/>
-      <c r="L8" s="218"/>
-      <c r="M8" s="218"/>
+      <c r="A8" s="244" t="s">
+        <v>345</v>
+      </c>
+      <c r="B8" s="245"/>
+      <c r="C8" s="245"/>
+      <c r="D8" s="245"/>
+      <c r="E8" s="245"/>
+      <c r="F8" s="245"/>
+      <c r="G8" s="245"/>
+      <c r="H8" s="245"/>
+      <c r="I8" s="245"/>
+      <c r="J8" s="245"/>
+      <c r="K8" s="217"/>
+      <c r="L8" s="217"/>
+      <c r="M8" s="217"/>
       <c r="N8" s="180" t="str">
         <f>"- h: Height of rectangular section (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- h: Height of rectangular section (Input as Float) (m)</v>
       </c>
-      <c r="O8" s="202"/>
-      <c r="P8" s="202"/>
-      <c r="Q8" s="202"/>
-      <c r="R8" s="206"/>
-      <c r="S8" s="208"/>
+      <c r="O8" s="201"/>
+      <c r="P8" s="201"/>
+      <c r="Q8" s="201"/>
+      <c r="R8" s="205"/>
+      <c r="S8" s="207"/>
       <c r="T8" s="181"/>
-      <c r="U8" s="208"/>
-      <c r="V8" s="208"/>
-      <c r="W8" s="210"/>
-      <c r="X8" s="210"/>
-      <c r="Y8" s="210"/>
-      <c r="Z8" s="210"/>
-      <c r="AA8" s="210"/>
-      <c r="AB8" s="210"/>
-      <c r="AC8" s="210"/>
-      <c r="AD8" s="198"/>
+      <c r="U8" s="207"/>
+      <c r="V8" s="207"/>
+      <c r="W8" s="209"/>
+      <c r="X8" s="209"/>
+      <c r="Y8" s="209"/>
+      <c r="Z8" s="209"/>
+      <c r="AA8" s="209"/>
+      <c r="AB8" s="209"/>
+      <c r="AC8" s="209"/>
+      <c r="AD8" s="197"/>
     </row>
     <row r="9" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="240" t="s">
-        <v>351</v>
-      </c>
-      <c r="B9" s="241"/>
-      <c r="C9" s="241"/>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="218"/>
-      <c r="L9" s="218"/>
-      <c r="M9" s="218"/>
+      <c r="A9" s="244" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" s="245"/>
+      <c r="C9" s="245"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="245"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="245"/>
+      <c r="J9" s="245"/>
+      <c r="K9" s="217"/>
+      <c r="L9" s="217"/>
+      <c r="M9" s="217"/>
       <c r="N9" s="180" t="str">
         <f>"- b: Width of rectangular section (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- b: Width of rectangular section (Input as Float) (m)</v>
       </c>
-      <c r="O9" s="202"/>
-      <c r="P9" s="202"/>
-      <c r="Q9" s="202"/>
-      <c r="R9" s="206"/>
-      <c r="S9" s="208"/>
+      <c r="O9" s="201"/>
+      <c r="P9" s="201"/>
+      <c r="Q9" s="201"/>
+      <c r="R9" s="205"/>
+      <c r="S9" s="207"/>
       <c r="T9" s="181"/>
-      <c r="U9" s="208"/>
-      <c r="V9" s="208"/>
-      <c r="W9" s="210"/>
-      <c r="X9" s="210"/>
-      <c r="Y9" s="210"/>
-      <c r="Z9" s="210"/>
-      <c r="AA9" s="210"/>
-      <c r="AB9" s="210"/>
-      <c r="AC9" s="210"/>
-      <c r="AD9" s="198"/>
+      <c r="U9" s="207"/>
+      <c r="V9" s="207"/>
+      <c r="W9" s="209"/>
+      <c r="X9" s="209"/>
+      <c r="Y9" s="209"/>
+      <c r="Z9" s="209"/>
+      <c r="AA9" s="209"/>
+      <c r="AB9" s="209"/>
+      <c r="AC9" s="209"/>
+      <c r="AD9" s="197"/>
     </row>
     <row r="10" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="240" t="s">
-        <v>352</v>
-      </c>
-      <c r="B10" s="241"/>
-      <c r="C10" s="241"/>
-      <c r="D10" s="241"/>
-      <c r="E10" s="241"/>
-      <c r="F10" s="241"/>
-      <c r="G10" s="241"/>
-      <c r="H10" s="241"/>
-      <c r="I10" s="241"/>
-      <c r="J10" s="241"/>
-      <c r="K10" s="218"/>
-      <c r="L10" s="218"/>
-      <c r="M10" s="218"/>
+      <c r="A10" s="244" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="245"/>
+      <c r="G10" s="245"/>
+      <c r="H10" s="245"/>
+      <c r="I10" s="245"/>
+      <c r="J10" s="245"/>
+      <c r="K10" s="217"/>
+      <c r="L10" s="217"/>
+      <c r="M10" s="217"/>
       <c r="N10" s="173" t="str">
         <f>"- c: Concrete cover (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- c: Concrete cover (Input as Float) (m)</v>
       </c>
-      <c r="O10" s="202"/>
-      <c r="P10" s="202"/>
-      <c r="Q10" s="202"/>
-      <c r="R10" s="207"/>
-      <c r="S10" s="208"/>
+      <c r="O10" s="201"/>
+      <c r="P10" s="201"/>
+      <c r="Q10" s="201"/>
+      <c r="R10" s="206"/>
+      <c r="S10" s="207"/>
       <c r="T10" s="181"/>
-      <c r="U10" s="208"/>
-      <c r="V10" s="208"/>
-      <c r="W10" s="210"/>
-      <c r="X10" s="210"/>
-      <c r="Y10" s="210"/>
-      <c r="Z10" s="210"/>
-      <c r="AA10" s="210"/>
-      <c r="AB10" s="210"/>
-      <c r="AC10" s="210"/>
-      <c r="AD10" s="198"/>
+      <c r="U10" s="207"/>
+      <c r="V10" s="207"/>
+      <c r="W10" s="209"/>
+      <c r="X10" s="209"/>
+      <c r="Y10" s="209"/>
+      <c r="Z10" s="209"/>
+      <c r="AA10" s="209"/>
+      <c r="AB10" s="209"/>
+      <c r="AC10" s="209"/>
+      <c r="AD10" s="197"/>
     </row>
     <row r="11" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="240" t="s">
-        <v>353</v>
-      </c>
-      <c r="B11" s="241"/>
-      <c r="C11" s="241"/>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="218"/>
-      <c r="L11" s="218"/>
-      <c r="M11" s="218"/>
+      <c r="A11" s="244" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="245"/>
+      <c r="C11" s="245"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="217"/>
+      <c r="L11" s="217"/>
+      <c r="M11" s="217"/>
       <c r="N11" s="180" t="str">
         <f>"- barDiaHoop: Diameter of hoops (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- barDiaHoop: Diameter of hoops (Input as Float) (m)</v>
       </c>
-      <c r="O11" s="202"/>
-      <c r="P11" s="202"/>
-      <c r="Q11" s="202"/>
-      <c r="R11" s="206"/>
-      <c r="S11" s="208"/>
+      <c r="O11" s="201"/>
+      <c r="P11" s="201"/>
+      <c r="Q11" s="201"/>
+      <c r="R11" s="205"/>
+      <c r="S11" s="207"/>
       <c r="T11" s="181"/>
-      <c r="U11" s="208"/>
-      <c r="V11" s="208"/>
-      <c r="W11" s="210"/>
-      <c r="X11" s="210"/>
-      <c r="Y11" s="210"/>
-      <c r="Z11" s="210"/>
-      <c r="AA11" s="210"/>
-      <c r="AB11" s="210"/>
-      <c r="AC11" s="210"/>
-      <c r="AD11" s="198"/>
+      <c r="U11" s="207"/>
+      <c r="V11" s="207"/>
+      <c r="W11" s="209"/>
+      <c r="X11" s="209"/>
+      <c r="Y11" s="209"/>
+      <c r="Z11" s="209"/>
+      <c r="AA11" s="209"/>
+      <c r="AB11" s="209"/>
+      <c r="AC11" s="209"/>
+      <c r="AD11" s="197"/>
     </row>
     <row r="12" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="220" t="s">
-        <v>334</v>
-      </c>
-      <c r="B12" s="202"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="202"/>
-      <c r="G12" s="202"/>
-      <c r="H12" s="202"/>
-      <c r="I12" s="202"/>
-      <c r="J12" s="206"/>
-      <c r="K12" s="206"/>
-      <c r="L12" s="206"/>
-      <c r="M12" s="206"/>
+      <c r="A12" s="219" t="s">
+        <v>329</v>
+      </c>
+      <c r="B12" s="201"/>
+      <c r="C12" s="201"/>
+      <c r="D12" s="201"/>
+      <c r="E12" s="201"/>
+      <c r="F12" s="201"/>
+      <c r="G12" s="201"/>
+      <c r="H12" s="201"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="205"/>
+      <c r="K12" s="205"/>
+      <c r="L12" s="205"/>
+      <c r="M12" s="205"/>
       <c r="N12" s="180" t="str">
         <f>"- barDiaTop: Diameter of top reinforcements (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- barDiaTop: Diameter of top reinforcements (Input as Float) (m)</v>
       </c>
-      <c r="O12" s="208"/>
-      <c r="P12" s="208"/>
-      <c r="Q12" s="208"/>
-      <c r="R12" s="206"/>
-      <c r="S12" s="208"/>
+      <c r="O12" s="207"/>
+      <c r="P12" s="207"/>
+      <c r="Q12" s="207"/>
+      <c r="R12" s="205"/>
+      <c r="S12" s="207"/>
       <c r="T12" s="181"/>
-      <c r="U12" s="208"/>
-      <c r="V12" s="208"/>
-      <c r="W12" s="210"/>
-      <c r="X12" s="210"/>
-      <c r="Y12" s="210"/>
-      <c r="Z12" s="210"/>
-      <c r="AA12" s="210"/>
-      <c r="AB12" s="210"/>
-      <c r="AC12" s="210"/>
-      <c r="AD12" s="198"/>
+      <c r="U12" s="207"/>
+      <c r="V12" s="207"/>
+      <c r="W12" s="209"/>
+      <c r="X12" s="209"/>
+      <c r="Y12" s="209"/>
+      <c r="Z12" s="209"/>
+      <c r="AA12" s="209"/>
+      <c r="AB12" s="209"/>
+      <c r="AC12" s="209"/>
+      <c r="AD12" s="197"/>
     </row>
     <row r="13" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="220" t="s">
-        <v>335</v>
-      </c>
-      <c r="B13" s="204"/>
-      <c r="C13" s="204"/>
-      <c r="D13" s="204"/>
-      <c r="E13" s="204"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="204"/>
-      <c r="H13" s="204"/>
-      <c r="I13" s="204"/>
-      <c r="J13" s="206"/>
-      <c r="K13" s="206"/>
-      <c r="L13" s="206"/>
-      <c r="M13" s="206"/>
+      <c r="A13" s="219" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="203"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="203"/>
+      <c r="H13" s="203"/>
+      <c r="I13" s="203"/>
+      <c r="J13" s="205"/>
+      <c r="K13" s="205"/>
+      <c r="L13" s="205"/>
+      <c r="M13" s="205"/>
       <c r="N13" s="180" t="str">
         <f>"- barDiaBot: Diameter of bottom reinforcements (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- barDiaBot: Diameter of bottom reinforcements (Input as Float) (m)</v>
       </c>
-      <c r="O13" s="208"/>
-      <c r="P13" s="208"/>
-      <c r="Q13" s="208"/>
-      <c r="R13" s="206"/>
-      <c r="S13" s="208"/>
+      <c r="O13" s="207"/>
+      <c r="P13" s="207"/>
+      <c r="Q13" s="207"/>
+      <c r="R13" s="205"/>
+      <c r="S13" s="207"/>
       <c r="T13" s="181"/>
-      <c r="U13" s="208"/>
-      <c r="V13" s="208"/>
-      <c r="W13" s="210"/>
-      <c r="X13" s="210"/>
-      <c r="Y13" s="210"/>
-      <c r="Z13" s="210"/>
-      <c r="AA13" s="210"/>
-      <c r="AB13" s="210"/>
-      <c r="AC13" s="210"/>
-      <c r="AD13" s="198"/>
+      <c r="U13" s="207"/>
+      <c r="V13" s="207"/>
+      <c r="W13" s="209"/>
+      <c r="X13" s="209"/>
+      <c r="Y13" s="209"/>
+      <c r="Z13" s="209"/>
+      <c r="AA13" s="209"/>
+      <c r="AB13" s="209"/>
+      <c r="AC13" s="209"/>
+      <c r="AD13" s="197"/>
     </row>
     <row r="14" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="201" t="s">
+      <c r="A14" s="200" t="s">
         <v>301</v>
       </c>
-      <c r="B14" s="204"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="204"/>
-      <c r="H14" s="204"/>
-      <c r="I14" s="204"/>
-      <c r="J14" s="206"/>
-      <c r="K14" s="206"/>
-      <c r="L14" s="206"/>
-      <c r="M14" s="206"/>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="203"/>
+      <c r="I14" s="203"/>
+      <c r="J14" s="205"/>
+      <c r="K14" s="205"/>
+      <c r="L14" s="205"/>
+      <c r="M14" s="205"/>
       <c r="N14" s="180" t="str">
         <f>"- barDiaInt: Diameter of intermediate reinforcements (Input as Float) ("&amp;'User Defined Units'!$B$11&amp;")"</f>
         <v>- barDiaInt: Diameter of intermediate reinforcements (Input as Float) (m)</v>
       </c>
-      <c r="O14" s="208"/>
-      <c r="P14" s="208"/>
-      <c r="Q14" s="208"/>
-      <c r="R14" s="206"/>
-      <c r="S14" s="208"/>
+      <c r="O14" s="207"/>
+      <c r="P14" s="207"/>
+      <c r="Q14" s="207"/>
+      <c r="R14" s="205"/>
+      <c r="S14" s="207"/>
       <c r="T14" s="181"/>
-      <c r="U14" s="208"/>
-      <c r="V14" s="208"/>
-      <c r="W14" s="210"/>
-      <c r="X14" s="210"/>
-      <c r="Y14" s="210"/>
-      <c r="Z14" s="210"/>
-      <c r="AA14" s="210"/>
-      <c r="AB14" s="210"/>
-      <c r="AC14" s="210"/>
-      <c r="AD14" s="198"/>
+      <c r="U14" s="207"/>
+      <c r="V14" s="207"/>
+      <c r="W14" s="209"/>
+      <c r="X14" s="209"/>
+      <c r="Y14" s="209"/>
+      <c r="Z14" s="209"/>
+      <c r="AA14" s="209"/>
+      <c r="AB14" s="209"/>
+      <c r="AC14" s="209"/>
+      <c r="AD14" s="197"/>
     </row>
     <row r="15" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="203"/>
-      <c r="B15" s="204"/>
-      <c r="C15" s="204"/>
-      <c r="D15" s="204"/>
-      <c r="E15" s="204"/>
-      <c r="F15" s="204"/>
-      <c r="G15" s="204"/>
-      <c r="H15" s="204"/>
-      <c r="I15" s="204"/>
-      <c r="J15" s="206"/>
-      <c r="K15" s="206"/>
-      <c r="L15" s="206"/>
-      <c r="M15" s="206"/>
+      <c r="A15" s="202"/>
+      <c r="B15" s="203"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="203"/>
+      <c r="G15" s="203"/>
+      <c r="H15" s="203"/>
+      <c r="I15" s="203"/>
+      <c r="J15" s="205"/>
+      <c r="K15" s="205"/>
+      <c r="L15" s="205"/>
+      <c r="M15" s="205"/>
       <c r="N15" s="180" t="s">
         <v>168</v>
       </c>
-      <c r="O15" s="208"/>
-      <c r="P15" s="208"/>
-      <c r="Q15" s="208"/>
-      <c r="R15" s="206"/>
-      <c r="S15" s="208"/>
+      <c r="O15" s="207"/>
+      <c r="P15" s="207"/>
+      <c r="Q15" s="207"/>
+      <c r="R15" s="205"/>
+      <c r="S15" s="207"/>
       <c r="T15" s="181"/>
-      <c r="U15" s="208"/>
-      <c r="V15" s="208"/>
-      <c r="W15" s="210"/>
-      <c r="X15" s="210"/>
-      <c r="Y15" s="210"/>
-      <c r="Z15" s="210"/>
-      <c r="AA15" s="210"/>
-      <c r="AB15" s="210"/>
-      <c r="AC15" s="210"/>
-      <c r="AD15" s="198"/>
+      <c r="U15" s="207"/>
+      <c r="V15" s="207"/>
+      <c r="W15" s="209"/>
+      <c r="X15" s="209"/>
+      <c r="Y15" s="209"/>
+      <c r="Z15" s="209"/>
+      <c r="AA15" s="209"/>
+      <c r="AB15" s="209"/>
+      <c r="AC15" s="209"/>
+      <c r="AD15" s="197"/>
     </row>
     <row r="16" spans="1:30" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="183" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="204"/>
-      <c r="C16" s="204"/>
-      <c r="D16" s="204"/>
-      <c r="E16" s="204"/>
-      <c r="F16" s="204"/>
-      <c r="G16" s="204"/>
-      <c r="H16" s="204"/>
-      <c r="I16" s="204"/>
-      <c r="J16" s="206"/>
-      <c r="K16" s="206"/>
-      <c r="L16" s="206"/>
-      <c r="M16" s="206"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="203"/>
+      <c r="G16" s="203"/>
+      <c r="H16" s="203"/>
+      <c r="I16" s="203"/>
+      <c r="J16" s="205"/>
+      <c r="K16" s="205"/>
+      <c r="L16" s="205"/>
+      <c r="M16" s="205"/>
       <c r="N16" s="180" t="s">
         <v>169</v>
       </c>
-      <c r="O16" s="208"/>
-      <c r="P16" s="208"/>
-      <c r="Q16" s="208"/>
-      <c r="R16" s="206"/>
-      <c r="S16" s="208"/>
+      <c r="O16" s="207"/>
+      <c r="P16" s="207"/>
+      <c r="Q16" s="207"/>
+      <c r="R16" s="205"/>
+      <c r="S16" s="207"/>
       <c r="T16" s="181"/>
-      <c r="U16" s="208"/>
-      <c r="V16" s="208"/>
-      <c r="W16" s="210"/>
-      <c r="X16" s="210"/>
-      <c r="Y16" s="210"/>
-      <c r="Z16" s="210"/>
-      <c r="AA16" s="210"/>
-      <c r="AB16" s="210"/>
-      <c r="AC16" s="210"/>
-      <c r="AD16" s="198"/>
+      <c r="U16" s="207"/>
+      <c r="V16" s="207"/>
+      <c r="W16" s="209"/>
+      <c r="X16" s="209"/>
+      <c r="Y16" s="209"/>
+      <c r="Z16" s="209"/>
+      <c r="AA16" s="209"/>
+      <c r="AB16" s="209"/>
+      <c r="AC16" s="209"/>
+      <c r="AD16" s="197"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="184" t="s">
@@ -22655,29 +24082,29 @@
       <c r="G17" s="185"/>
       <c r="H17" s="185"/>
       <c r="I17" s="185"/>
-      <c r="J17" s="211"/>
-      <c r="K17" s="211"/>
-      <c r="L17" s="211"/>
-      <c r="M17" s="211"/>
-      <c r="N17" s="213" t="s">
+      <c r="J17" s="210"/>
+      <c r="K17" s="210"/>
+      <c r="L17" s="210"/>
+      <c r="M17" s="210"/>
+      <c r="N17" s="212" t="s">
         <v>170</v>
       </c>
       <c r="O17" s="186"/>
       <c r="P17" s="186"/>
       <c r="Q17" s="186"/>
-      <c r="R17" s="211"/>
+      <c r="R17" s="210"/>
       <c r="S17" s="186"/>
       <c r="T17" s="187"/>
       <c r="U17" s="186"/>
       <c r="V17" s="186"/>
-      <c r="W17" s="199"/>
-      <c r="X17" s="199"/>
-      <c r="Y17" s="199"/>
-      <c r="Z17" s="199"/>
-      <c r="AA17" s="199"/>
-      <c r="AB17" s="199"/>
-      <c r="AC17" s="199"/>
-      <c r="AD17" s="200"/>
+      <c r="W17" s="198"/>
+      <c r="X17" s="198"/>
+      <c r="Y17" s="198"/>
+      <c r="Z17" s="198"/>
+      <c r="AA17" s="198"/>
+      <c r="AB17" s="198"/>
+      <c r="AC17" s="198"/>
+      <c r="AD17" s="199"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="188"/>
@@ -22743,13 +24170,13 @@
         <v>27</v>
       </c>
       <c r="K19" s="125" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="L19" s="125" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="M19" s="125" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="N19" s="125" t="s">
         <v>28</v>
@@ -22928,13 +24355,13 @@
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A22" s="195"/>
+      <c r="A22" s="228"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A23" s="223"/>
+      <c r="A23" s="222"/>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A24" s="229"/>
+      <c r="A24" s="228"/>
       <c r="C24" s="191" t="str">
         <f t="shared" ref="C24:C86" si="0">IF(A24=0,"","Elastic")</f>
         <v/>
@@ -28920,32 +30347,32 @@
     <mergeCell ref="A8:J8"/>
   </mergeCells>
   <conditionalFormatting sqref="E20:J1048576">
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>OR($C20="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K20:K1048576">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>OR(AND($A20&lt;&gt;"",$J20=""),$J20="Hinge Radau")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20:M1048576">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>OR(AND($A20&lt;&gt;"",$J20=""),$J20="Lobatto")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20:N1048576">
-    <cfRule type="expression" dxfId="4" priority="9">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>OR($C20="Elastic",$C20="Fiber")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O20:AD1048576">
-    <cfRule type="expression" dxfId="3" priority="8">
+    <cfRule type="expression" dxfId="5" priority="8">
       <formula>AND($C20="Aggregator",$N20&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W20:AD1048576">
-    <cfRule type="expression" dxfId="2" priority="12">
+    <cfRule type="expression" dxfId="4" priority="12">
       <formula>OR($C20="Elastic")</formula>
     </cfRule>
   </conditionalFormatting>

--- a/src/sadpropy/model_inputfile.xlsx
+++ b/src/sadpropy/model_inputfile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SadProPy\src\sadpropy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FFCC10-122B-49E7-852B-5FB9E744AFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088BEBC2-C18A-4100-A589-736026C683AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="836" firstSheet="1" activeTab="6" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="836" firstSheet="8" activeTab="14" xr2:uid="{59A5497E-26E6-41F2-97A3-F930024339A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design Preferences" sheetId="25" r:id="rId1"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="443">
   <si>
     <t>SI (N-m)</t>
   </si>
@@ -1419,12 +1419,6 @@
   </si>
   <si>
     <t>Comb1</t>
-  </si>
-  <si>
-    <t>Comb2</t>
-  </si>
-  <si>
-    <t>Comb3</t>
   </si>
   <si>
     <t>Load Name 2</t>
@@ -16797,7 +16791,7 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="252" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B2" s="248"/>
       <c r="C2" s="270"/>
@@ -16822,7 +16816,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="252" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B3" s="249"/>
       <c r="C3" s="270"/>
@@ -16847,7 +16841,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="279" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B4" s="250"/>
       <c r="C4" s="257"/>
@@ -16904,58 +16898,58 @@
         <v>392</v>
       </c>
       <c r="D6" s="125" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E6" s="260" t="s">
         <v>393</v>
       </c>
       <c r="F6" s="125" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G6" s="260" t="s">
         <v>394</v>
       </c>
       <c r="H6" s="125" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="I6" s="260" t="s">
         <v>395</v>
       </c>
       <c r="J6" s="125" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K6" s="260" t="s">
         <v>396</v>
       </c>
       <c r="L6" s="125" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="M6" s="260" t="s">
         <v>397</v>
       </c>
       <c r="N6" s="125" t="s">
+        <v>433</v>
+      </c>
+      <c r="O6" s="260" t="s">
+        <v>434</v>
+      </c>
+      <c r="P6" s="125" t="s">
         <v>435</v>
       </c>
-      <c r="O6" s="260" t="s">
+      <c r="Q6" s="260" t="s">
         <v>436</v>
       </c>
-      <c r="P6" s="125" t="s">
+      <c r="R6" s="125" t="s">
         <v>437</v>
       </c>
-      <c r="Q6" s="260" t="s">
+      <c r="S6" s="260" t="s">
         <v>438</v>
       </c>
-      <c r="R6" s="125" t="s">
+      <c r="T6" s="125" t="s">
         <v>439</v>
       </c>
-      <c r="S6" s="260" t="s">
+      <c r="U6" s="260" t="s">
         <v>440</v>
-      </c>
-      <c r="T6" s="125" t="s">
-        <v>441</v>
-      </c>
-      <c r="U6" s="260" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -16970,14 +16964,10 @@
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="251" t="s">
-        <v>427</v>
-      </c>
+      <c r="A8" s="251"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="251" t="s">
-        <v>428</v>
-      </c>
+      <c r="A9" s="251"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="251"/>
